--- a/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10116FB6-0979-4ABD-8D4D-E865E0EEC142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A319FA60-CFAF-4416-A523-15D876003440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="8" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="画面設計書" sheetId="7" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
@@ -68,9 +65,6 @@
   </si>
   <si>
     <t>承認印</t>
-  </si>
-  <si>
-    <t>ユースケース名</t>
   </si>
   <si>
     <t>概要</t>
@@ -338,73 +332,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク一覧画面が表示されている。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスク情報の取得に失敗した場合
-a. システムエラーが発生する。
-b. システムはエラーメッセージを表示する。
-c. システムは処理を終了する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・.登録済みタスクが存在しない場合
-a. システムはタスク情報を取得する。
-b. システムは登録済みタスクが存在しないことを確認する。
-c. システムは「表示するタスクがありません。」というメッセージを表示する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1,社員はメニュー画面で「タスク一覧」を選択する。
-2,システムは社員のタスク情報を取得する。
-3,システムは取得したタスク情報を一覧形式で表示する。
-4,社員はタスク一覧を参照する。</t>
-    <rPh sb="2" eb="4">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>社員がシステムにログインしている。</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>社員</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>社員が現在の登録済みタスク一覧を参照する。</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>トウロクズ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク一覧表示</t>
     <rPh sb="3" eb="7">
       <t>イチランヒョウジ</t>
@@ -420,6 +347,72 @@
   </si>
   <si>
     <t>TaskBoy（TasBo）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザが現在の登録済みタスク一覧を参照する。</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>トウロクズ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユースケース名+A5:J12D10A5:J13A5:J11A5:J12A5:J13</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザがログイン済みであること/メニュー画面が表示されていること</t>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1,ユーザはメニュー画面で「タスク一覧表示」を選択する。
+2,システムはユーザのタスク情報を取得する。
+3,システムは取得したタスク情報を一覧形式で表示する。
+4,ユーザはタスク一覧を参照する。</t>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>成功時 : タスク一覧画面が表示されている/社員がタスク情報を参照可能な状態になっている。
+タスク未登録時 : タスク一覧画面が表示されている/「表示するデータが存在しません」が表示されている。</t>
+    <rPh sb="0" eb="3">
+      <t>セイコウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1. 表示対象のタスクが存在しない場合（基本フロー2から分岐）
+a. システムはタスク情報を取得する。
+b. システムは表示対象のタスクが存在しないことを判定する。
+c. システムは「表示するデータが存在しません」を表示する。</t>
+    <rPh sb="101" eb="103">
+      <t>ソンザイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1475,125 +1468,290 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1619,6 +1777,111 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1633,276 +1896,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2227,36 +2220,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="表紙 "/>
-      <sheetName val="ユースケース記述"/>
-      <sheetName val="画面遷移図"/>
-      <sheetName val="詳細クラス図"/>
-      <sheetName val="画面設計書"/>
-      <sheetName val="テスト仕様書兼結果報告書"/>
-      <sheetName val="JUnitテスト仕様書兼報告書"/>
-      <sheetName val="カバレッジレポート　ログイン"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -2458,166 +2421,166 @@
   <dimension ref="C1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="16" width="7.7109375" style="138" customWidth="1"/>
-    <col min="17" max="26" width="8.7109375" style="138" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="138"/>
+    <col min="1" max="16" width="7.7109375" style="44" customWidth="1"/>
+    <col min="17" max="26" width="8.7109375" style="44" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="44"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="141"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="45"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="142"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="142"/>
-      <c r="N3" s="142"/>
-      <c r="O3" s="142"/>
-      <c r="P3" s="141"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="45"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142"/>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142"/>
-      <c r="P4" s="141"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="45"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-      <c r="M5" s="142"/>
-      <c r="N5" s="142"/>
-      <c r="O5" s="142"/>
-      <c r="P5" s="141"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
+      <c r="P5" s="45"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="142"/>
-      <c r="D6" s="142"/>
-      <c r="E6" s="142"/>
-      <c r="F6" s="142"/>
-      <c r="G6" s="142"/>
-      <c r="H6" s="142"/>
-      <c r="I6" s="142"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="142"/>
-      <c r="N6" s="142"/>
-      <c r="O6" s="142"/>
-      <c r="P6" s="141"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
+      <c r="P6" s="45"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="143"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="143"/>
-      <c r="I7" s="143"/>
-      <c r="J7" s="143"/>
-      <c r="K7" s="143"/>
-      <c r="L7" s="143"/>
-      <c r="M7" s="143"/>
-      <c r="N7" s="143"/>
-      <c r="O7" s="143"/>
-      <c r="P7" s="141"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="45"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="144" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="142"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="142"/>
+      <c r="E8" s="96" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="145" t="s">
+      <c r="G13" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="146"/>
-      <c r="I13" s="147">
+      <c r="H13" s="90"/>
+      <c r="I13" s="97">
         <v>46175</v>
       </c>
-      <c r="J13" s="148"/>
-      <c r="K13" s="146"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="90"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="145"/>
-      <c r="H14" s="146"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="148"/>
-      <c r="K14" s="146"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="90"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="145"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="145"/>
-      <c r="J15" s="148"/>
-      <c r="K15" s="146"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="90"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
-      <c r="I16" s="149"/>
-      <c r="J16" s="149"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="150" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="142"/>
-      <c r="I17" s="142"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="142"/>
+      <c r="G17" s="92" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -2634,974 +2597,974 @@
     <row r="30" spans="7:11" ht="12.75" customHeight="1"/>
     <row r="31" spans="7:11" ht="12.75" customHeight="1"/>
     <row r="32" spans="7:11" ht="12.75" customHeight="1"/>
-    <row r="33" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="138" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="G15:H15"/>
@@ -3632,1223 +3595,1206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="133" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="168"/>
-      <c r="F1" s="133" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="168"/>
+      <c r="G1" s="111"/>
       <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="183" t="s">
+      <c r="J1" s="48" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="180"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="134" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="112" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="113"/>
+      <c r="F2" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="113"/>
+      <c r="H2" s="116">
+        <v>46175</v>
+      </c>
+      <c r="I2" s="122" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="123"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="124"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="107"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="125"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="126" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="127"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="128" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="129"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="99"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="100"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="99"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="98" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="100"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="130" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="99"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="119" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="100"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="121"/>
+      <c r="D9" s="119" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="100"/>
+    </row>
+    <row r="10" spans="1:10" ht="84" customHeight="1">
+      <c r="A10" s="137"/>
+      <c r="B10" s="120" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="121"/>
+      <c r="D10" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="182"/>
-      <c r="F2" s="134" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="182"/>
-      <c r="H2" s="181">
-        <v>46175</v>
-      </c>
-      <c r="I2" s="114" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="100"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="138"/>
+      <c r="B11" s="120" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="121"/>
+      <c r="D11" s="119" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100"/>
+    </row>
+    <row r="12" spans="1:10" ht="72" customHeight="1">
+      <c r="A12" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="99"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="J2" s="116"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="180"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="176"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="175"/>
-      <c r="B4" s="174"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="172"/>
-      <c r="H4" s="171"/>
-      <c r="I4" s="171"/>
-      <c r="J4" s="170"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="166"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="167" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="166"/>
-      <c r="I5" s="166"/>
-      <c r="J5" s="165"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="159" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="157"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="157"/>
-      <c r="J6" s="156"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="159" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="157"/>
-      <c r="C7" s="158"/>
-      <c r="D7" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="156"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="159" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="157"/>
-      <c r="C8" s="158"/>
-      <c r="D8" s="160" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157"/>
-      <c r="I8" s="157"/>
-      <c r="J8" s="156"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="164" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="161" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="158"/>
-      <c r="D9" s="160" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="157"/>
-      <c r="F9" s="157"/>
-      <c r="G9" s="157"/>
-      <c r="H9" s="157"/>
-      <c r="I9" s="157"/>
-      <c r="J9" s="156"/>
-    </row>
-    <row r="10" spans="1:10" ht="84" customHeight="1">
-      <c r="A10" s="163"/>
-      <c r="B10" s="161" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="158"/>
-      <c r="D10" s="160" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="157"/>
-      <c r="H10" s="157"/>
-      <c r="I10" s="157"/>
-      <c r="J10" s="156"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="162"/>
-      <c r="B11" s="161" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="158"/>
-      <c r="D11" s="160" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="156"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="159" t="s">
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="100"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="157"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="105" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="157"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="157"/>
-      <c r="H12" s="157"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="156"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="155" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="152"/>
-      <c r="C13" s="154"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="152"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="152"/>
-      <c r="I13" s="152"/>
-      <c r="J13" s="151"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="135"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="17" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="18" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="19" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="20" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="21" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="22" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="23" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="24" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="25" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="26" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="27" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="28" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="29" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="30" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="31" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="32" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="33" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="33" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="17" ht="12.75" customHeight="1"/>
+    <row r="18" ht="12.75" customHeight="1"/>
+    <row r="19" ht="12.75" customHeight="1"/>
+    <row r="20" ht="12.75" customHeight="1"/>
+    <row r="21" ht="12.75" customHeight="1"/>
+    <row r="22" ht="12.75" customHeight="1"/>
+    <row r="23" ht="12.75" customHeight="1"/>
+    <row r="24" ht="12.75" customHeight="1"/>
+    <row r="25" ht="12.75" customHeight="1"/>
+    <row r="26" ht="12.75" customHeight="1"/>
+    <row r="27" ht="12.75" customHeight="1"/>
+    <row r="28" ht="12.75" customHeight="1"/>
+    <row r="29" ht="12.75" customHeight="1"/>
+    <row r="30" ht="12.75" customHeight="1"/>
+    <row r="31" ht="12.75" customHeight="1"/>
+    <row r="32" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4859,6 +4805,23 @@
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4877,19 +4840,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="82" t="s">
+      <c r="A1" s="145" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="82" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -4901,40 +4864,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="87"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="142"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="88"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="143"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="89"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="144"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -6290,19 +6253,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="82" t="s">
+      <c r="A1" s="145" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="82" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -6314,48 +6277,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="73"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="65" t="s">
+      <c r="G2" s="60"/>
+      <c r="H2" s="146">
+        <v>46182</v>
+      </c>
+      <c r="I2" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="91">
-        <v>46182</v>
-      </c>
-      <c r="I2" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="87"/>
+      <c r="J2" s="142"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="88"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="143"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="89"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="144"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -7707,19 +7670,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="129" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="133" t="s">
+      <c r="A1" s="164" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="165"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="120"/>
-      <c r="F1" s="133" t="s">
+      <c r="E1" s="155"/>
+      <c r="F1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="120"/>
+      <c r="G1" s="155"/>
       <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
@@ -7731,534 +7694,534 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="134" t="s">
+      <c r="A2" s="162"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="168"/>
+      <c r="F2" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="135"/>
-      <c r="F2" s="134" t="s">
+      <c r="G2" s="168"/>
+      <c r="H2" s="170">
+        <v>46182</v>
+      </c>
+      <c r="I2" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="137">
-        <v>46182</v>
-      </c>
-      <c r="I2" s="114" t="s">
+      <c r="J2" s="123"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="162"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="152"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="162"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="152"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="153" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="116"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="126"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="117"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="117"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="118" t="s">
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="157"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="158" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="121" t="s">
+      <c r="B6" s="148"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="150"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="161"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="162"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="163"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="162"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="163"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="162"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="163"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="162"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="163"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="162"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="163"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="162"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="163"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="158" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="148"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="148"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="150"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="158" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="148"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="98" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="122"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="106"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="123"/>
-      <c r="B7" s="124"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="125"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="126"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="128"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="126"/>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="128"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="126"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="128"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="126"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="128"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="126"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="128"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="126"/>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="128"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="112" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="106"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="112" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="103"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="105" t="s">
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="158" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="148"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="171" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="148"/>
+      <c r="J16" s="150"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="147">
+        <v>1</v>
+      </c>
+      <c r="B17" s="148"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="112" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="113" t="s">
+      <c r="F17" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="98"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="150"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="147">
+        <v>2</v>
+      </c>
+      <c r="B18" s="148"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I16" s="103"/>
-      <c r="J16" s="106"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="102">
-        <v>1</v>
-      </c>
-      <c r="B17" s="103"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="36" t="s">
+      <c r="G18" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="105"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="106"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="102">
-        <v>2</v>
-      </c>
-      <c r="B18" s="103"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="105"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="106"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="102">
+      <c r="A19" s="147">
         <v>3</v>
       </c>
-      <c r="B19" s="103"/>
-      <c r="C19" s="104"/>
+      <c r="B19" s="148"/>
+      <c r="C19" s="149"/>
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="106"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="102">
+      <c r="A20" s="147">
         <v>4</v>
       </c>
-      <c r="B20" s="103"/>
-      <c r="C20" s="104"/>
+      <c r="B20" s="148"/>
+      <c r="C20" s="149"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="106"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="148"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="102">
+      <c r="A21" s="147">
         <v>5</v>
       </c>
-      <c r="B21" s="103"/>
-      <c r="C21" s="104"/>
+      <c r="B21" s="148"/>
+      <c r="C21" s="149"/>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37"/>
       <c r="G21" s="37"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="106"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="102">
+      <c r="A22" s="147">
         <v>6</v>
       </c>
-      <c r="B22" s="103"/>
-      <c r="C22" s="104"/>
+      <c r="B22" s="148"/>
+      <c r="C22" s="149"/>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="37"/>
       <c r="G22" s="37"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="106"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="107">
+      <c r="A23" s="172">
         <v>7</v>
       </c>
-      <c r="B23" s="108"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="174"/>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="111"/>
+      <c r="H23" s="175"/>
+      <c r="I23" s="173"/>
+      <c r="J23" s="176"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="97">
+      <c r="A24" s="177">
         <v>8</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
+      <c r="B24" s="178"/>
+      <c r="C24" s="179"/>
       <c r="D24" s="40"/>
       <c r="E24" s="40"/>
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="101"/>
+      <c r="H24" s="180"/>
+      <c r="I24" s="178"/>
+      <c r="J24" s="181"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="112" t="s">
+      <c r="A25" s="158" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="148"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="148"/>
+      <c r="G25" s="148"/>
+      <c r="H25" s="148"/>
+      <c r="I25" s="148"/>
+      <c r="J25" s="150"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="158" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="106"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="112" t="s">
+      <c r="B26" s="148"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="98" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="103"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="105" t="s">
+      <c r="J26" s="35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="158" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="148"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="171" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="148"/>
+      <c r="J27" s="150"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="147">
+        <v>1</v>
+      </c>
+      <c r="B28" s="148"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28" s="98"/>
+      <c r="I28" s="148"/>
+      <c r="J28" s="150"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="147">
+        <v>2</v>
+      </c>
+      <c r="B29" s="148"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="112" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="103"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="113" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="103"/>
-      <c r="J27" s="106"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="102">
-        <v>1</v>
-      </c>
-      <c r="B28" s="103"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="105"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="106"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="102">
-        <v>2</v>
-      </c>
-      <c r="B29" s="103"/>
-      <c r="C29" s="104"/>
-      <c r="D29" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="105"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="106"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="148"/>
+      <c r="J29" s="150"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="102">
+      <c r="A30" s="147">
         <v>3</v>
       </c>
-      <c r="B30" s="103"/>
-      <c r="C30" s="104"/>
+      <c r="B30" s="148"/>
+      <c r="C30" s="149"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="103"/>
-      <c r="J30" s="106"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="150"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="102">
+      <c r="A31" s="147">
         <v>4</v>
       </c>
-      <c r="B31" s="103"/>
-      <c r="C31" s="104"/>
+      <c r="B31" s="148"/>
+      <c r="C31" s="149"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="106"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="148"/>
+      <c r="J31" s="150"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="102">
+      <c r="A32" s="147">
         <v>5</v>
       </c>
-      <c r="B32" s="103"/>
-      <c r="C32" s="104"/>
+      <c r="B32" s="148"/>
+      <c r="C32" s="149"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="106"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="148"/>
+      <c r="J32" s="150"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="107">
+      <c r="A33" s="172">
         <v>6</v>
       </c>
-      <c r="B33" s="108"/>
-      <c r="C33" s="109"/>
+      <c r="B33" s="173"/>
+      <c r="C33" s="174"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
-      <c r="H33" s="110"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="111"/>
+      <c r="H33" s="175"/>
+      <c r="I33" s="173"/>
+      <c r="J33" s="176"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="92">
+      <c r="A34" s="182">
         <v>7</v>
       </c>
-      <c r="B34" s="93"/>
-      <c r="C34" s="94"/>
+      <c r="B34" s="183"/>
+      <c r="C34" s="184"/>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="96"/>
+      <c r="H34" s="185"/>
+      <c r="I34" s="183"/>
+      <c r="J34" s="186"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="97">
+      <c r="A35" s="177">
         <v>8</v>
       </c>
-      <c r="B35" s="98"/>
-      <c r="C35" s="99"/>
+      <c r="B35" s="178"/>
+      <c r="C35" s="179"/>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="101"/>
+      <c r="H35" s="180"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="181"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9228,6 +9191,44 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -9244,44 +9245,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9301,182 +9264,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="75" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="77"/>
+      <c r="S1" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="78"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="73"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="67"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="73"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="68"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="74"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="69"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="56"/>
-      <c r="S1" s="82" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" s="58"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="74"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="75"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="76"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="57" t="s">
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="78"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="58"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="50"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="83"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="61"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="83"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -9504,11 +9467,11 @@
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
@@ -9538,7 +9501,7 @@
       <c r="C10" s="19"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="20"/>
@@ -9568,7 +9531,7 @@
       <c r="C11" s="19"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="20"/>
@@ -9598,7 +9561,7 @@
       <c r="C12" s="19"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="20"/>
@@ -9628,7 +9591,7 @@
       <c r="C13" s="21"/>
       <c r="D13" s="22"/>
       <c r="E13" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="22"/>
       <c r="G13" s="23"/>
@@ -9675,79 +9638,79 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="81" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="64" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="63" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="63" t="s">
+      <c r="H15" s="50"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="63" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="63" t="s">
+      <c r="M15" s="50"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="51"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="63" t="s">
+      <c r="P15" s="50"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="12" t="s">
+      <c r="S15" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="S15" s="12" t="s">
+      <c r="T15" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T15" s="24" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="84">
+        <v>1</v>
+      </c>
+      <c r="B16" s="51"/>
+      <c r="C16" s="85" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="44">
-        <v>1</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="46" t="s">
+      <c r="D16" s="51"/>
+      <c r="E16" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="46" t="s">
+      <c r="F16" s="51"/>
+      <c r="G16" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="62" t="s">
+      <c r="H16" s="50"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="62" t="s">
+      <c r="K16" s="51"/>
+      <c r="L16" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="L16" s="50" t="s">
+      <c r="M16" s="50"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="51"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="45"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="51"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
       <c r="T16" s="26"/>
@@ -9759,37 +9722,37 @@
       <c r="Z16" s="27"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="44">
+      <c r="A17" s="84">
         <v>2</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="46" t="s">
+      <c r="B17" s="51"/>
+      <c r="C17" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="51"/>
+      <c r="E17" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="46" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="62" t="s">
+      <c r="H17" s="50"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="62" t="s">
+      <c r="K17" s="51"/>
+      <c r="L17" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="50" t="s">
+      <c r="M17" s="50"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="51"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="45"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="51"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26"/>
@@ -9801,23 +9764,23 @@
       <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="44"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="45"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="51"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="26"/>
@@ -9829,23 +9792,23 @@
       <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="44"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="45"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="56"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="51"/>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
       <c r="T19" s="26"/>
@@ -9857,23 +9820,23 @@
       <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="44"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="45"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="56"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="51"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="26"/>
@@ -9885,23 +9848,23 @@
       <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="45"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="51"/>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
       <c r="T21" s="26"/>
@@ -9913,23 +9876,23 @@
       <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="44"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="45"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="51"/>
       <c r="R22" s="25"/>
       <c r="S22" s="25"/>
       <c r="T22" s="26"/>
@@ -9941,23 +9904,23 @@
       <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="45"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="51"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
       <c r="T23" s="26"/>
@@ -9969,23 +9932,23 @@
       <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="45"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="51"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
       <c r="T24" s="26"/>
@@ -9997,23 +9960,23 @@
       <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="45"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="50"/>
+      <c r="Q25" s="51"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
@@ -10025,23 +9988,23 @@
       <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="45"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="51"/>
       <c r="R26" s="25"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -10053,23 +10016,23 @@
       <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="45"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="51"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="26"/>
@@ -10081,23 +10044,23 @@
       <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="51"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
       <c r="T28" s="26"/>
@@ -10109,23 +10072,23 @@
       <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="44"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="51"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
       <c r="T29" s="26"/>
@@ -10137,23 +10100,23 @@
       <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="44"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="45"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="51"/>
       <c r="R30" s="25"/>
       <c r="S30" s="25"/>
       <c r="T30" s="26"/>
@@ -10165,23 +10128,23 @@
       <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="47"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="48"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="54"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="55"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="29"/>
@@ -11179,62 +11142,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11259,62 +11222,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
@@ -5,48 +5,41 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER121\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A319FA60-CFAF-4416-A523-15D876003440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2C0B4D-E6BF-4362-AF25-CB6FF8FA9797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="表紙 " sheetId="8" r:id="rId1"/>
-    <sheet name="ユースケース記述" sheetId="9" r:id="rId2"/>
+    <sheet name="表紙" sheetId="1" r:id="rId1"/>
+    <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="7" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="範囲１">#REF!</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
+    <t>○○○○システム</t>
+  </si>
+  <si>
     <t>初版</t>
+  </si>
+  <si>
+    <t>YYYY/MM/DD</t>
+  </si>
+  <si>
+    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -65,6 +58,9 @@
   </si>
   <si>
     <t>承認印</t>
+  </si>
+  <si>
+    <t>ユースケース名</t>
   </si>
   <si>
     <t>概要</t>
@@ -133,10 +129,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>テスト仕様書兼
-結果報告書</t>
-  </si>
-  <si>
     <t>テストレベル</t>
   </si>
   <si>
@@ -147,9 +139,6 @@
   </si>
   <si>
     <t>テスト対象</t>
-  </si>
-  <si>
-    <t>ログイン画面</t>
   </si>
   <si>
     <t>重要度</t>
@@ -261,10 +250,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>POST</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>備考</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -273,25 +258,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>submit</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>削除</t>
-    <rPh sb="0" eb="2">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>task-edit-servlet</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -321,97 +288,33 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク管理システム「TaskBoy」（TasBo）</t>
-    <rPh sb="3" eb="5">
-      <t>カンリ</t>
+    <t>一覧画面</t>
+    <rPh sb="0" eb="4">
+      <t>イチランガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>チーム名「チームTasBo」</t>
+    <t>テスト仕様書兼
+結果報告書</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク一覧表示</t>
-    <rPh sb="3" eb="7">
-      <t>イチランヒョウジ</t>
-    </rPh>
+    <t>task-alter-servlet</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>栗原</t>
-    <rPh sb="0" eb="2">
-      <t>クリハラ</t>
-    </rPh>
+    <t>GET</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>TaskBoy（TasBo）</t>
+    <t>menu.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザが現在の登録済みタスク一覧を参照する。</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>トウロクズ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユーザ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユースケース名+A5:J12D10A5:J13A5:J11A5:J12A5:J13</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユーザがログイン済みであること/メニュー画面が表示されていること</t>
-    <rPh sb="20" eb="22">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1,ユーザはメニュー画面で「タスク一覧表示」を選択する。
-2,システムはユーザのタスク情報を取得する。
-3,システムは取得したタスク情報を一覧形式で表示する。
-4,ユーザはタスク一覧を参照する。</t>
-    <rPh sb="19" eb="21">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>なし</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>成功時 : タスク一覧画面が表示されている/社員がタスク情報を参照可能な状態になっている。
-タスク未登録時 : タスク一覧画面が表示されている/「表示するデータが存在しません」が表示されている。</t>
-    <rPh sb="0" eb="3">
-      <t>セイコウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1. 表示対象のタスクが存在しない場合（基本フロー2から分岐）
-a. システムはタスク情報を取得する。
-b. システムは表示対象のタスクが存在しないことを判定する。
-c. システムは「表示するデータが存在しません」を表示する。</t>
-    <rPh sb="101" eb="103">
-      <t>ソンザイ</t>
+    <t>戻る</t>
+    <rPh sb="0" eb="1">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -441,7 +344,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1330,15 +1232,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1348,6 +1255,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1468,440 +1378,337 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{336D8449-DF56-4652-8247-ECBED917399C}"/>
-    <cellStyle name="標準 3" xfId="2" xr:uid="{08FCC2A5-2490-499B-ACCD-48F611CBDBA1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1920,16 +1727,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1048528</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>135768</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1952,14 +1759,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1047750" y="971550"/>
-          <a:ext cx="6601603" cy="4476749"/>
+          <a:off x="790575" y="933449"/>
+          <a:ext cx="6858000" cy="4650619"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1975,23 +1781,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>676276</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>923926</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>104776</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>242430</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="グラフィックス 1" descr="バッジ 1 枠線">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B3293CB-90D8-40B5-A198-B6AE13650415}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A772E96-D482-B6C6-DBDD-208D0A80EBAA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2001,56 +1807,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2819401" y="2200276"/>
-          <a:ext cx="247650" cy="247650"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>933450</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1107748</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502596B5-893A-42E4-ABEE-C4312E739900}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2063,8 +1819,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3076575" y="1590675"/>
-          <a:ext cx="3517573" cy="1704975"/>
+          <a:off x="2124075" y="1590675"/>
+          <a:ext cx="4029075" cy="1795005"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2073,148 +1829,324 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>80415</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>18342</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="楕円 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C95468F-3FF3-4860-8480-BAB2DCC8B753}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D3FF7AC-2F4F-1500-F21D-39D21E8256D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3057525" y="2266950"/>
-          <a:ext cx="280440" cy="627942"/>
+          <a:off x="2152650" y="2419350"/>
+          <a:ext cx="266700" cy="561975"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>933449</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>247649</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F84E0D01-D8B7-AD68-4A62-9FD8562688E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1962149" y="2324099"/>
+          <a:ext cx="371475" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>971550</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>257175</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="グラフィックス 4" descr="バッジ 枠線">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{833AAD42-E903-4B63-9C13-62263B29E061}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8DC0EE3-2048-A85E-A157-D393AC207FEE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3886200" y="3133725"/>
-          <a:ext cx="257175" cy="257175"/>
+          <a:off x="2000250" y="3000375"/>
+          <a:ext cx="295275" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>809625</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
+      <xdr:colOff>762000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="グラフィックス 5" descr="バッジ 枠線">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F293DCA6-9AF7-4CBA-8FE8-57AE16C30A19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3694225-5D14-C87C-3154-64791C3A4859}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2952750" y="3124200"/>
-          <a:ext cx="257175" cy="257175"/>
+          <a:off x="2600325" y="2990850"/>
+          <a:ext cx="304800" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1000125</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="テキスト ボックス 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E47991B-02D9-FBBC-6EE3-CD40AB6F29F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3143250" y="2990850"/>
+          <a:ext cx="285750" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2417,170 +2349,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6402A1E9-D679-4E64-A6B4-6B5738B2A00D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="16" width="7.7109375" style="44" customWidth="1"/>
-    <col min="17" max="26" width="8.7109375" style="44" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="44"/>
+    <col min="1" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
-    <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="94" t="s">
+    <row r="1" spans="3:16" ht="30" customHeight="1"/>
+    <row r="2" spans="3:16" ht="30" customHeight="1">
+      <c r="C2" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="45"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="45"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="45"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
-      <c r="P5" s="45"/>
-    </row>
-    <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="45"/>
-    </row>
-    <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="45"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="3:16" ht="30" customHeight="1">
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="3:16" ht="30" customHeight="1">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
+      <c r="E8" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="90"/>
-      <c r="I13" s="97">
-        <v>46175</v>
-      </c>
-      <c r="J13" s="91"/>
-      <c r="K13" s="90"/>
+      <c r="G13" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="95"/>
+      <c r="I13" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="94"/>
+      <c r="K13" s="95"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="89"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="90"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="95"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="89"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="90"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="95"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
+      <c r="G17" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3567,7 +3498,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="G17:K17"/>
     <mergeCell ref="C2:O6"/>
@@ -3576,6 +3506,7 @@
     <mergeCell ref="I13:K13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:K14"/>
+    <mergeCell ref="G15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -3584,227 +3515,202 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACCC434A-DC21-499D-B5DE-5BD56DF4FFF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="33" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="33"/>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="110" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="111"/>
-      <c r="F1" s="110" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="31" t="s">
+      <c r="A1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="48" t="s">
+      <c r="E1" s="120"/>
+      <c r="F1" s="132" t="s">
         <v>7</v>
       </c>
+      <c r="G1" s="120"/>
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="112" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="113"/>
-      <c r="F2" s="112" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="113"/>
-      <c r="H2" s="116">
-        <v>46175</v>
-      </c>
-      <c r="I2" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" s="123"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="124"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="107"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="125"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="130"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="126" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="128" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="129"/>
+      <c r="A5" s="119" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="105"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="106"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="130" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="100"/>
+      <c r="A6" s="121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="94"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="108"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="130" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="98" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="100"/>
+      <c r="A7" s="121" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="108"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="130" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="99"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="119" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="100"/>
+      <c r="A8" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="94"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="108"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="136" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="120" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="119" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="100"/>
-    </row>
-    <row r="10" spans="1:10" ht="84" customHeight="1">
-      <c r="A10" s="137"/>
-      <c r="B10" s="120" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="121"/>
-      <c r="D10" s="119" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100"/>
+      <c r="A9" s="122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="95"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="108"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="123"/>
+      <c r="B10" s="125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="95"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="108"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="138"/>
-      <c r="B11" s="120" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="121"/>
-      <c r="D11" s="119" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="100"/>
-    </row>
-    <row r="12" spans="1:10" ht="72" customHeight="1">
-      <c r="A12" s="130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="119" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="100"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="131" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="135"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="125" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="95"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="108"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="94"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="108"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="102"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4795,23 +4701,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
@@ -4819,9 +4708,26 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4840,424 +4746,424 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="145" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="A1" s="137" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="E1" s="120"/>
+      <c r="F1" s="132" t="s">
         <v>7</v>
       </c>
+      <c r="G1" s="120"/>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="142"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="73"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="143"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="130"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="144"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="7"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6253,420 +6159,420 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="145" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="A1" s="137" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="E1" s="120"/>
+      <c r="F1" s="132" t="s">
         <v>7</v>
       </c>
+      <c r="G1" s="120"/>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="146">
+      <c r="A2" s="114"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="133" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="134"/>
+      <c r="F2" s="133" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138">
         <v>46182</v>
       </c>
-      <c r="I2" s="139" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="142"/>
+      <c r="I2" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="73"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="143"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="130"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="144"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="7"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6679,7 +6585,7 @@
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="J44" s="11"/>
+      <c r="J44" s="14"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7663,577 +7569,706 @@
   <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="33" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="33"/>
+    <col min="1" max="3" width="5.140625" style="36" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="36" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="36" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="164" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="110" t="s">
+      <c r="A1" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="75"/>
+      <c r="F1" s="88" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="75"/>
+      <c r="H1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="90"/>
+      <c r="F2" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="90"/>
+      <c r="H2" s="92">
+        <v>46184</v>
+      </c>
+      <c r="I2" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="71"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="81"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="72"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="72"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="77"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="78"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="80"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="81"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="83"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="81"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="81"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="83"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="81"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="83"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="81"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="83"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="81"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="83"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="61"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="58"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="58"/>
+      <c r="J16" s="61"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="57">
+        <v>1</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="60"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="61"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="57">
+        <v>2</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="60"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="61"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="57"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="61"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="57"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="61"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="57"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="61"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="57"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="61"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="62"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="66"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="56"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="61"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="58"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="58"/>
+      <c r="J27" s="61"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="57">
+        <v>1</v>
+      </c>
+      <c r="B28" s="58"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" s="60"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="61"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="57">
         <v>3</v>
       </c>
-      <c r="E1" s="155"/>
-      <c r="F1" s="110" t="s">
+      <c r="B29" s="58"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="60"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="61"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A30" s="57"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="61"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A31" s="57"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="61"/>
+    </row>
+    <row r="32" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A32" s="57"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="61"/>
+    </row>
+    <row r="33" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A33" s="62"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="66"/>
+    </row>
+    <row r="34" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A34" s="47"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="51"/>
+    </row>
+    <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="56"/>
+    </row>
+    <row r="36" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A36" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="61"/>
+    </row>
+    <row r="37" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A37" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="58"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A38" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="58"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="58"/>
+      <c r="J38" s="61"/>
+    </row>
+    <row r="39" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A39" s="57">
         <v>4</v>
       </c>
-      <c r="G1" s="155"/>
-      <c r="H1" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="162"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="167"/>
-      <c r="D2" s="112" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="168"/>
-      <c r="F2" s="112" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="170">
-        <v>46182</v>
-      </c>
-      <c r="I2" s="122" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="123"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="162"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="169"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="151"/>
-      <c r="I3" s="151"/>
-      <c r="J3" s="152"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="162"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="152"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="153" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="156" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="157"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="158" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="150"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="162"/>
-      <c r="B8" s="105"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="163"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="162"/>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="163"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="162"/>
-      <c r="B10" s="105"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="163"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="162"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="163"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="162"/>
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="163"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="162"/>
-      <c r="B13" s="105"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="163"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="158" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="148"/>
-      <c r="I14" s="148"/>
-      <c r="J14" s="150"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="158" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="148"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="158" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="171" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" s="148"/>
-      <c r="J16" s="150"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="147">
-        <v>1</v>
-      </c>
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="98"/>
-      <c r="I17" s="148"/>
-      <c r="J17" s="150"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="147">
-        <v>2</v>
-      </c>
-      <c r="B18" s="148"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="36" t="s">
+      <c r="B39" s="58"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="98"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="150"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="147">
-        <v>3</v>
-      </c>
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="148"/>
-      <c r="J19" s="150"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="147">
-        <v>4</v>
-      </c>
-      <c r="B20" s="148"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="148"/>
-      <c r="J20" s="150"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="147">
-        <v>5</v>
-      </c>
-      <c r="B21" s="148"/>
-      <c r="C21" s="149"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="148"/>
-      <c r="J21" s="150"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="147">
-        <v>6</v>
-      </c>
-      <c r="B22" s="148"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="148"/>
-      <c r="J22" s="150"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="172">
-        <v>7</v>
-      </c>
-      <c r="B23" s="173"/>
-      <c r="C23" s="174"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="175"/>
-      <c r="I23" s="173"/>
-      <c r="J23" s="176"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="177">
-        <v>8</v>
-      </c>
-      <c r="B24" s="178"/>
-      <c r="C24" s="179"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="180"/>
-      <c r="I24" s="178"/>
-      <c r="J24" s="181"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="158" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="148"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="148"/>
-      <c r="I25" s="148"/>
-      <c r="J25" s="150"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="158" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="148"/>
-      <c r="C26" s="149"/>
-      <c r="D26" s="98" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="149"/>
-      <c r="I26" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="158" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="148"/>
-      <c r="C27" s="149"/>
-      <c r="D27" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="H27" s="171" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="148"/>
-      <c r="J27" s="150"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="147">
-        <v>1</v>
-      </c>
-      <c r="B28" s="148"/>
-      <c r="C28" s="149"/>
-      <c r="D28" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="98"/>
-      <c r="I28" s="148"/>
-      <c r="J28" s="150"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="147">
-        <v>2</v>
-      </c>
-      <c r="B29" s="148"/>
-      <c r="C29" s="149"/>
-      <c r="D29" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="H29" s="98"/>
-      <c r="I29" s="148"/>
-      <c r="J29" s="150"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="147">
-        <v>3</v>
-      </c>
-      <c r="B30" s="148"/>
-      <c r="C30" s="149"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="148"/>
-      <c r="J30" s="150"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="147">
-        <v>4</v>
-      </c>
-      <c r="B31" s="148"/>
-      <c r="C31" s="149"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="150"/>
-    </row>
-    <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="147">
-        <v>5</v>
-      </c>
-      <c r="B32" s="148"/>
-      <c r="C32" s="149"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="148"/>
-      <c r="J32" s="150"/>
-    </row>
-    <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="172">
-        <v>6</v>
-      </c>
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="175"/>
-      <c r="I33" s="173"/>
-      <c r="J33" s="176"/>
-    </row>
-    <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="182">
-        <v>7</v>
-      </c>
-      <c r="B34" s="183"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="185"/>
-      <c r="I34" s="183"/>
-      <c r="J34" s="186"/>
-    </row>
-    <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="177">
-        <v>8</v>
-      </c>
-      <c r="B35" s="178"/>
-      <c r="C35" s="179"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="180"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="181"/>
-    </row>
-    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="40" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="41" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="44" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="G39" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="H39" s="60"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A40" s="57"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="61"/>
+    </row>
+    <row r="41" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A41" s="57"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="61"/>
+    </row>
+    <row r="42" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A42" s="57"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="61"/>
+    </row>
+    <row r="43" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A43" s="57"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="61"/>
+    </row>
+    <row r="44" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A44" s="62"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="66"/>
+    </row>
+    <row r="45" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A45" s="47"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="51"/>
+    </row>
+    <row r="46" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A46" s="52"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="56"/>
+    </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" ht="12.75" customHeight="1"/>
@@ -9190,24 +9225,28 @@
     <row r="1000" ht="12.75" customHeight="1"/>
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
+  <mergeCells count="75">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
@@ -9224,27 +9263,44 @@
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="H44:J44"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9264,914 +9320,922 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="75" t="s">
+      <c r="A1" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="77"/>
-      <c r="S1" s="75" t="s">
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="78"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="132" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="132" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="120"/>
+      <c r="S1" s="132" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="106"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="67"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="133" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="133" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="134"/>
+      <c r="O2" s="151">
+        <v>46182</v>
+      </c>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="133" t="s">
+        <v>67</v>
+      </c>
+      <c r="R2" s="134"/>
+      <c r="S2" s="133"/>
+      <c r="T2" s="152"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="73"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="68"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="135"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="135"/>
+      <c r="T3" s="153"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="69"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="136"/>
+      <c r="T4" s="154"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="79" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="78"/>
+      <c r="A5" s="145" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="105"/>
+      <c r="S5" s="105"/>
+      <c r="T5" s="106"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="83"/>
+      <c r="A6" s="146" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="107" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="108"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="83"/>
+      <c r="A7" s="146" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="107" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
+      <c r="T7" s="108"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="25"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+    </row>
+    <row r="14" spans="1:26" ht="8.25" customHeight="1">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="10"/>
+    </row>
+    <row r="15" spans="1:26" ht="18.75" customHeight="1">
+      <c r="A15" s="146" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="95"/>
+      <c r="C15" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-    </row>
-    <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-    </row>
-    <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-    </row>
-    <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-    </row>
-    <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="7"/>
-    </row>
-    <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="49" t="s">
+      <c r="D15" s="95"/>
+      <c r="E15" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="49" t="s">
+      <c r="F15" s="95"/>
+      <c r="G15" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="50"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="49" t="s">
+      <c r="H15" s="94"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="12" t="s">
+      <c r="K15" s="95"/>
+      <c r="L15" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="S15" s="12" t="s">
+      <c r="M15" s="94"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="T15" s="24" t="s">
+      <c r="P15" s="94"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
+      <c r="S15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="T15" s="27" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="84">
+      <c r="A16" s="139">
         <v>1</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="51"/>
-      <c r="E16" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="51"/>
-      <c r="G16" s="52" t="s">
+      <c r="B16" s="95"/>
+      <c r="C16" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52" t="s">
+      <c r="D16" s="95"/>
+      <c r="E16" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="51"/>
-      <c r="L16" s="56" t="s">
+      <c r="F16" s="95"/>
+      <c r="G16" s="147" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="50"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="56" t="s">
+      <c r="H16" s="94"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="147" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="143" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="94"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="143" t="s">
+        <v>58</v>
+      </c>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="84">
+      <c r="A17" s="139">
         <v>2</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="85" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="85" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52" t="s">
+      <c r="B17" s="95"/>
+      <c r="C17" s="140" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52" t="s">
+      <c r="D17" s="95"/>
+      <c r="E17" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="51"/>
-      <c r="L17" s="56" t="s">
+      <c r="F17" s="95"/>
+      <c r="G17" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="50"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="56" t="s">
+      <c r="H17" s="94"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="147" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="27"/>
-      <c r="Y17" s="27"/>
-      <c r="Z17" s="27"/>
-    </row>
-    <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="56"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="56"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-      <c r="X18" s="27"/>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="27"/>
-    </row>
-    <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="84"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="56"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="56"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-    </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="84"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="25"/>
-      <c r="S20" s="25"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-    </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="84"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="56"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="27"/>
-      <c r="Y21" s="27"/>
-      <c r="Z21" s="27"/>
-    </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="84"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="56"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="56"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="27"/>
-    </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="84"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="56"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="56"/>
-      <c r="P23" s="50"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-    </row>
-    <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="84"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="56"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="56"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="51"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="27"/>
-      <c r="Y24" s="27"/>
-      <c r="Z24" s="27"/>
-    </row>
-    <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="84"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="56"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="51"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-    </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="84"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-    </row>
-    <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="84"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-    </row>
-    <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="84"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="56"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="56"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-    </row>
-    <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="84"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-    </row>
-    <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="84"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="25"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
-      <c r="W30" s="27"/>
-      <c r="X30" s="27"/>
-      <c r="Y30" s="27"/>
-      <c r="Z30" s="27"/>
-    </row>
-    <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="87"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
-      <c r="Z31" s="27"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="143" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" s="94"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="143" t="s">
+        <v>64</v>
+      </c>
+      <c r="P17" s="94"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+    </row>
+    <row r="18" spans="1:26" ht="48" customHeight="1">
+      <c r="A18" s="139"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="95"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+    </row>
+    <row r="19" spans="1:26" ht="48" customHeight="1">
+      <c r="A19" s="139"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="147"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="143"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="95"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+    </row>
+    <row r="20" spans="1:26" ht="48" customHeight="1">
+      <c r="A20" s="139"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="147"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="147"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="143"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+    </row>
+    <row r="21" spans="1:26" ht="48" customHeight="1">
+      <c r="A21" s="139"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="147"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="143"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+    </row>
+    <row r="22" spans="1:26" ht="48" customHeight="1">
+      <c r="A22" s="139"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="147"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="95"/>
+      <c r="L22" s="143"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="95"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="95"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+    </row>
+    <row r="23" spans="1:26" ht="48" customHeight="1">
+      <c r="A23" s="139"/>
+      <c r="B23" s="95"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="143"/>
+      <c r="P23" s="94"/>
+      <c r="Q23" s="95"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+    </row>
+    <row r="24" spans="1:26" ht="48" customHeight="1">
+      <c r="A24" s="139"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="147"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="147"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="143"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+    </row>
+    <row r="25" spans="1:26" ht="48" customHeight="1">
+      <c r="A25" s="139"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="143"/>
+      <c r="M25" s="94"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="143"/>
+      <c r="P25" s="94"/>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+    </row>
+    <row r="26" spans="1:26" ht="48" customHeight="1">
+      <c r="A26" s="139"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="147"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="143"/>
+      <c r="M26" s="94"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="143"/>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+    </row>
+    <row r="27" spans="1:26" ht="48" customHeight="1">
+      <c r="A27" s="139"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="147"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="143"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+    </row>
+    <row r="28" spans="1:26" ht="48" customHeight="1">
+      <c r="A28" s="139"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="143"/>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="95"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+    </row>
+    <row r="29" spans="1:26" ht="48" customHeight="1">
+      <c r="A29" s="139"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="94"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="94"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+    </row>
+    <row r="30" spans="1:26" ht="48" customHeight="1">
+      <c r="A30" s="139"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="94"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+    </row>
+    <row r="31" spans="1:26" ht="48" customHeight="1">
+      <c r="A31" s="141"/>
+      <c r="B31" s="110"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="155"/>
+      <c r="K31" s="110"/>
+      <c r="L31" s="144"/>
+      <c r="M31" s="102"/>
+      <c r="N31" s="110"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="102"/>
+      <c r="Q31" s="110"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
@@ -11142,6 +11206,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11166,118 +11342,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\新しいフォルダー (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119036E1-D524-4207-9F7E-CB13F5411263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A746D5-0492-4AF7-A6BC-38C7055149CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,25 @@
   <definedNames>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -310,48 +323,10 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>成功時 : タスク一覧画面が表示されている/社員がタスク情報を参照可能な状態になっている。
-タスク未登録時 : タスク一覧画面が表示されている/「表示するデータが存在しません」が表示されている。
-例外時 : ログイン画面が表示されている。</t>
-    <rPh sb="0" eb="3">
-      <t>セイコウジ</t>
-    </rPh>
-    <rPh sb="98" eb="101">
-      <t>レイガイジ</t>
-    </rPh>
-    <rPh sb="108" eb="110">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>E1. ユーザが未ログインの場合（基本フロー1から分岐）
 a. システムはユーザのログイン状態を確認する。
 b. システムはユーザが未ログインであることを判定する。
 c. システムはログイン画面へ遷移する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1. 表示対象のタスクが存在しない場合（基本フロー2から分岐）
-a. システムはタスク情報を取得する。
-b. システムは表示対象のタスクが存在しないことを判定する。
-c. システムは「表示するデータが存在しません」を表示する。</t>
-    <rPh sb="101" eb="103">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1,ユーザはメニュー画面で「タスク一覧表示」を選択する。
-2,システムはユーザのタスク情報を取得する。
-3,システムは取得したタスク情報を一覧形式で表示する。
-4,ユーザはタスク一覧を参照する。</t>
-    <rPh sb="19" eb="21">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -417,6 +392,63 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>A1. 表示対象のタスクが存在しない場合（基本フロー2から分岐）
+a. システムはログイン中のユーザに紐づくタスク情報を取得する。
+b. システムは表示対象のタスクが存在しないことを判定する。
+c. システムは「表示するデータが存在しません」を表示する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>成功時　:　タスク一覧画面が表示されている。/ログイン中のユーザに紐づくタスク情報を参照可能な状態になっている。
+タスク未登録時　:　タスク一覧画面が表示されている。/「表示するデータが存在しません」が表示されている。
+例外時　:　ログイン画面が表示されている。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザはメニュー画面で「タスク一覧表示」を選択する。
+2.システムはデータベースに登録されている全ユーザのタスク情報を取得する。
+3.システムは取得したタスク情報を一覧形式で表示する。
+表示項目
+　・選択ラジオボタン
+　・タスク名
+　・カテゴリ情報
+　・期限
+　・担当者情報
+　・ステータス情報
+　・メモ
+4.システムは表示項目の期限・メモに null 値が存在する場合、空文字として表示する。
+5.ユーザはタスク一覧を参照する。</t>
+    <rPh sb="43" eb="45">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>キゲン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>第二版</t>
+    <rPh sb="0" eb="3">
+      <t>ダイニハン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -443,6 +475,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1336,7 +1369,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1472,6 +1505,63 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1484,279 +1574,306 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1813,45 +1930,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2502,166 +2580,170 @@
   <dimension ref="C1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="16" width="7.7109375" style="159" customWidth="1"/>
-    <col min="17" max="26" width="8.7109375" style="159" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="159"/>
+    <col min="1" max="16" width="7.7109375" style="45" customWidth="1"/>
+    <col min="17" max="26" width="8.7109375" style="45" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
-      <c r="O2" s="170"/>
-      <c r="P2" s="168"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="47"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="168"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="104"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="160"/>
-      <c r="D4" s="160"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="160"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160"/>
-      <c r="K4" s="160"/>
-      <c r="L4" s="160"/>
-      <c r="M4" s="160"/>
-      <c r="N4" s="160"/>
-      <c r="O4" s="160"/>
-      <c r="P4" s="168"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="104"/>
+      <c r="P4" s="47"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="160"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="160"/>
-      <c r="F5" s="160"/>
-      <c r="G5" s="160"/>
-      <c r="H5" s="160"/>
-      <c r="I5" s="160"/>
-      <c r="J5" s="160"/>
-      <c r="K5" s="160"/>
-      <c r="L5" s="160"/>
-      <c r="M5" s="160"/>
-      <c r="N5" s="160"/>
-      <c r="O5" s="160"/>
-      <c r="P5" s="168"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="47"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="160"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="160"/>
-      <c r="J6" s="160"/>
-      <c r="K6" s="160"/>
-      <c r="L6" s="160"/>
-      <c r="M6" s="160"/>
-      <c r="N6" s="160"/>
-      <c r="O6" s="160"/>
-      <c r="P6" s="168"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="47"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="168"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="47"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="167" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="160"/>
-      <c r="I8" s="160"/>
-      <c r="J8" s="160"/>
-      <c r="K8" s="160"/>
-      <c r="L8" s="160"/>
-      <c r="M8" s="160"/>
+      <c r="E8" s="107" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="165" t="s">
+      <c r="G13" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="163"/>
-      <c r="I13" s="166">
+      <c r="H13" s="101"/>
+      <c r="I13" s="108">
         <v>46189</v>
       </c>
-      <c r="J13" s="164"/>
-      <c r="K13" s="163"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="101"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="165"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="165"/>
-      <c r="J14" s="164"/>
-      <c r="K14" s="163"/>
+      <c r="G14" s="100" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="101"/>
+      <c r="I14" s="108">
+        <v>46189</v>
+      </c>
+      <c r="J14" s="102"/>
+      <c r="K14" s="101"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="165"/>
-      <c r="H15" s="163"/>
-      <c r="I15" s="165"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="163"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="101"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G16" s="162"/>
-      <c r="H16" s="162"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="162"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="161" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="160"/>
-      <c r="I17" s="160"/>
-      <c r="J17" s="160"/>
-      <c r="K17" s="160"/>
+      <c r="G17" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -2678,974 +2760,974 @@
     <row r="30" spans="7:11" ht="12.75" customHeight="1"/>
     <row r="31" spans="7:11" ht="12.75" customHeight="1"/>
     <row r="32" spans="7:11" ht="12.75" customHeight="1"/>
-    <row r="33" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="159" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="G15:H15"/>
@@ -3676,19 +3758,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="72" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="72" t="s">
+      <c r="E1" s="90"/>
+      <c r="F1" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="90"/>
       <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
@@ -3700,1182 +3782,1183 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="91" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="92"/>
+      <c r="F2" s="91" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="92"/>
+      <c r="H2" s="68">
+        <v>46175</v>
+      </c>
+      <c r="I2" s="71" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" s="74"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="75"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="99"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="63"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="63"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="51"/>
+    </row>
+    <row r="9" spans="1:10" ht="198" customHeight="1">
+      <c r="A9" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51"/>
+    </row>
+    <row r="10" spans="1:10" ht="69.75" customHeight="1">
+      <c r="A10" s="65"/>
+      <c r="B10" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
-        <v>46175</v>
-      </c>
-      <c r="I2" s="81" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="82"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="83"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="84"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="85" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="52"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="52"/>
-    </row>
-    <row r="10" spans="1:10" ht="69.75" customHeight="1">
-      <c r="A10" s="46"/>
-      <c r="B10" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="52"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="51"/>
     </row>
     <row r="11" spans="1:10" ht="77.25" customHeight="1">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="52"/>
-    </row>
-    <row r="12" spans="1:10" ht="60" customHeight="1">
-      <c r="A12" s="56" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="51"/>
+    </row>
+    <row r="12" spans="1:10" ht="67.5" customHeight="1">
+      <c r="A12" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="52"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="51"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="61"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="60"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="17" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="18" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="19" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="20" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="21" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="22" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="23" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="24" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="25" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="26" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="27" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="28" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="29" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="30" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="31" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="32" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="33" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="33" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="17" ht="12.75" customHeight="1"/>
+    <row r="18" ht="12.75" customHeight="1"/>
+    <row r="19" ht="12.75" customHeight="1"/>
+    <row r="20" ht="12.75" customHeight="1"/>
+    <row r="21" ht="12.75" customHeight="1"/>
+    <row r="22" ht="12.75" customHeight="1"/>
+    <row r="23" ht="12.75" customHeight="1"/>
+    <row r="24" ht="12.75" customHeight="1"/>
+    <row r="25" ht="12.75" customHeight="1"/>
+    <row r="26" ht="12.75" customHeight="1"/>
+    <row r="27" ht="12.75" customHeight="1"/>
+    <row r="28" ht="12.75" customHeight="1"/>
+    <row r="29" ht="12.75" customHeight="1"/>
+    <row r="30" ht="12.75" customHeight="1"/>
+    <row r="31" ht="12.75" customHeight="1"/>
+    <row r="32" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
@@ -4886,6 +4969,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -4901,8 +4985,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4921,19 +5003,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="104"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="125"/>
+      <c r="F1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="104"/>
+      <c r="G1" s="125"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -4945,40 +5027,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="92"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="93"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -6334,19 +6416,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="104"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="125"/>
+      <c r="F1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="104"/>
+      <c r="G1" s="125"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -6358,48 +6440,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="105" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="106"/>
-      <c r="F2" s="105" t="s">
+      <c r="E2" s="127"/>
+      <c r="F2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="106"/>
-      <c r="H2" s="109">
+      <c r="G2" s="127"/>
+      <c r="H2" s="130">
         <v>46182</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="92"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="93"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -7751,19 +7833,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="72" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="72" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
@@ -7775,190 +7857,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="153"/>
+      <c r="F2" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="131">
+      <c r="G2" s="153"/>
+      <c r="H2" s="155">
         <v>46184</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="82"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="83"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="157"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="157"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="158" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="133" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="55"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="159"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="140"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="148"/>
+      <c r="B7" s="149"/>
+      <c r="C7" s="149"/>
+      <c r="D7" s="149"/>
+      <c r="E7" s="149"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="149"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="149"/>
+      <c r="J7" s="150"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="129"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="151"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="66"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="129"/>
+      <c r="A9" s="83"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="151"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="129"/>
+      <c r="A10" s="83"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="151"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="129"/>
+      <c r="A11" s="83"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="151"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="129"/>
+      <c r="A12" s="83"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="151"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="66"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="129"/>
+      <c r="A13" s="83"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="151"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="140"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="62" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="49"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="34" t="s">
         <v>24</v>
       </c>
@@ -7967,11 +8049,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="49"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="34" t="s">
         <v>26</v>
       </c>
@@ -7984,18 +8066,18 @@
       <c r="G16" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="147" t="s">
         <v>65</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="140"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="118">
+      <c r="A17" s="139">
         <v>1</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="49"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="36" t="s">
         <v>66</v>
       </c>
@@ -8008,16 +8090,16 @@
       <c r="G17" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="62"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="140"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="118">
+      <c r="A18" s="139">
         <v>2</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="49"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="36" t="s">
         <v>70</v>
       </c>
@@ -8030,109 +8112,109 @@
       <c r="G18" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="62"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="140"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="118"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="49"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="52"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="140"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="118"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="49"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="52"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="140"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="118"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="49"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37"/>
       <c r="G21" s="37"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="52"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="140"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="118"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="49"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="37"/>
       <c r="G22" s="37"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="140"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="142"/>
+      <c r="C23" s="143"/>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="123"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="145"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="115"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="71"/>
+      <c r="A24" s="136"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="88"/>
       <c r="D24" s="40"/>
       <c r="E24" s="40"/>
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="117"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="138"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="124" t="s">
+      <c r="A25" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="52"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="140"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="124" t="s">
+      <c r="A26" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="62" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="49"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="54"/>
       <c r="I26" s="34" t="s">
         <v>24</v>
       </c>
@@ -8141,11 +8223,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="124" t="s">
+      <c r="A27" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="49"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="34" t="s">
         <v>26</v>
       </c>
@@ -8158,18 +8240,18 @@
       <c r="G27" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="125" t="s">
+      <c r="H27" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="51"/>
-      <c r="J27" s="52"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="140"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="118">
+      <c r="A28" s="139">
         <v>1</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="49"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="36" t="s">
         <v>66</v>
       </c>
@@ -8182,16 +8264,16 @@
       <c r="G28" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="H28" s="62"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="52"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="140"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="118">
+      <c r="A29" s="139">
         <v>3</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="49"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="36" t="s">
         <v>72</v>
       </c>
@@ -8204,109 +8286,109 @@
       <c r="G29" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="62"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="52"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="140"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="118"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="49"/>
+      <c r="A30" s="139"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="54"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="52"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="140"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="118"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="49"/>
+      <c r="A31" s="139"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="54"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="52"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="140"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="118"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="49"/>
+      <c r="A32" s="139"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="54"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="52"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="140"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="119"/>
-      <c r="B33" s="120"/>
-      <c r="C33" s="121"/>
+      <c r="A33" s="141"/>
+      <c r="B33" s="142"/>
+      <c r="C33" s="143"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
-      <c r="H33" s="122"/>
-      <c r="I33" s="120"/>
-      <c r="J33" s="123"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="145"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="110"/>
-      <c r="B34" s="111"/>
-      <c r="C34" s="112"/>
+      <c r="A34" s="131"/>
+      <c r="B34" s="132"/>
+      <c r="C34" s="133"/>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
-      <c r="H34" s="113"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="114"/>
+      <c r="H34" s="134"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="135"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="115"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="71"/>
+      <c r="A35" s="136"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="88"/>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="117"/>
+      <c r="H35" s="137"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="138"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A36" s="124" t="s">
+      <c r="A36" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="52"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="140"/>
     </row>
     <row r="37" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A37" s="124" t="s">
+      <c r="A37" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="49"/>
-      <c r="D37" s="62" t="s">
+      <c r="B37" s="53"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="49"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="54"/>
       <c r="I37" s="34" t="s">
         <v>24</v>
       </c>
@@ -8315,11 +8397,11 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A38" s="124" t="s">
+      <c r="A38" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="49"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="54"/>
       <c r="D38" s="34" t="s">
         <v>26</v>
       </c>
@@ -8332,18 +8414,18 @@
       <c r="G38" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="125" t="s">
+      <c r="H38" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="I38" s="51"/>
-      <c r="J38" s="52"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="140"/>
     </row>
     <row r="39" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A39" s="118">
+      <c r="A39" s="139">
         <v>4</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="49"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="54"/>
       <c r="D39" s="36" t="s">
         <v>78</v>
       </c>
@@ -8356,93 +8438,93 @@
       <c r="G39" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="H39" s="62"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="52"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="140"/>
     </row>
     <row r="40" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A40" s="118"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="49"/>
+      <c r="A40" s="139"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="54"/>
       <c r="D40" s="36"/>
       <c r="E40" s="36"/>
       <c r="F40" s="36"/>
       <c r="G40" s="36"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="52"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="140"/>
     </row>
     <row r="41" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A41" s="118"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="49"/>
+      <c r="A41" s="139"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="54"/>
       <c r="D41" s="36"/>
       <c r="E41" s="36"/>
       <c r="F41" s="37"/>
       <c r="G41" s="37"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="52"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="140"/>
     </row>
     <row r="42" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A42" s="118"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="49"/>
+      <c r="A42" s="139"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="54"/>
       <c r="D42" s="36"/>
       <c r="E42" s="36"/>
       <c r="F42" s="37"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="52"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="140"/>
     </row>
     <row r="43" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A43" s="118"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="49"/>
+      <c r="A43" s="139"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="54"/>
       <c r="D43" s="36"/>
       <c r="E43" s="36"/>
       <c r="F43" s="37"/>
       <c r="G43" s="37"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="52"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="140"/>
     </row>
     <row r="44" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A44" s="119"/>
-      <c r="B44" s="120"/>
-      <c r="C44" s="121"/>
+      <c r="A44" s="141"/>
+      <c r="B44" s="142"/>
+      <c r="C44" s="143"/>
       <c r="D44" s="38"/>
       <c r="E44" s="38"/>
       <c r="F44" s="39"/>
       <c r="G44" s="39"/>
-      <c r="H44" s="122"/>
-      <c r="I44" s="120"/>
-      <c r="J44" s="123"/>
+      <c r="H44" s="144"/>
+      <c r="I44" s="142"/>
+      <c r="J44" s="145"/>
     </row>
     <row r="45" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A45" s="110"/>
-      <c r="B45" s="111"/>
-      <c r="C45" s="112"/>
+      <c r="A45" s="131"/>
+      <c r="B45" s="132"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="42"/>
       <c r="E45" s="42"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
-      <c r="H45" s="113"/>
-      <c r="I45" s="111"/>
-      <c r="J45" s="114"/>
+      <c r="H45" s="134"/>
+      <c r="I45" s="132"/>
+      <c r="J45" s="135"/>
     </row>
     <row r="46" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A46" s="115"/>
-      <c r="B46" s="70"/>
-      <c r="C46" s="71"/>
+      <c r="A46" s="136"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="88"/>
       <c r="D46" s="40"/>
       <c r="E46" s="40"/>
       <c r="F46" s="41"/>
       <c r="G46" s="41"/>
-      <c r="H46" s="116"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="117"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="87"/>
+      <c r="J46" s="138"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9495,190 +9577,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="103" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="103" t="s">
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="103" t="s">
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="103" t="s">
+      <c r="P1" s="125"/>
+      <c r="Q1" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="104"/>
-      <c r="S1" s="103" t="s">
+      <c r="R1" s="125"/>
+      <c r="S1" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="145"/>
+      <c r="T1" s="173"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="105" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="105" t="s">
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="153">
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="181">
         <v>46182</v>
       </c>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="105" t="s">
+      <c r="P2" s="127"/>
+      <c r="Q2" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="R2" s="106"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="154"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="182"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="107"/>
-      <c r="T3" s="155"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="183"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="156"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="184"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="144" t="s">
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
-      <c r="R5" s="143"/>
-      <c r="S5" s="143"/>
-      <c r="T5" s="145"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="171"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="173"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="174" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="147" t="s">
+      <c r="B6" s="167"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="86"/>
-      <c r="R6" s="86"/>
-      <c r="S6" s="86"/>
-      <c r="T6" s="148"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
+      <c r="O6" s="167"/>
+      <c r="P6" s="167"/>
+      <c r="Q6" s="167"/>
+      <c r="R6" s="167"/>
+      <c r="S6" s="167"/>
+      <c r="T6" s="176"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="146" t="s">
+      <c r="A7" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="147" t="s">
+      <c r="B7" s="167"/>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="86"/>
-      <c r="R7" s="86"/>
-      <c r="S7" s="86"/>
-      <c r="T7" s="148"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="167"/>
+      <c r="L7" s="167"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
+      <c r="O7" s="167"/>
+      <c r="P7" s="167"/>
+      <c r="Q7" s="167"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="167"/>
+      <c r="T7" s="176"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -9877,37 +9959,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="87"/>
-      <c r="C15" s="151" t="s">
+      <c r="B15" s="161"/>
+      <c r="C15" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="87"/>
-      <c r="E15" s="150" t="s">
+      <c r="D15" s="161"/>
+      <c r="E15" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="87"/>
-      <c r="G15" s="150" t="s">
+      <c r="F15" s="161"/>
+      <c r="G15" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="86"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="150" t="s">
+      <c r="H15" s="167"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="87"/>
-      <c r="L15" s="150" t="s">
+      <c r="K15" s="161"/>
+      <c r="L15" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="86"/>
-      <c r="N15" s="87"/>
-      <c r="O15" s="150" t="s">
+      <c r="M15" s="167"/>
+      <c r="N15" s="161"/>
+      <c r="O15" s="178" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="86"/>
-      <c r="Q15" s="87"/>
+      <c r="P15" s="167"/>
+      <c r="Q15" s="161"/>
       <c r="R15" s="12" t="s">
         <v>46</v>
       </c>
@@ -9919,37 +10001,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="160">
         <v>1</v>
       </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="161"/>
+      <c r="C16" s="162" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="135" t="s">
+      <c r="D16" s="161"/>
+      <c r="E16" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="87"/>
-      <c r="G16" s="149" t="s">
+      <c r="F16" s="161"/>
+      <c r="G16" s="177" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="86"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="149" t="s">
+      <c r="H16" s="167"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="87"/>
-      <c r="L16" s="139" t="s">
+      <c r="K16" s="161"/>
+      <c r="L16" s="166" t="s">
         <v>53</v>
       </c>
-      <c r="M16" s="86"/>
-      <c r="N16" s="87"/>
-      <c r="O16" s="139" t="s">
+      <c r="M16" s="167"/>
+      <c r="N16" s="161"/>
+      <c r="O16" s="166" t="s">
         <v>54</v>
       </c>
-      <c r="P16" s="86"/>
-      <c r="Q16" s="87"/>
+      <c r="P16" s="167"/>
+      <c r="Q16" s="161"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
       <c r="T16" s="26"/>
@@ -9961,37 +10043,37 @@
       <c r="Z16" s="27"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="160">
         <v>2</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="135" t="s">
+      <c r="B17" s="161"/>
+      <c r="C17" s="162" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="87"/>
-      <c r="E17" s="135" t="s">
+      <c r="D17" s="161"/>
+      <c r="E17" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="87"/>
-      <c r="G17" s="149" t="s">
+      <c r="F17" s="161"/>
+      <c r="G17" s="177" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="86"/>
-      <c r="I17" s="87"/>
-      <c r="J17" s="149" t="s">
+      <c r="H17" s="167"/>
+      <c r="I17" s="161"/>
+      <c r="J17" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="K17" s="87"/>
-      <c r="L17" s="139" t="s">
+      <c r="K17" s="161"/>
+      <c r="L17" s="166" t="s">
         <v>59</v>
       </c>
-      <c r="M17" s="86"/>
-      <c r="N17" s="87"/>
-      <c r="O17" s="139" t="s">
+      <c r="M17" s="167"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="166" t="s">
         <v>60</v>
       </c>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="87"/>
+      <c r="P17" s="167"/>
+      <c r="Q17" s="161"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26"/>
@@ -10003,23 +10085,23 @@
       <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="134"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="87"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="87"/>
+      <c r="A18" s="160"/>
+      <c r="B18" s="161"/>
+      <c r="C18" s="162"/>
+      <c r="D18" s="161"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="177"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="177"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="166"/>
+      <c r="M18" s="167"/>
+      <c r="N18" s="161"/>
+      <c r="O18" s="166"/>
+      <c r="P18" s="167"/>
+      <c r="Q18" s="161"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="26"/>
@@ -10031,23 +10113,23 @@
       <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="48" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="149"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="139"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="139"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="87"/>
+      <c r="A19" s="160"/>
+      <c r="B19" s="161"/>
+      <c r="C19" s="162"/>
+      <c r="D19" s="161"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="161"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="161"/>
+      <c r="J19" s="177"/>
+      <c r="K19" s="161"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="167"/>
+      <c r="N19" s="161"/>
+      <c r="O19" s="166"/>
+      <c r="P19" s="167"/>
+      <c r="Q19" s="161"/>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
       <c r="T19" s="26"/>
@@ -10059,23 +10141,23 @@
       <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="48" customHeight="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="149"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="87"/>
+      <c r="A20" s="160"/>
+      <c r="B20" s="161"/>
+      <c r="C20" s="162"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="177"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="177"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="166"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="161"/>
+      <c r="O20" s="166"/>
+      <c r="P20" s="167"/>
+      <c r="Q20" s="161"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="26"/>
@@ -10087,23 +10169,23 @@
       <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="48" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="87"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="86"/>
-      <c r="I21" s="87"/>
-      <c r="J21" s="149"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="139"/>
-      <c r="M21" s="86"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="139"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="87"/>
+      <c r="A21" s="160"/>
+      <c r="B21" s="161"/>
+      <c r="C21" s="162"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="177"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="177"/>
+      <c r="K21" s="161"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="167"/>
+      <c r="N21" s="161"/>
+      <c r="O21" s="166"/>
+      <c r="P21" s="167"/>
+      <c r="Q21" s="161"/>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
       <c r="T21" s="26"/>
@@ -10115,23 +10197,23 @@
       <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="48" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="87"/>
-      <c r="J22" s="149"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="86"/>
-      <c r="N22" s="87"/>
-      <c r="O22" s="139"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="87"/>
+      <c r="A22" s="160"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="162"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="177"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="167"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="166"/>
+      <c r="P22" s="167"/>
+      <c r="Q22" s="161"/>
       <c r="R22" s="25"/>
       <c r="S22" s="25"/>
       <c r="T22" s="26"/>
@@ -10143,23 +10225,23 @@
       <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="48" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="87"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="87"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="149"/>
-      <c r="K23" s="87"/>
-      <c r="L23" s="139"/>
-      <c r="M23" s="86"/>
-      <c r="N23" s="87"/>
-      <c r="O23" s="139"/>
-      <c r="P23" s="86"/>
-      <c r="Q23" s="87"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="161"/>
+      <c r="C23" s="162"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="177"/>
+      <c r="H23" s="167"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="177"/>
+      <c r="K23" s="161"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="167"/>
+      <c r="N23" s="161"/>
+      <c r="O23" s="166"/>
+      <c r="P23" s="167"/>
+      <c r="Q23" s="161"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
       <c r="T23" s="26"/>
@@ -10171,23 +10253,23 @@
       <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="48" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="149"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="149"/>
-      <c r="K24" s="87"/>
-      <c r="L24" s="139"/>
-      <c r="M24" s="86"/>
-      <c r="N24" s="87"/>
-      <c r="O24" s="139"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="87"/>
+      <c r="A24" s="160"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="162"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="177"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="161"/>
+      <c r="J24" s="177"/>
+      <c r="K24" s="161"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="167"/>
+      <c r="N24" s="161"/>
+      <c r="O24" s="166"/>
+      <c r="P24" s="167"/>
+      <c r="Q24" s="161"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
       <c r="T24" s="26"/>
@@ -10199,23 +10281,23 @@
       <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="48" customHeight="1">
-      <c r="A25" s="134"/>
-      <c r="B25" s="87"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="149"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="139"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="87"/>
-      <c r="O25" s="139"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="87"/>
+      <c r="A25" s="160"/>
+      <c r="B25" s="161"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="177"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="177"/>
+      <c r="K25" s="161"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="167"/>
+      <c r="N25" s="161"/>
+      <c r="O25" s="166"/>
+      <c r="P25" s="167"/>
+      <c r="Q25" s="161"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
@@ -10227,23 +10309,23 @@
       <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="48" customHeight="1">
-      <c r="A26" s="134"/>
-      <c r="B26" s="87"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="149"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="139"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="87"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="87"/>
+      <c r="A26" s="160"/>
+      <c r="B26" s="161"/>
+      <c r="C26" s="162"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="161"/>
+      <c r="G26" s="177"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="161"/>
+      <c r="J26" s="177"/>
+      <c r="K26" s="161"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="167"/>
+      <c r="N26" s="161"/>
+      <c r="O26" s="166"/>
+      <c r="P26" s="167"/>
+      <c r="Q26" s="161"/>
       <c r="R26" s="25"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -10255,23 +10337,23 @@
       <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="48" customHeight="1">
-      <c r="A27" s="134"/>
-      <c r="B27" s="87"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="149"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="149"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="139"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="87"/>
+      <c r="A27" s="160"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="162"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="161"/>
+      <c r="G27" s="177"/>
+      <c r="H27" s="167"/>
+      <c r="I27" s="161"/>
+      <c r="J27" s="177"/>
+      <c r="K27" s="161"/>
+      <c r="L27" s="166"/>
+      <c r="M27" s="167"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="166"/>
+      <c r="P27" s="167"/>
+      <c r="Q27" s="161"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="26"/>
@@ -10283,23 +10365,23 @@
       <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="48" customHeight="1">
-      <c r="A28" s="134"/>
-      <c r="B28" s="87"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="87"/>
-      <c r="G28" s="149"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="149"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="139"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="87"/>
-      <c r="O28" s="139"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="87"/>
+      <c r="A28" s="160"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="177"/>
+      <c r="H28" s="167"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="177"/>
+      <c r="K28" s="161"/>
+      <c r="L28" s="166"/>
+      <c r="M28" s="167"/>
+      <c r="N28" s="161"/>
+      <c r="O28" s="166"/>
+      <c r="P28" s="167"/>
+      <c r="Q28" s="161"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
       <c r="T28" s="26"/>
@@ -10311,23 +10393,23 @@
       <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="48" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="87"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="87"/>
-      <c r="G29" s="149"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="149"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="139"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="87"/>
-      <c r="O29" s="139"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="87"/>
+      <c r="A29" s="160"/>
+      <c r="B29" s="161"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="177"/>
+      <c r="H29" s="167"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="177"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="167"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="166"/>
+      <c r="P29" s="167"/>
+      <c r="Q29" s="161"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
       <c r="T29" s="26"/>
@@ -10339,23 +10421,23 @@
       <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="48" customHeight="1">
-      <c r="A30" s="134"/>
-      <c r="B30" s="87"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="139"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="139"/>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="87"/>
+      <c r="A30" s="160"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="162"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="177"/>
+      <c r="H30" s="167"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="177"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="161"/>
+      <c r="O30" s="166"/>
+      <c r="P30" s="167"/>
+      <c r="Q30" s="161"/>
       <c r="R30" s="25"/>
       <c r="S30" s="25"/>
       <c r="T30" s="26"/>
@@ -10367,23 +10449,23 @@
       <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="48" customHeight="1">
-      <c r="A31" s="136"/>
-      <c r="B31" s="137"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="141"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="158"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="140"/>
-      <c r="M31" s="141"/>
-      <c r="N31" s="137"/>
-      <c r="O31" s="140"/>
-      <c r="P31" s="141"/>
-      <c r="Q31" s="137"/>
+      <c r="A31" s="163"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="186"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="186"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="168"/>
+      <c r="M31" s="169"/>
+      <c r="N31" s="164"/>
+      <c r="O31" s="168"/>
+      <c r="P31" s="169"/>
+      <c r="Q31" s="164"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="29"/>

--- a/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_一覧表示.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER121\Documents\TasBo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A746D5-0492-4AF7-A6BC-38C7055149CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F819B5-C61B-4455-97E2-84E5CC2BA1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="10" r:id="rId1"/>
@@ -19,8 +19,14 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="7" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="12" r:id="rId7"/>
+    <sheet name="カバレッジレポート　一覧表示" sheetId="11" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="範囲１" localSheetId="6">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="125">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -449,6 +455,241 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>備　考</t>
+    <rPh sb="0" eb="1">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>分析・考察</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウサツ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>調査結果</t>
+    <rPh sb="0" eb="2">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>（２）報告事項</t>
+    <rPh sb="3" eb="5">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>カバレッジ率</t>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>TaskDAO.java</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>対象クラス</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>（１）概要</t>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>カバレッジレポート</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>正しくタスク一覧が取得できることを確認する</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>selectAll()</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>TaskDAO.java</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>畠山</t>
+    <rPh sb="0" eb="2">
+      <t>ハタケヤマ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>タスク一覧表示機能</t>
+    <rPh sb="3" eb="9">
+      <t>イチランヒョウジキノウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>TaskBoy(TasBo)</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
 </sst>
 </file>
 
@@ -457,7 +698,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -532,8 +773,95 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,8 +874,20 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="69">
+  <borders count="88">
     <border>
       <left/>
       <right/>
@@ -1363,13 +1703,245 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1517,6 +2089,135 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1532,9 +2233,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1571,132 +2269,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1763,6 +2335,78 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1778,164 +2422,306 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="73" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="74" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="75" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="64" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="76" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="77" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="76" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="76" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="70" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="70" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="78" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="78" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="79" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="80" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="81" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="79" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="80" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="81" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="78" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="78" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="79" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="80" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="81" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="82" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="83" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="20" fillId="0" borderId="84" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="82" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="85" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="83" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="77" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="76" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="64" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="74" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="74" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="76" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="77" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="76" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="76" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="6">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{336D8449-DF56-4652-8247-ECBED917399C}"/>
     <cellStyle name="標準 3" xfId="2" xr:uid="{696E1966-CC6B-4B0B-8E3E-1AA6FBCB4321}"/>
+    <cellStyle name="標準 4" xfId="3" xr:uid="{EBF0450F-71AD-4FD7-B5CB-D680FE01070E}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="4" xr:uid="{E4142539-C000-4566-A4C2-46C57E491272}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="5" xr:uid="{EF467B0D-9E01-4C37-AB92-C7561169ECF4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2379,6 +3165,118 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10487025" cy="2152649"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D1ED8F8-F7E5-418B-A446-C679A3740CE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="85725" y="7419975"/>
+          <a:ext cx="10487025" cy="2152649"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10582275" cy="4514850"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACE8DF06-511C-4EE2-B121-36EA21109DB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525" y="2095501"/>
+          <a:ext cx="10582275" cy="4514850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="別紙"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -2587,85 +3485,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="47"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
       <c r="P3" s="47"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="104"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
       <c r="P4" s="47"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
       <c r="P5" s="47"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="104"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="53"/>
       <c r="P6" s="47"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -2685,50 +3583,50 @@
       <c r="P7" s="47"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="107" t="s">
+      <c r="E8" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="100" t="s">
+      <c r="G13" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="101"/>
-      <c r="I13" s="108">
+      <c r="H13" s="50"/>
+      <c r="I13" s="57">
         <v>46189</v>
       </c>
-      <c r="J13" s="102"/>
-      <c r="K13" s="101"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="100" t="s">
+      <c r="G14" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="H14" s="101"/>
-      <c r="I14" s="108">
+      <c r="H14" s="50"/>
+      <c r="I14" s="57">
         <v>46189</v>
       </c>
-      <c r="J14" s="102"/>
-      <c r="K14" s="101"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="50"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="100"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="101"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="46"/>
@@ -2737,13 +3635,13 @@
       <c r="J16" s="46"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="103" t="s">
+      <c r="G17" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3758,19 +4656,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="89" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="89" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="90"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
@@ -3782,192 +4680,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="83"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="91" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="92"/>
-      <c r="F2" s="91" t="s">
+      <c r="E2" s="84"/>
+      <c r="F2" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="92"/>
-      <c r="H2" s="68">
+      <c r="G2" s="84"/>
+      <c r="H2" s="60">
         <v>46175</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="66"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="83"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="67"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="86"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="99"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="91"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="61" t="s">
+      <c r="B6" s="96"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="63"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="105"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="61" t="s">
+      <c r="B7" s="96"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="63"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="105"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="49" t="s">
+      <c r="B8" s="96"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="51"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="94"/>
     </row>
     <row r="9" spans="1:10" ht="198" customHeight="1">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="49" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="51"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="69.75" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="67" t="s">
+      <c r="A10" s="107"/>
+      <c r="B10" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="49" t="s">
+      <c r="C10" s="59"/>
+      <c r="D10" s="92" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="51"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="94"/>
     </row>
     <row r="11" spans="1:10" ht="77.25" customHeight="1">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67" t="s">
+      <c r="A11" s="108"/>
+      <c r="B11" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="49" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="51"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="67.5" customHeight="1">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="49" t="s">
+      <c r="B12" s="96"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="51"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="94"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="60"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="102"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4958,6 +5856,19 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
@@ -4971,20 +5882,7 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D11:J11"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
     <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7833,19 +8731,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="89" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="89" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="79"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
@@ -7857,190 +8755,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="83"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="91" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="153"/>
-      <c r="F2" s="91" t="s">
+      <c r="E2" s="138"/>
+      <c r="F2" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="153"/>
-      <c r="H2" s="155">
+      <c r="G2" s="138"/>
+      <c r="H2" s="140">
         <v>46184</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="66"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="83"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="157"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="142"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
-      <c r="J4" s="157"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="142"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="98" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="159"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="140"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="132"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="148"/>
-      <c r="B7" s="149"/>
-      <c r="C7" s="149"/>
-      <c r="D7" s="149"/>
-      <c r="E7" s="149"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="149"/>
-      <c r="I7" s="149"/>
-      <c r="J7" s="150"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="83"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="151"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="136"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="83"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="151"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="136"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="151"/>
+      <c r="A10" s="75"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="136"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="83"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="151"/>
+      <c r="A11" s="75"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="83"/>
-      <c r="B12" s="84"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="151"/>
+      <c r="A12" s="75"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="136"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="83"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="151"/>
+      <c r="A13" s="75"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="140"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="132"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="61" t="s">
+      <c r="B15" s="96"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>24</v>
       </c>
@@ -8049,11 +8947,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>26</v>
       </c>
@@ -8066,18 +8964,18 @@
       <c r="G16" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="147" t="s">
+      <c r="H16" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="I16" s="53"/>
-      <c r="J16" s="140"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="132"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="54"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="36" t="s">
         <v>66</v>
       </c>
@@ -8090,16 +8988,16 @@
       <c r="G17" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="140"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="132"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="139">
+      <c r="A18" s="146">
         <v>2</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="36" t="s">
         <v>70</v>
       </c>
@@ -8112,109 +9010,109 @@
       <c r="G18" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="140"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="132"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="139"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
+      <c r="A19" s="146"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="140"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="132"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="139"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
+      <c r="A20" s="146"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="140"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="132"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="139"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="54"/>
+      <c r="A21" s="146"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37"/>
       <c r="G21" s="37"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="140"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="132"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="139"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
+      <c r="A22" s="146"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="37"/>
       <c r="G22" s="37"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="140"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="132"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="143"/>
+      <c r="A23" s="147"/>
+      <c r="B23" s="148"/>
+      <c r="C23" s="149"/>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="142"/>
-      <c r="J23" s="145"/>
+      <c r="H23" s="150"/>
+      <c r="I23" s="148"/>
+      <c r="J23" s="151"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="136"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="88"/>
+      <c r="A24" s="152"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="40"/>
       <c r="E24" s="40"/>
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
-      <c r="H24" s="137"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="138"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="154"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="146" t="s">
+      <c r="A25" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="140"/>
+      <c r="B25" s="96"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="132"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="146" t="s">
+      <c r="A26" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="61" t="s">
+      <c r="B26" s="96"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="54"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="59"/>
       <c r="I26" s="34" t="s">
         <v>24</v>
       </c>
@@ -8223,11 +9121,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="146" t="s">
+      <c r="A27" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="54"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>26</v>
       </c>
@@ -8240,18 +9138,18 @@
       <c r="G27" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="147" t="s">
+      <c r="H27" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="53"/>
-      <c r="J27" s="140"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="132"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="139">
+      <c r="A28" s="146">
         <v>1</v>
       </c>
-      <c r="B28" s="53"/>
-      <c r="C28" s="54"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="59"/>
       <c r="D28" s="36" t="s">
         <v>66</v>
       </c>
@@ -8264,16 +9162,16 @@
       <c r="G28" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="H28" s="61"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="140"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="132"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="139">
+      <c r="A29" s="146">
         <v>3</v>
       </c>
-      <c r="B29" s="53"/>
-      <c r="C29" s="54"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="36" t="s">
         <v>72</v>
       </c>
@@ -8286,109 +9184,109 @@
       <c r="G29" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="61"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="140"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="132"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="139"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="54"/>
+      <c r="A30" s="146"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="59"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="140"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="132"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="139"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="54"/>
+      <c r="A31" s="146"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="140"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="132"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="139"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="54"/>
+      <c r="A32" s="146"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="140"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="132"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="141"/>
-      <c r="B33" s="142"/>
-      <c r="C33" s="143"/>
+      <c r="A33" s="147"/>
+      <c r="B33" s="148"/>
+      <c r="C33" s="149"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
-      <c r="H33" s="144"/>
-      <c r="I33" s="142"/>
-      <c r="J33" s="145"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="148"/>
+      <c r="J33" s="151"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="131"/>
-      <c r="B34" s="132"/>
-      <c r="C34" s="133"/>
+      <c r="A34" s="155"/>
+      <c r="B34" s="156"/>
+      <c r="C34" s="157"/>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
-      <c r="H34" s="134"/>
-      <c r="I34" s="132"/>
-      <c r="J34" s="135"/>
+      <c r="H34" s="158"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="159"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="136"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="88"/>
+      <c r="A35" s="152"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="80"/>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="137"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="138"/>
+      <c r="H35" s="153"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="154"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A36" s="146" t="s">
+      <c r="A36" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="140"/>
+      <c r="B36" s="96"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="96"/>
+      <c r="H36" s="96"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="132"/>
     </row>
     <row r="37" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A37" s="146" t="s">
+      <c r="A37" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="61" t="s">
+      <c r="B37" s="96"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="54"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="59"/>
       <c r="I37" s="34" t="s">
         <v>24</v>
       </c>
@@ -8397,11 +9295,11 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A38" s="146" t="s">
+      <c r="A38" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="53"/>
-      <c r="C38" s="54"/>
+      <c r="B38" s="96"/>
+      <c r="C38" s="59"/>
       <c r="D38" s="34" t="s">
         <v>26</v>
       </c>
@@ -8414,18 +9312,18 @@
       <c r="G38" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="147" t="s">
+      <c r="H38" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="I38" s="53"/>
-      <c r="J38" s="140"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="132"/>
     </row>
     <row r="39" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A39" s="139">
+      <c r="A39" s="146">
         <v>4</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="54"/>
+      <c r="B39" s="96"/>
+      <c r="C39" s="59"/>
       <c r="D39" s="36" t="s">
         <v>78</v>
       </c>
@@ -8438,93 +9336,93 @@
       <c r="G39" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="H39" s="61"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="140"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="132"/>
     </row>
     <row r="40" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A40" s="139"/>
-      <c r="B40" s="53"/>
-      <c r="C40" s="54"/>
+      <c r="A40" s="146"/>
+      <c r="B40" s="96"/>
+      <c r="C40" s="59"/>
       <c r="D40" s="36"/>
       <c r="E40" s="36"/>
       <c r="F40" s="36"/>
       <c r="G40" s="36"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="140"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="132"/>
     </row>
     <row r="41" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A41" s="139"/>
-      <c r="B41" s="53"/>
-      <c r="C41" s="54"/>
+      <c r="A41" s="146"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="59"/>
       <c r="D41" s="36"/>
       <c r="E41" s="36"/>
       <c r="F41" s="37"/>
       <c r="G41" s="37"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="140"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="132"/>
     </row>
     <row r="42" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A42" s="139"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="54"/>
+      <c r="A42" s="146"/>
+      <c r="B42" s="96"/>
+      <c r="C42" s="59"/>
       <c r="D42" s="36"/>
       <c r="E42" s="36"/>
       <c r="F42" s="37"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="140"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="96"/>
+      <c r="J42" s="132"/>
     </row>
     <row r="43" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A43" s="139"/>
-      <c r="B43" s="53"/>
-      <c r="C43" s="54"/>
+      <c r="A43" s="146"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="59"/>
       <c r="D43" s="36"/>
       <c r="E43" s="36"/>
       <c r="F43" s="37"/>
       <c r="G43" s="37"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="140"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="132"/>
     </row>
     <row r="44" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A44" s="141"/>
-      <c r="B44" s="142"/>
-      <c r="C44" s="143"/>
+      <c r="A44" s="147"/>
+      <c r="B44" s="148"/>
+      <c r="C44" s="149"/>
       <c r="D44" s="38"/>
       <c r="E44" s="38"/>
       <c r="F44" s="39"/>
       <c r="G44" s="39"/>
-      <c r="H44" s="144"/>
-      <c r="I44" s="142"/>
-      <c r="J44" s="145"/>
+      <c r="H44" s="150"/>
+      <c r="I44" s="148"/>
+      <c r="J44" s="151"/>
     </row>
     <row r="45" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A45" s="131"/>
-      <c r="B45" s="132"/>
-      <c r="C45" s="133"/>
+      <c r="A45" s="155"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="157"/>
       <c r="D45" s="42"/>
       <c r="E45" s="42"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
-      <c r="H45" s="134"/>
-      <c r="I45" s="132"/>
-      <c r="J45" s="135"/>
+      <c r="H45" s="158"/>
+      <c r="I45" s="156"/>
+      <c r="J45" s="159"/>
     </row>
     <row r="46" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A46" s="136"/>
-      <c r="B46" s="87"/>
-      <c r="C46" s="88"/>
+      <c r="A46" s="152"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="80"/>
       <c r="D46" s="40"/>
       <c r="E46" s="40"/>
       <c r="F46" s="41"/>
       <c r="G46" s="41"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="87"/>
-      <c r="J46" s="138"/>
+      <c r="H46" s="153"/>
+      <c r="I46" s="79"/>
+      <c r="J46" s="154"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9483,27 +10381,44 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
@@ -9520,44 +10435,27 @@
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9577,7 +10475,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="174" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="116"/>
@@ -9588,14 +10486,14 @@
       <c r="G1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
       <c r="J1" s="125"/>
       <c r="K1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="125"/>
       <c r="O1" s="124" t="s">
         <v>5</v>
@@ -9608,7 +10506,7 @@
       <c r="S1" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="173"/>
+      <c r="T1" s="176"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="118"/>
@@ -9620,16 +10518,16 @@
       <c r="G2" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="180"/>
-      <c r="I2" s="180"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="127"/>
       <c r="K2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="180"/>
-      <c r="M2" s="180"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
       <c r="N2" s="127"/>
-      <c r="O2" s="181">
+      <c r="O2" s="170">
         <v>46182</v>
       </c>
       <c r="P2" s="127"/>
@@ -9638,7 +10536,7 @@
       </c>
       <c r="R2" s="127"/>
       <c r="S2" s="126"/>
-      <c r="T2" s="182"/>
+      <c r="T2" s="171"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="118"/>
@@ -9660,7 +10558,7 @@
       <c r="Q3" s="128"/>
       <c r="R3" s="120"/>
       <c r="S3" s="128"/>
-      <c r="T3" s="183"/>
+      <c r="T3" s="172"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="121"/>
@@ -9682,85 +10580,85 @@
       <c r="Q4" s="129"/>
       <c r="R4" s="123"/>
       <c r="S4" s="129"/>
-      <c r="T4" s="184"/>
+      <c r="T4" s="173"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="170" t="s">
+      <c r="A5" s="177" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="171"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
       <c r="F5" s="125"/>
-      <c r="G5" s="172" t="s">
+      <c r="G5" s="178" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="171"/>
-      <c r="O5" s="171"/>
-      <c r="P5" s="171"/>
-      <c r="Q5" s="171"/>
-      <c r="R5" s="171"/>
-      <c r="S5" s="171"/>
-      <c r="T5" s="173"/>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="175"/>
+      <c r="P5" s="175"/>
+      <c r="Q5" s="175"/>
+      <c r="R5" s="175"/>
+      <c r="S5" s="175"/>
+      <c r="T5" s="176"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="174" t="s">
+      <c r="A6" s="179" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="167"/>
-      <c r="C6" s="167"/>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="175" t="s">
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
-      <c r="J6" s="167"/>
-      <c r="K6" s="167"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="167"/>
-      <c r="N6" s="167"/>
-      <c r="O6" s="167"/>
-      <c r="P6" s="167"/>
-      <c r="Q6" s="167"/>
-      <c r="R6" s="167"/>
-      <c r="S6" s="167"/>
-      <c r="T6" s="176"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="161"/>
+      <c r="O6" s="161"/>
+      <c r="P6" s="161"/>
+      <c r="Q6" s="161"/>
+      <c r="R6" s="161"/>
+      <c r="S6" s="161"/>
+      <c r="T6" s="181"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="174" t="s">
+      <c r="A7" s="179" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="167"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="175" t="s">
+      <c r="B7" s="161"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="167"/>
-      <c r="I7" s="167"/>
-      <c r="J7" s="167"/>
-      <c r="K7" s="167"/>
-      <c r="L7" s="167"/>
-      <c r="M7" s="167"/>
-      <c r="N7" s="167"/>
-      <c r="O7" s="167"/>
-      <c r="P7" s="167"/>
-      <c r="Q7" s="167"/>
-      <c r="R7" s="167"/>
-      <c r="S7" s="167"/>
-      <c r="T7" s="176"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
+      <c r="R7" s="161"/>
+      <c r="S7" s="161"/>
+      <c r="T7" s="181"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -9959,37 +10857,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="174" t="s">
+      <c r="A15" s="179" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="161"/>
-      <c r="C15" s="179" t="s">
+      <c r="B15" s="162"/>
+      <c r="C15" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="161"/>
-      <c r="E15" s="178" t="s">
+      <c r="D15" s="162"/>
+      <c r="E15" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="161"/>
-      <c r="G15" s="178" t="s">
+      <c r="F15" s="162"/>
+      <c r="G15" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="167"/>
-      <c r="I15" s="161"/>
-      <c r="J15" s="178" t="s">
+      <c r="H15" s="161"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="161"/>
-      <c r="L15" s="178" t="s">
+      <c r="K15" s="162"/>
+      <c r="L15" s="160" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="167"/>
-      <c r="N15" s="161"/>
-      <c r="O15" s="178" t="s">
+      <c r="M15" s="161"/>
+      <c r="N15" s="162"/>
+      <c r="O15" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="167"/>
-      <c r="Q15" s="161"/>
+      <c r="P15" s="161"/>
+      <c r="Q15" s="162"/>
       <c r="R15" s="12" t="s">
         <v>46</v>
       </c>
@@ -10001,37 +10899,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="160">
+      <c r="A16" s="182">
         <v>1</v>
       </c>
-      <c r="B16" s="161"/>
-      <c r="C16" s="162" t="s">
+      <c r="B16" s="162"/>
+      <c r="C16" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="161"/>
-      <c r="E16" s="162" t="s">
+      <c r="D16" s="162"/>
+      <c r="E16" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="161"/>
-      <c r="G16" s="177" t="s">
+      <c r="F16" s="162"/>
+      <c r="G16" s="163" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="167"/>
-      <c r="I16" s="161"/>
-      <c r="J16" s="177" t="s">
+      <c r="H16" s="161"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="163" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="161"/>
-      <c r="L16" s="166" t="s">
+      <c r="K16" s="162"/>
+      <c r="L16" s="167" t="s">
         <v>53</v>
       </c>
-      <c r="M16" s="167"/>
-      <c r="N16" s="161"/>
-      <c r="O16" s="166" t="s">
+      <c r="M16" s="161"/>
+      <c r="N16" s="162"/>
+      <c r="O16" s="167" t="s">
         <v>54</v>
       </c>
-      <c r="P16" s="167"/>
-      <c r="Q16" s="161"/>
+      <c r="P16" s="161"/>
+      <c r="Q16" s="162"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
       <c r="T16" s="26"/>
@@ -10043,37 +10941,37 @@
       <c r="Z16" s="27"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="160">
+      <c r="A17" s="182">
         <v>2</v>
       </c>
-      <c r="B17" s="161"/>
-      <c r="C17" s="162" t="s">
+      <c r="B17" s="162"/>
+      <c r="C17" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="161"/>
-      <c r="E17" s="162" t="s">
+      <c r="D17" s="162"/>
+      <c r="E17" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="161"/>
-      <c r="G17" s="177" t="s">
+      <c r="F17" s="162"/>
+      <c r="G17" s="163" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="167"/>
-      <c r="I17" s="161"/>
-      <c r="J17" s="177" t="s">
+      <c r="H17" s="161"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="K17" s="161"/>
-      <c r="L17" s="166" t="s">
+      <c r="K17" s="162"/>
+      <c r="L17" s="167" t="s">
         <v>59</v>
       </c>
-      <c r="M17" s="167"/>
-      <c r="N17" s="161"/>
-      <c r="O17" s="166" t="s">
+      <c r="M17" s="161"/>
+      <c r="N17" s="162"/>
+      <c r="O17" s="167" t="s">
         <v>60</v>
       </c>
-      <c r="P17" s="167"/>
-      <c r="Q17" s="161"/>
+      <c r="P17" s="161"/>
+      <c r="Q17" s="162"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26"/>
@@ -10085,23 +10983,23 @@
       <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="160"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="162"/>
-      <c r="D18" s="161"/>
-      <c r="E18" s="162"/>
-      <c r="F18" s="161"/>
-      <c r="G18" s="177"/>
-      <c r="H18" s="167"/>
-      <c r="I18" s="161"/>
-      <c r="J18" s="177"/>
-      <c r="K18" s="161"/>
-      <c r="L18" s="166"/>
-      <c r="M18" s="167"/>
-      <c r="N18" s="161"/>
-      <c r="O18" s="166"/>
-      <c r="P18" s="167"/>
-      <c r="Q18" s="161"/>
+      <c r="A18" s="182"/>
+      <c r="B18" s="162"/>
+      <c r="C18" s="183"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="162"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="161"/>
+      <c r="N18" s="162"/>
+      <c r="O18" s="167"/>
+      <c r="P18" s="161"/>
+      <c r="Q18" s="162"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="26"/>
@@ -10113,23 +11011,23 @@
       <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="48" customHeight="1">
-      <c r="A19" s="160"/>
-      <c r="B19" s="161"/>
-      <c r="C19" s="162"/>
-      <c r="D19" s="161"/>
-      <c r="E19" s="162"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="177"/>
-      <c r="H19" s="167"/>
-      <c r="I19" s="161"/>
-      <c r="J19" s="177"/>
-      <c r="K19" s="161"/>
-      <c r="L19" s="166"/>
-      <c r="M19" s="167"/>
-      <c r="N19" s="161"/>
-      <c r="O19" s="166"/>
-      <c r="P19" s="167"/>
-      <c r="Q19" s="161"/>
+      <c r="A19" s="182"/>
+      <c r="B19" s="162"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="162"/>
+      <c r="L19" s="167"/>
+      <c r="M19" s="161"/>
+      <c r="N19" s="162"/>
+      <c r="O19" s="167"/>
+      <c r="P19" s="161"/>
+      <c r="Q19" s="162"/>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
       <c r="T19" s="26"/>
@@ -10141,23 +11039,23 @@
       <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="48" customHeight="1">
-      <c r="A20" s="160"/>
-      <c r="B20" s="161"/>
-      <c r="C20" s="162"/>
-      <c r="D20" s="161"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="177"/>
-      <c r="H20" s="167"/>
-      <c r="I20" s="161"/>
-      <c r="J20" s="177"/>
-      <c r="K20" s="161"/>
-      <c r="L20" s="166"/>
-      <c r="M20" s="167"/>
-      <c r="N20" s="161"/>
-      <c r="O20" s="166"/>
-      <c r="P20" s="167"/>
-      <c r="Q20" s="161"/>
+      <c r="A20" s="182"/>
+      <c r="B20" s="162"/>
+      <c r="C20" s="183"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="163"/>
+      <c r="K20" s="162"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="161"/>
+      <c r="N20" s="162"/>
+      <c r="O20" s="167"/>
+      <c r="P20" s="161"/>
+      <c r="Q20" s="162"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="26"/>
@@ -10169,23 +11067,23 @@
       <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="48" customHeight="1">
-      <c r="A21" s="160"/>
-      <c r="B21" s="161"/>
-      <c r="C21" s="162"/>
-      <c r="D21" s="161"/>
-      <c r="E21" s="162"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="177"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="161"/>
-      <c r="J21" s="177"/>
-      <c r="K21" s="161"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="167"/>
-      <c r="N21" s="161"/>
-      <c r="O21" s="166"/>
-      <c r="P21" s="167"/>
-      <c r="Q21" s="161"/>
+      <c r="A21" s="182"/>
+      <c r="B21" s="162"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="183"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="162"/>
+      <c r="L21" s="167"/>
+      <c r="M21" s="161"/>
+      <c r="N21" s="162"/>
+      <c r="O21" s="167"/>
+      <c r="P21" s="161"/>
+      <c r="Q21" s="162"/>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
       <c r="T21" s="26"/>
@@ -10197,23 +11095,23 @@
       <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="48" customHeight="1">
-      <c r="A22" s="160"/>
-      <c r="B22" s="161"/>
-      <c r="C22" s="162"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="162"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="177"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="161"/>
-      <c r="J22" s="177"/>
-      <c r="K22" s="161"/>
-      <c r="L22" s="166"/>
-      <c r="M22" s="167"/>
-      <c r="N22" s="161"/>
-      <c r="O22" s="166"/>
-      <c r="P22" s="167"/>
-      <c r="Q22" s="161"/>
+      <c r="A22" s="182"/>
+      <c r="B22" s="162"/>
+      <c r="C22" s="183"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="183"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="163"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="167"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="167"/>
+      <c r="P22" s="161"/>
+      <c r="Q22" s="162"/>
       <c r="R22" s="25"/>
       <c r="S22" s="25"/>
       <c r="T22" s="26"/>
@@ -10225,23 +11123,23 @@
       <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="48" customHeight="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="161"/>
-      <c r="C23" s="162"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="162"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="177"/>
-      <c r="H23" s="167"/>
-      <c r="I23" s="161"/>
-      <c r="J23" s="177"/>
-      <c r="K23" s="161"/>
-      <c r="L23" s="166"/>
-      <c r="M23" s="167"/>
-      <c r="N23" s="161"/>
-      <c r="O23" s="166"/>
-      <c r="P23" s="167"/>
-      <c r="Q23" s="161"/>
+      <c r="A23" s="182"/>
+      <c r="B23" s="162"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="163"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="163"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="167"/>
+      <c r="M23" s="161"/>
+      <c r="N23" s="162"/>
+      <c r="O23" s="167"/>
+      <c r="P23" s="161"/>
+      <c r="Q23" s="162"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
       <c r="T23" s="26"/>
@@ -10253,23 +11151,23 @@
       <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="48" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="161"/>
-      <c r="C24" s="162"/>
-      <c r="D24" s="161"/>
-      <c r="E24" s="162"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="177"/>
-      <c r="H24" s="167"/>
-      <c r="I24" s="161"/>
-      <c r="J24" s="177"/>
-      <c r="K24" s="161"/>
-      <c r="L24" s="166"/>
-      <c r="M24" s="167"/>
-      <c r="N24" s="161"/>
-      <c r="O24" s="166"/>
-      <c r="P24" s="167"/>
-      <c r="Q24" s="161"/>
+      <c r="A24" s="182"/>
+      <c r="B24" s="162"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="163"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="162"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="161"/>
+      <c r="N24" s="162"/>
+      <c r="O24" s="167"/>
+      <c r="P24" s="161"/>
+      <c r="Q24" s="162"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
       <c r="T24" s="26"/>
@@ -10281,23 +11179,23 @@
       <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="48" customHeight="1">
-      <c r="A25" s="160"/>
-      <c r="B25" s="161"/>
-      <c r="C25" s="162"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="162"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="177"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="161"/>
-      <c r="J25" s="177"/>
-      <c r="K25" s="161"/>
-      <c r="L25" s="166"/>
-      <c r="M25" s="167"/>
-      <c r="N25" s="161"/>
-      <c r="O25" s="166"/>
-      <c r="P25" s="167"/>
-      <c r="Q25" s="161"/>
+      <c r="A25" s="182"/>
+      <c r="B25" s="162"/>
+      <c r="C25" s="183"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="183"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="163"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="167"/>
+      <c r="M25" s="161"/>
+      <c r="N25" s="162"/>
+      <c r="O25" s="167"/>
+      <c r="P25" s="161"/>
+      <c r="Q25" s="162"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
@@ -10309,23 +11207,23 @@
       <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="48" customHeight="1">
-      <c r="A26" s="160"/>
-      <c r="B26" s="161"/>
-      <c r="C26" s="162"/>
-      <c r="D26" s="161"/>
-      <c r="E26" s="162"/>
-      <c r="F26" s="161"/>
-      <c r="G26" s="177"/>
-      <c r="H26" s="167"/>
-      <c r="I26" s="161"/>
-      <c r="J26" s="177"/>
-      <c r="K26" s="161"/>
-      <c r="L26" s="166"/>
-      <c r="M26" s="167"/>
-      <c r="N26" s="161"/>
-      <c r="O26" s="166"/>
-      <c r="P26" s="167"/>
-      <c r="Q26" s="161"/>
+      <c r="A26" s="182"/>
+      <c r="B26" s="162"/>
+      <c r="C26" s="183"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="183"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="163"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="162"/>
+      <c r="L26" s="167"/>
+      <c r="M26" s="161"/>
+      <c r="N26" s="162"/>
+      <c r="O26" s="167"/>
+      <c r="P26" s="161"/>
+      <c r="Q26" s="162"/>
       <c r="R26" s="25"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -10337,23 +11235,23 @@
       <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="48" customHeight="1">
-      <c r="A27" s="160"/>
-      <c r="B27" s="161"/>
-      <c r="C27" s="162"/>
-      <c r="D27" s="161"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="161"/>
-      <c r="G27" s="177"/>
-      <c r="H27" s="167"/>
-      <c r="I27" s="161"/>
-      <c r="J27" s="177"/>
-      <c r="K27" s="161"/>
-      <c r="L27" s="166"/>
-      <c r="M27" s="167"/>
-      <c r="N27" s="161"/>
-      <c r="O27" s="166"/>
-      <c r="P27" s="167"/>
-      <c r="Q27" s="161"/>
+      <c r="A27" s="182"/>
+      <c r="B27" s="162"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="183"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="163"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="162"/>
+      <c r="L27" s="167"/>
+      <c r="M27" s="161"/>
+      <c r="N27" s="162"/>
+      <c r="O27" s="167"/>
+      <c r="P27" s="161"/>
+      <c r="Q27" s="162"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="26"/>
@@ -10365,23 +11263,23 @@
       <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="48" customHeight="1">
-      <c r="A28" s="160"/>
-      <c r="B28" s="161"/>
-      <c r="C28" s="162"/>
-      <c r="D28" s="161"/>
-      <c r="E28" s="162"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="177"/>
-      <c r="H28" s="167"/>
-      <c r="I28" s="161"/>
-      <c r="J28" s="177"/>
-      <c r="K28" s="161"/>
-      <c r="L28" s="166"/>
-      <c r="M28" s="167"/>
-      <c r="N28" s="161"/>
-      <c r="O28" s="166"/>
-      <c r="P28" s="167"/>
-      <c r="Q28" s="161"/>
+      <c r="A28" s="182"/>
+      <c r="B28" s="162"/>
+      <c r="C28" s="183"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="183"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="163"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="163"/>
+      <c r="K28" s="162"/>
+      <c r="L28" s="167"/>
+      <c r="M28" s="161"/>
+      <c r="N28" s="162"/>
+      <c r="O28" s="167"/>
+      <c r="P28" s="161"/>
+      <c r="Q28" s="162"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
       <c r="T28" s="26"/>
@@ -10393,23 +11291,23 @@
       <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="48" customHeight="1">
-      <c r="A29" s="160"/>
-      <c r="B29" s="161"/>
-      <c r="C29" s="162"/>
-      <c r="D29" s="161"/>
-      <c r="E29" s="162"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="177"/>
-      <c r="H29" s="167"/>
-      <c r="I29" s="161"/>
-      <c r="J29" s="177"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="166"/>
-      <c r="M29" s="167"/>
-      <c r="N29" s="161"/>
-      <c r="O29" s="166"/>
-      <c r="P29" s="167"/>
-      <c r="Q29" s="161"/>
+      <c r="A29" s="182"/>
+      <c r="B29" s="162"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="167"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="162"/>
+      <c r="O29" s="167"/>
+      <c r="P29" s="161"/>
+      <c r="Q29" s="162"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
       <c r="T29" s="26"/>
@@ -10421,23 +11319,23 @@
       <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="48" customHeight="1">
-      <c r="A30" s="160"/>
-      <c r="B30" s="161"/>
-      <c r="C30" s="162"/>
-      <c r="D30" s="161"/>
-      <c r="E30" s="162"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="177"/>
-      <c r="H30" s="167"/>
-      <c r="I30" s="161"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="161"/>
-      <c r="L30" s="166"/>
-      <c r="M30" s="167"/>
-      <c r="N30" s="161"/>
-      <c r="O30" s="166"/>
-      <c r="P30" s="167"/>
-      <c r="Q30" s="161"/>
+      <c r="A30" s="182"/>
+      <c r="B30" s="162"/>
+      <c r="C30" s="183"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="183"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="163"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="162"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="161"/>
+      <c r="N30" s="162"/>
+      <c r="O30" s="167"/>
+      <c r="P30" s="161"/>
+      <c r="Q30" s="162"/>
       <c r="R30" s="25"/>
       <c r="S30" s="25"/>
       <c r="T30" s="26"/>
@@ -10449,23 +11347,23 @@
       <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="48" customHeight="1">
-      <c r="A31" s="163"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="165"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="165"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="186"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="186"/>
-      <c r="K31" s="164"/>
+      <c r="A31" s="185"/>
+      <c r="B31" s="166"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="165"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="164"/>
+      <c r="K31" s="166"/>
       <c r="L31" s="168"/>
-      <c r="M31" s="169"/>
-      <c r="N31" s="164"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="166"/>
       <c r="O31" s="168"/>
-      <c r="P31" s="169"/>
-      <c r="Q31" s="164"/>
+      <c r="P31" s="165"/>
+      <c r="Q31" s="166"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="29"/>
@@ -11463,62 +12361,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11543,65 +12441,3581 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326B7E18-7F0C-4C95-83EE-A2B9A69E6A02}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="214" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="215" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="214" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="215" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="214" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="214" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="214"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="257" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="257"/>
+      <c r="C1" s="256" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="255"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="253" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="252"/>
+      <c r="H1" s="252"/>
+      <c r="I1" s="252"/>
+      <c r="J1" s="252"/>
+      <c r="K1" s="252"/>
+      <c r="L1" s="252"/>
+      <c r="M1" s="251"/>
+      <c r="N1" s="250" t="s">
+        <v>121</v>
+      </c>
+      <c r="O1" s="253" t="s">
+        <v>114</v>
+      </c>
+      <c r="P1" s="251"/>
+      <c r="Q1" s="250" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="253" t="s">
+        <v>119</v>
+      </c>
+      <c r="S1" s="251"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="257"/>
+      <c r="B2" s="257"/>
+      <c r="C2" s="256" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="255"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="253" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="252"/>
+      <c r="H2" s="252"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="M2" s="251"/>
+      <c r="N2" s="250" t="s">
+        <v>116</v>
+      </c>
+      <c r="O2" s="249">
+        <v>46190</v>
+      </c>
+      <c r="P2" s="248"/>
+      <c r="Q2" s="247" t="s">
+        <v>115</v>
+      </c>
+      <c r="R2" s="246" t="s">
+        <v>114</v>
+      </c>
+      <c r="S2" s="245"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="243"/>
+      <c r="B3" s="244"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="M3" s="243"/>
+      <c r="N3" s="243"/>
+      <c r="O3" s="243"/>
+      <c r="P3" s="243"/>
+      <c r="Q3" s="243"/>
+      <c r="R3" s="243"/>
+      <c r="S3" s="243"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="240" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="242" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="239" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="238"/>
+      <c r="H4" s="239" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="M4" s="238"/>
+      <c r="N4" s="239" t="s">
+        <v>109</v>
+      </c>
+      <c r="O4" s="241"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="240" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" s="239" t="s">
+        <v>107</v>
+      </c>
+      <c r="S4" s="238"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="237">
+        <v>1</v>
+      </c>
+      <c r="B5" s="236" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="235" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
+      <c r="M5" s="235"/>
+      <c r="N5" s="234" t="s">
+        <v>103</v>
+      </c>
+      <c r="O5" s="233"/>
+      <c r="P5" s="232"/>
+      <c r="Q5" s="231">
+        <v>46190</v>
+      </c>
+      <c r="R5" s="230"/>
+      <c r="S5" s="229"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="217"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="224"/>
+      <c r="I6" s="224"/>
+      <c r="J6" s="224"/>
+      <c r="K6" s="224"/>
+      <c r="L6" s="224"/>
+      <c r="M6" s="224"/>
+      <c r="N6" s="228"/>
+      <c r="O6" s="227"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="225"/>
+      <c r="R6" s="216"/>
+      <c r="S6" s="216"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="217"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="224"/>
+      <c r="H7" s="224"/>
+      <c r="I7" s="224"/>
+      <c r="J7" s="224"/>
+      <c r="K7" s="224"/>
+      <c r="L7" s="224"/>
+      <c r="M7" s="224"/>
+      <c r="N7" s="220"/>
+      <c r="O7" s="219"/>
+      <c r="P7" s="218"/>
+      <c r="Q7" s="225"/>
+      <c r="R7" s="216"/>
+      <c r="S7" s="216"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="217"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="224"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="224"/>
+      <c r="H8" s="224"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="224"/>
+      <c r="K8" s="224"/>
+      <c r="L8" s="224"/>
+      <c r="M8" s="224"/>
+      <c r="N8" s="220"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="218"/>
+      <c r="Q8" s="225"/>
+      <c r="R8" s="216"/>
+      <c r="S8" s="216"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="217"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="224"/>
+      <c r="D9" s="224"/>
+      <c r="E9" s="224"/>
+      <c r="F9" s="224"/>
+      <c r="G9" s="224"/>
+      <c r="H9" s="224"/>
+      <c r="I9" s="224"/>
+      <c r="J9" s="224"/>
+      <c r="K9" s="224"/>
+      <c r="L9" s="224"/>
+      <c r="M9" s="224"/>
+      <c r="N9" s="220"/>
+      <c r="O9" s="219"/>
+      <c r="P9" s="218"/>
+      <c r="Q9" s="217"/>
+      <c r="R9" s="216"/>
+      <c r="S9" s="216"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="217"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="224"/>
+      <c r="D10" s="224"/>
+      <c r="E10" s="224"/>
+      <c r="F10" s="224"/>
+      <c r="G10" s="224"/>
+      <c r="H10" s="223"/>
+      <c r="I10" s="222"/>
+      <c r="J10" s="222"/>
+      <c r="K10" s="222"/>
+      <c r="L10" s="222"/>
+      <c r="M10" s="221"/>
+      <c r="N10" s="220"/>
+      <c r="O10" s="219"/>
+      <c r="P10" s="218"/>
+      <c r="Q10" s="225"/>
+      <c r="R10" s="216"/>
+      <c r="S10" s="216"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="217"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="224"/>
+      <c r="D11" s="224"/>
+      <c r="E11" s="224"/>
+      <c r="F11" s="224"/>
+      <c r="G11" s="224"/>
+      <c r="H11" s="223"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="222"/>
+      <c r="K11" s="222"/>
+      <c r="L11" s="222"/>
+      <c r="M11" s="221"/>
+      <c r="N11" s="220"/>
+      <c r="O11" s="219"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="217"/>
+      <c r="R11" s="216"/>
+      <c r="S11" s="216"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="217"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="224"/>
+      <c r="D12" s="224"/>
+      <c r="E12" s="224"/>
+      <c r="F12" s="224"/>
+      <c r="G12" s="224"/>
+      <c r="H12" s="223"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="222"/>
+      <c r="K12" s="222"/>
+      <c r="L12" s="222"/>
+      <c r="M12" s="221"/>
+      <c r="N12" s="220"/>
+      <c r="O12" s="219"/>
+      <c r="P12" s="218"/>
+      <c r="Q12" s="217"/>
+      <c r="R12" s="216"/>
+      <c r="S12" s="216"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="217"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="224"/>
+      <c r="D13" s="224"/>
+      <c r="E13" s="224"/>
+      <c r="F13" s="224"/>
+      <c r="G13" s="224"/>
+      <c r="H13" s="223"/>
+      <c r="I13" s="222"/>
+      <c r="J13" s="222"/>
+      <c r="K13" s="222"/>
+      <c r="L13" s="222"/>
+      <c r="M13" s="221"/>
+      <c r="N13" s="220"/>
+      <c r="O13" s="219"/>
+      <c r="P13" s="218"/>
+      <c r="Q13" s="217"/>
+      <c r="R13" s="216"/>
+      <c r="S13" s="216"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="217"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="224"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="224"/>
+      <c r="G14" s="224"/>
+      <c r="H14" s="223"/>
+      <c r="I14" s="222"/>
+      <c r="J14" s="222"/>
+      <c r="K14" s="222"/>
+      <c r="L14" s="222"/>
+      <c r="M14" s="221"/>
+      <c r="N14" s="220"/>
+      <c r="O14" s="219"/>
+      <c r="P14" s="218"/>
+      <c r="Q14" s="217"/>
+      <c r="R14" s="216"/>
+      <c r="S14" s="216"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="217"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="224"/>
+      <c r="D15" s="224"/>
+      <c r="E15" s="224"/>
+      <c r="F15" s="224"/>
+      <c r="G15" s="224"/>
+      <c r="H15" s="223"/>
+      <c r="I15" s="222"/>
+      <c r="J15" s="222"/>
+      <c r="K15" s="222"/>
+      <c r="L15" s="222"/>
+      <c r="M15" s="221"/>
+      <c r="N15" s="220"/>
+      <c r="O15" s="219"/>
+      <c r="P15" s="218"/>
+      <c r="Q15" s="217"/>
+      <c r="R15" s="216"/>
+      <c r="S15" s="216"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="217"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="224"/>
+      <c r="D16" s="224"/>
+      <c r="E16" s="224"/>
+      <c r="F16" s="224"/>
+      <c r="G16" s="224"/>
+      <c r="H16" s="223"/>
+      <c r="I16" s="222"/>
+      <c r="J16" s="222"/>
+      <c r="K16" s="222"/>
+      <c r="L16" s="222"/>
+      <c r="M16" s="221"/>
+      <c r="N16" s="220"/>
+      <c r="O16" s="219"/>
+      <c r="P16" s="218"/>
+      <c r="Q16" s="217"/>
+      <c r="R16" s="216"/>
+      <c r="S16" s="216"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="217"/>
+      <c r="B17" s="217"/>
+      <c r="C17" s="224"/>
+      <c r="D17" s="224"/>
+      <c r="E17" s="224"/>
+      <c r="F17" s="224"/>
+      <c r="G17" s="224"/>
+      <c r="H17" s="223"/>
+      <c r="I17" s="222"/>
+      <c r="J17" s="222"/>
+      <c r="K17" s="222"/>
+      <c r="L17" s="222"/>
+      <c r="M17" s="221"/>
+      <c r="N17" s="220"/>
+      <c r="O17" s="219"/>
+      <c r="P17" s="218"/>
+      <c r="Q17" s="217"/>
+      <c r="R17" s="216"/>
+      <c r="S17" s="216"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="217"/>
+      <c r="B18" s="217"/>
+      <c r="C18" s="224"/>
+      <c r="D18" s="224"/>
+      <c r="E18" s="224"/>
+      <c r="F18" s="224"/>
+      <c r="G18" s="224"/>
+      <c r="H18" s="223"/>
+      <c r="I18" s="222"/>
+      <c r="J18" s="222"/>
+      <c r="K18" s="222"/>
+      <c r="L18" s="222"/>
+      <c r="M18" s="221"/>
+      <c r="N18" s="220"/>
+      <c r="O18" s="219"/>
+      <c r="P18" s="218"/>
+      <c r="Q18" s="217"/>
+      <c r="R18" s="216"/>
+      <c r="S18" s="216"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="217"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="224"/>
+      <c r="D19" s="224"/>
+      <c r="E19" s="224"/>
+      <c r="F19" s="224"/>
+      <c r="G19" s="224"/>
+      <c r="H19" s="223"/>
+      <c r="I19" s="222"/>
+      <c r="J19" s="222"/>
+      <c r="K19" s="222"/>
+      <c r="L19" s="222"/>
+      <c r="M19" s="221"/>
+      <c r="N19" s="220"/>
+      <c r="O19" s="219"/>
+      <c r="P19" s="218"/>
+      <c r="Q19" s="217"/>
+      <c r="R19" s="216"/>
+      <c r="S19" s="216"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="217"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="224"/>
+      <c r="D20" s="224"/>
+      <c r="E20" s="224"/>
+      <c r="F20" s="224"/>
+      <c r="G20" s="224"/>
+      <c r="H20" s="223"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
+      <c r="L20" s="222"/>
+      <c r="M20" s="221"/>
+      <c r="N20" s="220"/>
+      <c r="O20" s="219"/>
+      <c r="P20" s="218"/>
+      <c r="Q20" s="217"/>
+      <c r="R20" s="216"/>
+      <c r="S20" s="216"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="217"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="224"/>
+      <c r="D21" s="224"/>
+      <c r="E21" s="224"/>
+      <c r="F21" s="224"/>
+      <c r="G21" s="224"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="222"/>
+      <c r="J21" s="222"/>
+      <c r="K21" s="222"/>
+      <c r="L21" s="222"/>
+      <c r="M21" s="221"/>
+      <c r="N21" s="220"/>
+      <c r="O21" s="219"/>
+      <c r="P21" s="218"/>
+      <c r="Q21" s="217"/>
+      <c r="R21" s="216"/>
+      <c r="S21" s="216"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="217"/>
+      <c r="B22" s="217"/>
+      <c r="C22" s="224"/>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="224"/>
+      <c r="H22" s="223"/>
+      <c r="I22" s="222"/>
+      <c r="J22" s="222"/>
+      <c r="K22" s="222"/>
+      <c r="L22" s="222"/>
+      <c r="M22" s="221"/>
+      <c r="N22" s="220"/>
+      <c r="O22" s="219"/>
+      <c r="P22" s="218"/>
+      <c r="Q22" s="217"/>
+      <c r="R22" s="216"/>
+      <c r="S22" s="216"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="217"/>
+      <c r="B23" s="217"/>
+      <c r="C23" s="224"/>
+      <c r="D23" s="224"/>
+      <c r="E23" s="224"/>
+      <c r="F23" s="224"/>
+      <c r="G23" s="224"/>
+      <c r="H23" s="223"/>
+      <c r="I23" s="222"/>
+      <c r="J23" s="222"/>
+      <c r="K23" s="222"/>
+      <c r="L23" s="222"/>
+      <c r="M23" s="221"/>
+      <c r="N23" s="220"/>
+      <c r="O23" s="219"/>
+      <c r="P23" s="218"/>
+      <c r="Q23" s="217"/>
+      <c r="R23" s="216"/>
+      <c r="S23" s="216"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="217"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="224"/>
+      <c r="D24" s="224"/>
+      <c r="E24" s="224"/>
+      <c r="F24" s="224"/>
+      <c r="G24" s="224"/>
+      <c r="H24" s="223"/>
+      <c r="I24" s="222"/>
+      <c r="J24" s="222"/>
+      <c r="K24" s="222"/>
+      <c r="L24" s="222"/>
+      <c r="M24" s="221"/>
+      <c r="N24" s="220"/>
+      <c r="O24" s="219"/>
+      <c r="P24" s="218"/>
+      <c r="Q24" s="217"/>
+      <c r="R24" s="216"/>
+      <c r="S24" s="216"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="217"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="224"/>
+      <c r="D25" s="224"/>
+      <c r="E25" s="224"/>
+      <c r="F25" s="224"/>
+      <c r="G25" s="224"/>
+      <c r="H25" s="223"/>
+      <c r="I25" s="222"/>
+      <c r="J25" s="222"/>
+      <c r="K25" s="222"/>
+      <c r="L25" s="222"/>
+      <c r="M25" s="221"/>
+      <c r="N25" s="220"/>
+      <c r="O25" s="219"/>
+      <c r="P25" s="218"/>
+      <c r="Q25" s="217"/>
+      <c r="R25" s="216"/>
+      <c r="S25" s="216"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="217"/>
+      <c r="B26" s="217"/>
+      <c r="C26" s="224"/>
+      <c r="D26" s="224"/>
+      <c r="E26" s="224"/>
+      <c r="F26" s="224"/>
+      <c r="G26" s="224"/>
+      <c r="H26" s="223"/>
+      <c r="I26" s="222"/>
+      <c r="J26" s="222"/>
+      <c r="K26" s="222"/>
+      <c r="L26" s="222"/>
+      <c r="M26" s="221"/>
+      <c r="N26" s="220"/>
+      <c r="O26" s="219"/>
+      <c r="P26" s="218"/>
+      <c r="Q26" s="217"/>
+      <c r="R26" s="216"/>
+      <c r="S26" s="216"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="217"/>
+      <c r="B27" s="217"/>
+      <c r="C27" s="224"/>
+      <c r="D27" s="224"/>
+      <c r="E27" s="224"/>
+      <c r="F27" s="224"/>
+      <c r="G27" s="224"/>
+      <c r="H27" s="223"/>
+      <c r="I27" s="222"/>
+      <c r="J27" s="222"/>
+      <c r="K27" s="222"/>
+      <c r="L27" s="222"/>
+      <c r="M27" s="221"/>
+      <c r="N27" s="220"/>
+      <c r="O27" s="219"/>
+      <c r="P27" s="218"/>
+      <c r="Q27" s="217"/>
+      <c r="R27" s="216"/>
+      <c r="S27" s="216"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="217"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="224"/>
+      <c r="D28" s="224"/>
+      <c r="E28" s="224"/>
+      <c r="F28" s="224"/>
+      <c r="G28" s="224"/>
+      <c r="H28" s="223"/>
+      <c r="I28" s="222"/>
+      <c r="J28" s="222"/>
+      <c r="K28" s="222"/>
+      <c r="L28" s="222"/>
+      <c r="M28" s="221"/>
+      <c r="N28" s="220"/>
+      <c r="O28" s="219"/>
+      <c r="P28" s="218"/>
+      <c r="Q28" s="217"/>
+      <c r="R28" s="216"/>
+      <c r="S28" s="216"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="217"/>
+      <c r="B29" s="217"/>
+      <c r="C29" s="224"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="224"/>
+      <c r="H29" s="223"/>
+      <c r="I29" s="222"/>
+      <c r="J29" s="222"/>
+      <c r="K29" s="222"/>
+      <c r="L29" s="222"/>
+      <c r="M29" s="221"/>
+      <c r="N29" s="220"/>
+      <c r="O29" s="219"/>
+      <c r="P29" s="218"/>
+      <c r="Q29" s="217"/>
+      <c r="R29" s="216"/>
+      <c r="S29" s="216"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="217"/>
+      <c r="B30" s="217"/>
+      <c r="C30" s="224"/>
+      <c r="D30" s="224"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="224"/>
+      <c r="H30" s="223"/>
+      <c r="I30" s="222"/>
+      <c r="J30" s="222"/>
+      <c r="K30" s="222"/>
+      <c r="L30" s="222"/>
+      <c r="M30" s="221"/>
+      <c r="N30" s="220"/>
+      <c r="O30" s="219"/>
+      <c r="P30" s="218"/>
+      <c r="Q30" s="217"/>
+      <c r="R30" s="216"/>
+      <c r="S30" s="216"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="217"/>
+      <c r="B31" s="217"/>
+      <c r="C31" s="224"/>
+      <c r="D31" s="224"/>
+      <c r="E31" s="224"/>
+      <c r="F31" s="224"/>
+      <c r="G31" s="224"/>
+      <c r="H31" s="223"/>
+      <c r="I31" s="222"/>
+      <c r="J31" s="222"/>
+      <c r="K31" s="222"/>
+      <c r="L31" s="222"/>
+      <c r="M31" s="221"/>
+      <c r="N31" s="220"/>
+      <c r="O31" s="219"/>
+      <c r="P31" s="218"/>
+      <c r="Q31" s="217"/>
+      <c r="R31" s="216"/>
+      <c r="S31" s="216"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="217"/>
+      <c r="B32" s="217"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="223"/>
+      <c r="I32" s="222"/>
+      <c r="J32" s="222"/>
+      <c r="K32" s="222"/>
+      <c r="L32" s="222"/>
+      <c r="M32" s="221"/>
+      <c r="N32" s="220"/>
+      <c r="O32" s="219"/>
+      <c r="P32" s="218"/>
+      <c r="Q32" s="217"/>
+      <c r="R32" s="216"/>
+      <c r="S32" s="216"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="217"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="223"/>
+      <c r="I33" s="222"/>
+      <c r="J33" s="222"/>
+      <c r="K33" s="222"/>
+      <c r="L33" s="222"/>
+      <c r="M33" s="221"/>
+      <c r="N33" s="220"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="218"/>
+      <c r="Q33" s="217"/>
+      <c r="R33" s="216"/>
+      <c r="S33" s="216"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="217"/>
+      <c r="B34" s="217"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="223"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="222"/>
+      <c r="K34" s="222"/>
+      <c r="L34" s="222"/>
+      <c r="M34" s="221"/>
+      <c r="N34" s="220"/>
+      <c r="O34" s="219"/>
+      <c r="P34" s="218"/>
+      <c r="Q34" s="217"/>
+      <c r="R34" s="216"/>
+      <c r="S34" s="216"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="217"/>
+      <c r="B35" s="217"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="223"/>
+      <c r="I35" s="222"/>
+      <c r="J35" s="222"/>
+      <c r="K35" s="222"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="221"/>
+      <c r="N35" s="220"/>
+      <c r="O35" s="219"/>
+      <c r="P35" s="218"/>
+      <c r="Q35" s="217"/>
+      <c r="R35" s="216"/>
+      <c r="S35" s="216"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="217"/>
+      <c r="B36" s="217"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="222"/>
+      <c r="J36" s="222"/>
+      <c r="K36" s="222"/>
+      <c r="L36" s="222"/>
+      <c r="M36" s="221"/>
+      <c r="N36" s="220"/>
+      <c r="O36" s="219"/>
+      <c r="P36" s="218"/>
+      <c r="Q36" s="217"/>
+      <c r="R36" s="216"/>
+      <c r="S36" s="216"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="217"/>
+      <c r="B37" s="217"/>
+      <c r="C37" s="224"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="224"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="224"/>
+      <c r="H37" s="223"/>
+      <c r="I37" s="222"/>
+      <c r="J37" s="222"/>
+      <c r="K37" s="222"/>
+      <c r="L37" s="222"/>
+      <c r="M37" s="221"/>
+      <c r="N37" s="220"/>
+      <c r="O37" s="219"/>
+      <c r="P37" s="218"/>
+      <c r="Q37" s="217"/>
+      <c r="R37" s="216"/>
+      <c r="S37" s="216"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="217"/>
+      <c r="B38" s="217"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
+      <c r="H38" s="223"/>
+      <c r="I38" s="222"/>
+      <c r="J38" s="222"/>
+      <c r="K38" s="222"/>
+      <c r="L38" s="222"/>
+      <c r="M38" s="221"/>
+      <c r="N38" s="220"/>
+      <c r="O38" s="219"/>
+      <c r="P38" s="218"/>
+      <c r="Q38" s="217"/>
+      <c r="R38" s="216"/>
+      <c r="S38" s="216"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="217"/>
+      <c r="B39" s="217"/>
+      <c r="C39" s="224"/>
+      <c r="D39" s="224"/>
+      <c r="E39" s="224"/>
+      <c r="F39" s="224"/>
+      <c r="G39" s="224"/>
+      <c r="H39" s="223"/>
+      <c r="I39" s="222"/>
+      <c r="J39" s="222"/>
+      <c r="K39" s="222"/>
+      <c r="L39" s="222"/>
+      <c r="M39" s="221"/>
+      <c r="N39" s="220"/>
+      <c r="O39" s="219"/>
+      <c r="P39" s="218"/>
+      <c r="Q39" s="217"/>
+      <c r="R39" s="216"/>
+      <c r="S39" s="216"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="217"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="224"/>
+      <c r="D40" s="224"/>
+      <c r="E40" s="224"/>
+      <c r="F40" s="224"/>
+      <c r="G40" s="224"/>
+      <c r="H40" s="223"/>
+      <c r="I40" s="222"/>
+      <c r="J40" s="222"/>
+      <c r="K40" s="222"/>
+      <c r="L40" s="222"/>
+      <c r="M40" s="221"/>
+      <c r="N40" s="220"/>
+      <c r="O40" s="219"/>
+      <c r="P40" s="218"/>
+      <c r="Q40" s="217"/>
+      <c r="R40" s="216"/>
+      <c r="S40" s="216"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="217"/>
+      <c r="B41" s="217"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="224"/>
+      <c r="E41" s="224"/>
+      <c r="F41" s="224"/>
+      <c r="G41" s="224"/>
+      <c r="H41" s="223"/>
+      <c r="I41" s="222"/>
+      <c r="J41" s="222"/>
+      <c r="K41" s="222"/>
+      <c r="L41" s="222"/>
+      <c r="M41" s="221"/>
+      <c r="N41" s="220"/>
+      <c r="O41" s="219"/>
+      <c r="P41" s="218"/>
+      <c r="Q41" s="217"/>
+      <c r="R41" s="216"/>
+      <c r="S41" s="216"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="217"/>
+      <c r="B42" s="217"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="223"/>
+      <c r="I42" s="222"/>
+      <c r="J42" s="222"/>
+      <c r="K42" s="222"/>
+      <c r="L42" s="222"/>
+      <c r="M42" s="221"/>
+      <c r="N42" s="220"/>
+      <c r="O42" s="219"/>
+      <c r="P42" s="218"/>
+      <c r="Q42" s="217"/>
+      <c r="R42" s="216"/>
+      <c r="S42" s="216"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="217"/>
+      <c r="B43" s="217"/>
+      <c r="C43" s="224"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="224"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="223"/>
+      <c r="I43" s="222"/>
+      <c r="J43" s="222"/>
+      <c r="K43" s="222"/>
+      <c r="L43" s="222"/>
+      <c r="M43" s="221"/>
+      <c r="N43" s="220"/>
+      <c r="O43" s="219"/>
+      <c r="P43" s="218"/>
+      <c r="Q43" s="217"/>
+      <c r="R43" s="216"/>
+      <c r="S43" s="216"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="217"/>
+      <c r="B44" s="217"/>
+      <c r="C44" s="224"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="224"/>
+      <c r="F44" s="224"/>
+      <c r="G44" s="224"/>
+      <c r="H44" s="223"/>
+      <c r="I44" s="222"/>
+      <c r="J44" s="222"/>
+      <c r="K44" s="222"/>
+      <c r="L44" s="222"/>
+      <c r="M44" s="221"/>
+      <c r="N44" s="220"/>
+      <c r="O44" s="219"/>
+      <c r="P44" s="218"/>
+      <c r="Q44" s="217"/>
+      <c r="R44" s="216"/>
+      <c r="S44" s="216"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="217"/>
+      <c r="B45" s="217"/>
+      <c r="C45" s="224"/>
+      <c r="D45" s="224"/>
+      <c r="E45" s="224"/>
+      <c r="F45" s="224"/>
+      <c r="G45" s="224"/>
+      <c r="H45" s="223"/>
+      <c r="I45" s="222"/>
+      <c r="J45" s="222"/>
+      <c r="K45" s="222"/>
+      <c r="L45" s="222"/>
+      <c r="M45" s="221"/>
+      <c r="N45" s="220"/>
+      <c r="O45" s="219"/>
+      <c r="P45" s="218"/>
+      <c r="Q45" s="217"/>
+      <c r="R45" s="216"/>
+      <c r="S45" s="216"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="217"/>
+      <c r="B46" s="217"/>
+      <c r="C46" s="224"/>
+      <c r="D46" s="224"/>
+      <c r="E46" s="224"/>
+      <c r="F46" s="224"/>
+      <c r="G46" s="224"/>
+      <c r="H46" s="223"/>
+      <c r="I46" s="222"/>
+      <c r="J46" s="222"/>
+      <c r="K46" s="222"/>
+      <c r="L46" s="222"/>
+      <c r="M46" s="221"/>
+      <c r="N46" s="220"/>
+      <c r="O46" s="219"/>
+      <c r="P46" s="218"/>
+      <c r="Q46" s="217"/>
+      <c r="R46" s="216"/>
+      <c r="S46" s="216"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="217"/>
+      <c r="B47" s="217"/>
+      <c r="C47" s="224"/>
+      <c r="D47" s="224"/>
+      <c r="E47" s="224"/>
+      <c r="F47" s="224"/>
+      <c r="G47" s="224"/>
+      <c r="H47" s="223"/>
+      <c r="I47" s="222"/>
+      <c r="J47" s="222"/>
+      <c r="K47" s="222"/>
+      <c r="L47" s="222"/>
+      <c r="M47" s="221"/>
+      <c r="N47" s="220"/>
+      <c r="O47" s="219"/>
+      <c r="P47" s="218"/>
+      <c r="Q47" s="217"/>
+      <c r="R47" s="216"/>
+      <c r="S47" s="216"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="217"/>
+      <c r="B48" s="217"/>
+      <c r="C48" s="224"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="224"/>
+      <c r="H48" s="223"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="222"/>
+      <c r="L48" s="222"/>
+      <c r="M48" s="221"/>
+      <c r="N48" s="220"/>
+      <c r="O48" s="219"/>
+      <c r="P48" s="218"/>
+      <c r="Q48" s="217"/>
+      <c r="R48" s="216"/>
+      <c r="S48" s="216"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="217"/>
+      <c r="B49" s="217"/>
+      <c r="C49" s="224"/>
+      <c r="D49" s="224"/>
+      <c r="E49" s="224"/>
+      <c r="F49" s="224"/>
+      <c r="G49" s="224"/>
+      <c r="H49" s="223"/>
+      <c r="I49" s="222"/>
+      <c r="J49" s="222"/>
+      <c r="K49" s="222"/>
+      <c r="L49" s="222"/>
+      <c r="M49" s="221"/>
+      <c r="N49" s="220"/>
+      <c r="O49" s="219"/>
+      <c r="P49" s="218"/>
+      <c r="Q49" s="217"/>
+      <c r="R49" s="216"/>
+      <c r="S49" s="216"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="217"/>
+      <c r="B50" s="217"/>
+      <c r="C50" s="224"/>
+      <c r="D50" s="224"/>
+      <c r="E50" s="224"/>
+      <c r="F50" s="224"/>
+      <c r="G50" s="224"/>
+      <c r="H50" s="223"/>
+      <c r="I50" s="222"/>
+      <c r="J50" s="222"/>
+      <c r="K50" s="222"/>
+      <c r="L50" s="222"/>
+      <c r="M50" s="221"/>
+      <c r="N50" s="220"/>
+      <c r="O50" s="219"/>
+      <c r="P50" s="218"/>
+      <c r="Q50" s="217"/>
+      <c r="R50" s="216"/>
+      <c r="S50" s="216"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="217"/>
+      <c r="B51" s="217"/>
+      <c r="C51" s="224"/>
+      <c r="D51" s="224"/>
+      <c r="E51" s="224"/>
+      <c r="F51" s="224"/>
+      <c r="G51" s="224"/>
+      <c r="H51" s="223"/>
+      <c r="I51" s="222"/>
+      <c r="J51" s="222"/>
+      <c r="K51" s="222"/>
+      <c r="L51" s="222"/>
+      <c r="M51" s="221"/>
+      <c r="N51" s="220"/>
+      <c r="O51" s="219"/>
+      <c r="P51" s="218"/>
+      <c r="Q51" s="217"/>
+      <c r="R51" s="216"/>
+      <c r="S51" s="216"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="217"/>
+      <c r="B52" s="217"/>
+      <c r="C52" s="224"/>
+      <c r="D52" s="224"/>
+      <c r="E52" s="224"/>
+      <c r="F52" s="224"/>
+      <c r="G52" s="224"/>
+      <c r="H52" s="223"/>
+      <c r="I52" s="222"/>
+      <c r="J52" s="222"/>
+      <c r="K52" s="222"/>
+      <c r="L52" s="222"/>
+      <c r="M52" s="221"/>
+      <c r="N52" s="220"/>
+      <c r="O52" s="219"/>
+      <c r="P52" s="218"/>
+      <c r="Q52" s="217"/>
+      <c r="R52" s="216"/>
+      <c r="S52" s="216"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N46:P46"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792C554E-09C6-4F1C-BD6B-D011A7F642CE}">
+  <dimension ref="A1:BA55"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="24.95" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="3" style="187" customWidth="1"/>
+    <col min="3" max="3" width="3" style="188" customWidth="1"/>
+    <col min="4" max="5" width="3" style="187" customWidth="1"/>
+    <col min="6" max="6" width="3" style="188" customWidth="1"/>
+    <col min="7" max="16384" width="3" style="187"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:53" ht="30" customHeight="1">
+      <c r="A1" s="190"/>
+      <c r="B1" s="213" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="212"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="190"/>
+      <c r="R1" s="190"/>
+      <c r="S1" s="190"/>
+      <c r="T1" s="190"/>
+      <c r="U1" s="190"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="190"/>
+      <c r="Y1" s="190"/>
+      <c r="Z1" s="190"/>
+      <c r="AA1" s="190"/>
+      <c r="AB1" s="190"/>
+      <c r="AC1" s="211"/>
+      <c r="AD1" s="210"/>
+      <c r="AE1" s="211"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="190"/>
+      <c r="AH1" s="190"/>
+      <c r="AI1" s="190"/>
+      <c r="AJ1" s="190"/>
+      <c r="AK1" s="190"/>
+      <c r="AL1" s="190"/>
+      <c r="AM1" s="190"/>
+      <c r="AN1" s="190"/>
+      <c r="AO1" s="209" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP1" s="209"/>
+      <c r="AQ1" s="209"/>
+      <c r="AR1" s="209"/>
+      <c r="AS1" s="209"/>
+      <c r="AT1" s="208">
+        <v>46190</v>
+      </c>
+      <c r="AU1" s="207"/>
+      <c r="AV1" s="207"/>
+      <c r="AW1" s="207"/>
+      <c r="AX1" s="207"/>
+      <c r="AY1" s="207"/>
+      <c r="AZ1" s="207"/>
+      <c r="BA1" s="207"/>
+    </row>
+    <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="4" spans="1:53" ht="18" customHeight="1">
+      <c r="A4" s="201" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="201"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
+      <c r="M4" s="201"/>
+      <c r="N4" s="201"/>
+      <c r="O4" s="201"/>
+      <c r="P4" s="201"/>
+      <c r="Q4" s="201"/>
+      <c r="R4" s="201"/>
+      <c r="S4" s="201"/>
+      <c r="T4" s="201"/>
+      <c r="U4" s="201"/>
+      <c r="V4" s="201"/>
+      <c r="W4" s="201"/>
+      <c r="X4" s="201"/>
+      <c r="Y4" s="201"/>
+      <c r="Z4" s="201"/>
+      <c r="AA4" s="201"/>
+      <c r="AB4" s="201"/>
+      <c r="AC4" s="201"/>
+      <c r="AD4" s="201"/>
+      <c r="AE4" s="201"/>
+      <c r="AF4" s="201"/>
+      <c r="AG4" s="201"/>
+      <c r="AH4" s="201"/>
+      <c r="AI4" s="201"/>
+      <c r="AJ4" s="201"/>
+      <c r="AK4" s="201"/>
+    </row>
+    <row r="5" spans="1:53" ht="24.95" customHeight="1">
+      <c r="A5" s="199" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="205" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="203"/>
+      <c r="O5" s="203"/>
+      <c r="P5" s="203"/>
+      <c r="Q5" s="203"/>
+      <c r="R5" s="203"/>
+      <c r="S5" s="202"/>
+    </row>
+    <row r="6" spans="1:53" ht="24.95" customHeight="1">
+      <c r="A6" s="199" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="198"/>
+      <c r="C6" s="198"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="204">
+        <v>1</v>
+      </c>
+      <c r="H6" s="203"/>
+      <c r="I6" s="203"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="203"/>
+      <c r="O6" s="203"/>
+      <c r="P6" s="203"/>
+      <c r="Q6" s="203"/>
+      <c r="R6" s="203"/>
+      <c r="S6" s="202"/>
+    </row>
+    <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="8" spans="1:53" ht="18" customHeight="1">
+      <c r="A8" s="201" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" ht="18" customHeight="1">
+      <c r="A9" s="199" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="198"/>
+      <c r="F9" s="198"/>
+      <c r="G9" s="198"/>
+      <c r="H9" s="198"/>
+      <c r="I9" s="198"/>
+      <c r="J9" s="198"/>
+      <c r="K9" s="198"/>
+      <c r="L9" s="198"/>
+      <c r="M9" s="198"/>
+      <c r="N9" s="198"/>
+      <c r="O9" s="198"/>
+      <c r="P9" s="198"/>
+      <c r="Q9" s="198"/>
+      <c r="R9" s="198"/>
+      <c r="S9" s="198"/>
+      <c r="T9" s="198"/>
+      <c r="U9" s="198"/>
+      <c r="V9" s="198"/>
+      <c r="W9" s="198"/>
+      <c r="X9" s="198"/>
+      <c r="Y9" s="198"/>
+      <c r="Z9" s="198"/>
+      <c r="AA9" s="198"/>
+      <c r="AB9" s="198"/>
+      <c r="AC9" s="198"/>
+      <c r="AD9" s="198"/>
+      <c r="AE9" s="198"/>
+      <c r="AF9" s="198"/>
+      <c r="AG9" s="198"/>
+      <c r="AH9" s="198"/>
+      <c r="AI9" s="198"/>
+      <c r="AJ9" s="198"/>
+      <c r="AK9" s="198"/>
+      <c r="AL9" s="198"/>
+      <c r="AM9" s="198"/>
+      <c r="AN9" s="198"/>
+      <c r="AO9" s="198"/>
+      <c r="AP9" s="198"/>
+      <c r="AQ9" s="198"/>
+      <c r="AR9" s="198"/>
+      <c r="AS9" s="198"/>
+      <c r="AT9" s="198"/>
+      <c r="AU9" s="198"/>
+      <c r="AV9" s="198"/>
+      <c r="AW9" s="198"/>
+      <c r="AX9" s="198"/>
+      <c r="AY9" s="198"/>
+      <c r="AZ9" s="198"/>
+      <c r="BA9" s="200"/>
+    </row>
+    <row r="10" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A10" s="195"/>
+      <c r="B10" s="194"/>
+      <c r="C10" s="194"/>
+      <c r="D10" s="194"/>
+      <c r="E10" s="194"/>
+      <c r="F10" s="194"/>
+      <c r="G10" s="194"/>
+      <c r="H10" s="194"/>
+      <c r="I10" s="194"/>
+      <c r="J10" s="194"/>
+      <c r="K10" s="194"/>
+      <c r="L10" s="194"/>
+      <c r="M10" s="194"/>
+      <c r="N10" s="194"/>
+      <c r="O10" s="194"/>
+      <c r="P10" s="194"/>
+      <c r="Q10" s="194"/>
+      <c r="R10" s="194"/>
+      <c r="S10" s="194"/>
+      <c r="T10" s="194"/>
+      <c r="U10" s="194"/>
+      <c r="V10" s="194"/>
+      <c r="W10" s="194"/>
+      <c r="X10" s="194"/>
+      <c r="Y10" s="194"/>
+      <c r="Z10" s="194"/>
+      <c r="AA10" s="194"/>
+      <c r="AB10" s="194"/>
+      <c r="AC10" s="194"/>
+      <c r="AD10" s="194"/>
+      <c r="AE10" s="194"/>
+      <c r="AF10" s="194"/>
+      <c r="AG10" s="194"/>
+      <c r="AH10" s="194"/>
+      <c r="AI10" s="194"/>
+      <c r="AJ10" s="194"/>
+      <c r="AK10" s="194"/>
+      <c r="BA10" s="193"/>
+    </row>
+    <row r="11" spans="1:53" ht="21.75" customHeight="1">
+      <c r="A11" s="195"/>
+      <c r="B11" s="194"/>
+      <c r="C11" s="194"/>
+      <c r="D11" s="194"/>
+      <c r="E11" s="194"/>
+      <c r="F11" s="194"/>
+      <c r="G11" s="194"/>
+      <c r="H11" s="194"/>
+      <c r="I11" s="194"/>
+      <c r="J11" s="194"/>
+      <c r="K11" s="194"/>
+      <c r="L11" s="194"/>
+      <c r="M11" s="194"/>
+      <c r="N11" s="194"/>
+      <c r="O11" s="194"/>
+      <c r="P11" s="194"/>
+      <c r="Q11" s="194"/>
+      <c r="R11" s="194"/>
+      <c r="S11" s="194"/>
+      <c r="T11" s="194"/>
+      <c r="U11" s="194"/>
+      <c r="V11" s="194"/>
+      <c r="W11" s="194"/>
+      <c r="X11" s="194"/>
+      <c r="Y11" s="194"/>
+      <c r="Z11" s="194"/>
+      <c r="AA11" s="194"/>
+      <c r="AB11" s="194"/>
+      <c r="AC11" s="194"/>
+      <c r="AD11" s="194"/>
+      <c r="AE11" s="194"/>
+      <c r="AF11" s="194"/>
+      <c r="AG11" s="194"/>
+      <c r="AH11" s="194"/>
+      <c r="AI11" s="194"/>
+      <c r="AJ11" s="194"/>
+      <c r="AK11" s="194"/>
+      <c r="BA11" s="193"/>
+    </row>
+    <row r="12" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A12" s="195"/>
+      <c r="B12" s="194"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
+      <c r="F12" s="194"/>
+      <c r="G12" s="194"/>
+      <c r="H12" s="194"/>
+      <c r="I12" s="194"/>
+      <c r="J12" s="194"/>
+      <c r="K12" s="194"/>
+      <c r="L12" s="194"/>
+      <c r="M12" s="194"/>
+      <c r="N12" s="194"/>
+      <c r="O12" s="194"/>
+      <c r="P12" s="194"/>
+      <c r="Q12" s="194"/>
+      <c r="R12" s="194"/>
+      <c r="S12" s="194"/>
+      <c r="T12" s="194"/>
+      <c r="U12" s="194"/>
+      <c r="V12" s="194"/>
+      <c r="W12" s="194"/>
+      <c r="X12" s="194"/>
+      <c r="Y12" s="194"/>
+      <c r="Z12" s="194"/>
+      <c r="AA12" s="194"/>
+      <c r="AB12" s="194"/>
+      <c r="AC12" s="194"/>
+      <c r="AD12" s="194"/>
+      <c r="AE12" s="194"/>
+      <c r="AF12" s="194"/>
+      <c r="AG12" s="194"/>
+      <c r="AH12" s="194"/>
+      <c r="AI12" s="194"/>
+      <c r="AJ12" s="194"/>
+      <c r="AK12" s="194"/>
+      <c r="BA12" s="193"/>
+    </row>
+    <row r="13" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A13" s="195"/>
+      <c r="B13" s="194"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
+      <c r="F13" s="194"/>
+      <c r="G13" s="194"/>
+      <c r="H13" s="194"/>
+      <c r="I13" s="194"/>
+      <c r="J13" s="194"/>
+      <c r="K13" s="194"/>
+      <c r="L13" s="194"/>
+      <c r="M13" s="194"/>
+      <c r="N13" s="194"/>
+      <c r="O13" s="194"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="194"/>
+      <c r="S13" s="194"/>
+      <c r="T13" s="194"/>
+      <c r="U13" s="194"/>
+      <c r="V13" s="194"/>
+      <c r="W13" s="194"/>
+      <c r="X13" s="194"/>
+      <c r="Y13" s="194"/>
+      <c r="Z13" s="194"/>
+      <c r="AA13" s="194"/>
+      <c r="AB13" s="194"/>
+      <c r="AC13" s="194"/>
+      <c r="AD13" s="194"/>
+      <c r="AE13" s="194"/>
+      <c r="AF13" s="194"/>
+      <c r="AG13" s="194"/>
+      <c r="AH13" s="194"/>
+      <c r="AI13" s="194"/>
+      <c r="AJ13" s="194"/>
+      <c r="AK13" s="194"/>
+      <c r="BA13" s="193"/>
+    </row>
+    <row r="14" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A14" s="195"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
+      <c r="F14" s="194"/>
+      <c r="G14" s="194"/>
+      <c r="H14" s="194"/>
+      <c r="I14" s="194"/>
+      <c r="J14" s="194"/>
+      <c r="K14" s="194"/>
+      <c r="L14" s="194"/>
+      <c r="M14" s="194"/>
+      <c r="N14" s="194"/>
+      <c r="O14" s="194"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="194"/>
+      <c r="S14" s="194"/>
+      <c r="T14" s="194"/>
+      <c r="U14" s="194"/>
+      <c r="V14" s="194"/>
+      <c r="W14" s="194"/>
+      <c r="X14" s="194"/>
+      <c r="Y14" s="194"/>
+      <c r="Z14" s="194"/>
+      <c r="AA14" s="194"/>
+      <c r="AB14" s="194"/>
+      <c r="AC14" s="194"/>
+      <c r="AD14" s="194"/>
+      <c r="AE14" s="194"/>
+      <c r="AF14" s="194"/>
+      <c r="AG14" s="194"/>
+      <c r="AH14" s="194"/>
+      <c r="AI14" s="194"/>
+      <c r="AJ14" s="194"/>
+      <c r="AK14" s="194"/>
+      <c r="BA14" s="193"/>
+    </row>
+    <row r="15" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A15" s="195"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="194"/>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
+      <c r="F15" s="194"/>
+      <c r="G15" s="194"/>
+      <c r="H15" s="194"/>
+      <c r="I15" s="194"/>
+      <c r="J15" s="194"/>
+      <c r="K15" s="194"/>
+      <c r="L15" s="194"/>
+      <c r="M15" s="194"/>
+      <c r="N15" s="194"/>
+      <c r="O15" s="194"/>
+      <c r="P15" s="194"/>
+      <c r="Q15" s="194"/>
+      <c r="R15" s="194"/>
+      <c r="S15" s="194"/>
+      <c r="T15" s="194"/>
+      <c r="U15" s="194"/>
+      <c r="V15" s="194"/>
+      <c r="W15" s="194"/>
+      <c r="X15" s="194"/>
+      <c r="Y15" s="194"/>
+      <c r="Z15" s="194"/>
+      <c r="AA15" s="194"/>
+      <c r="AB15" s="194"/>
+      <c r="AC15" s="194"/>
+      <c r="AD15" s="194"/>
+      <c r="AE15" s="194"/>
+      <c r="AF15" s="194"/>
+      <c r="AG15" s="194"/>
+      <c r="AH15" s="194"/>
+      <c r="AI15" s="194"/>
+      <c r="AJ15" s="194"/>
+      <c r="AK15" s="194"/>
+      <c r="BA15" s="193"/>
+    </row>
+    <row r="16" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A16" s="195"/>
+      <c r="B16" s="194"/>
+      <c r="C16" s="194"/>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
+      <c r="F16" s="194"/>
+      <c r="G16" s="194"/>
+      <c r="H16" s="194"/>
+      <c r="I16" s="194"/>
+      <c r="J16" s="194"/>
+      <c r="K16" s="194"/>
+      <c r="L16" s="194"/>
+      <c r="M16" s="194"/>
+      <c r="N16" s="194"/>
+      <c r="O16" s="194"/>
+      <c r="P16" s="194"/>
+      <c r="Q16" s="194"/>
+      <c r="R16" s="194"/>
+      <c r="S16" s="194"/>
+      <c r="T16" s="194"/>
+      <c r="U16" s="194"/>
+      <c r="V16" s="194"/>
+      <c r="W16" s="194"/>
+      <c r="X16" s="194"/>
+      <c r="Y16" s="194"/>
+      <c r="Z16" s="194"/>
+      <c r="AA16" s="194"/>
+      <c r="AB16" s="194"/>
+      <c r="AC16" s="194"/>
+      <c r="AD16" s="194"/>
+      <c r="AE16" s="194"/>
+      <c r="AF16" s="194"/>
+      <c r="AG16" s="194"/>
+      <c r="AH16" s="194"/>
+      <c r="AI16" s="194"/>
+      <c r="AJ16" s="194"/>
+      <c r="AK16" s="194"/>
+      <c r="BA16" s="193"/>
+    </row>
+    <row r="17" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A17" s="195"/>
+      <c r="B17" s="194"/>
+      <c r="C17" s="194"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="194"/>
+      <c r="G17" s="194"/>
+      <c r="H17" s="194"/>
+      <c r="I17" s="194"/>
+      <c r="J17" s="194"/>
+      <c r="K17" s="194"/>
+      <c r="L17" s="194"/>
+      <c r="M17" s="194"/>
+      <c r="N17" s="194"/>
+      <c r="O17" s="194"/>
+      <c r="P17" s="194"/>
+      <c r="Q17" s="194"/>
+      <c r="R17" s="194"/>
+      <c r="S17" s="194"/>
+      <c r="T17" s="194"/>
+      <c r="U17" s="194"/>
+      <c r="V17" s="194"/>
+      <c r="W17" s="194"/>
+      <c r="X17" s="194"/>
+      <c r="Y17" s="194"/>
+      <c r="Z17" s="194"/>
+      <c r="AA17" s="194"/>
+      <c r="AB17" s="194"/>
+      <c r="AC17" s="194"/>
+      <c r="AD17" s="194"/>
+      <c r="AE17" s="194"/>
+      <c r="AF17" s="194"/>
+      <c r="AG17" s="194"/>
+      <c r="AH17" s="194"/>
+      <c r="AI17" s="194"/>
+      <c r="AJ17" s="194"/>
+      <c r="AK17" s="194"/>
+      <c r="BA17" s="193"/>
+    </row>
+    <row r="18" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A18" s="195"/>
+      <c r="B18" s="194"/>
+      <c r="C18" s="194"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="194"/>
+      <c r="G18" s="194"/>
+      <c r="H18" s="194"/>
+      <c r="I18" s="194"/>
+      <c r="J18" s="194"/>
+      <c r="K18" s="194"/>
+      <c r="L18" s="194"/>
+      <c r="M18" s="194"/>
+      <c r="N18" s="194"/>
+      <c r="O18" s="194"/>
+      <c r="P18" s="194"/>
+      <c r="Q18" s="194"/>
+      <c r="R18" s="194"/>
+      <c r="S18" s="194"/>
+      <c r="T18" s="194"/>
+      <c r="U18" s="194"/>
+      <c r="V18" s="194"/>
+      <c r="W18" s="194"/>
+      <c r="X18" s="194"/>
+      <c r="Y18" s="194"/>
+      <c r="Z18" s="194"/>
+      <c r="AA18" s="194"/>
+      <c r="AB18" s="194"/>
+      <c r="AC18" s="194"/>
+      <c r="AD18" s="194"/>
+      <c r="AE18" s="194"/>
+      <c r="AF18" s="194"/>
+      <c r="AG18" s="194"/>
+      <c r="AH18" s="194"/>
+      <c r="AI18" s="194"/>
+      <c r="AJ18" s="194"/>
+      <c r="AK18" s="194"/>
+      <c r="BA18" s="193"/>
+    </row>
+    <row r="19" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A19" s="195"/>
+      <c r="B19" s="194"/>
+      <c r="C19" s="194"/>
+      <c r="D19" s="194"/>
+      <c r="E19" s="194"/>
+      <c r="F19" s="194"/>
+      <c r="G19" s="194"/>
+      <c r="H19" s="194"/>
+      <c r="I19" s="194"/>
+      <c r="J19" s="194"/>
+      <c r="K19" s="194"/>
+      <c r="L19" s="194"/>
+      <c r="M19" s="194"/>
+      <c r="N19" s="194"/>
+      <c r="O19" s="194"/>
+      <c r="P19" s="194"/>
+      <c r="Q19" s="194"/>
+      <c r="R19" s="194"/>
+      <c r="S19" s="194"/>
+      <c r="T19" s="194"/>
+      <c r="U19" s="194"/>
+      <c r="V19" s="194"/>
+      <c r="W19" s="194"/>
+      <c r="X19" s="194"/>
+      <c r="Y19" s="194"/>
+      <c r="Z19" s="194"/>
+      <c r="AA19" s="194"/>
+      <c r="AB19" s="194"/>
+      <c r="AC19" s="194"/>
+      <c r="AD19" s="194"/>
+      <c r="AE19" s="194"/>
+      <c r="AF19" s="194"/>
+      <c r="AG19" s="194"/>
+      <c r="AH19" s="194"/>
+      <c r="AI19" s="194"/>
+      <c r="AJ19" s="194"/>
+      <c r="AK19" s="194"/>
+      <c r="BA19" s="193"/>
+    </row>
+    <row r="20" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A20" s="195"/>
+      <c r="B20" s="194"/>
+      <c r="C20" s="194"/>
+      <c r="D20" s="194"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="194"/>
+      <c r="G20" s="194"/>
+      <c r="H20" s="194"/>
+      <c r="I20" s="194"/>
+      <c r="J20" s="194"/>
+      <c r="K20" s="194"/>
+      <c r="L20" s="194"/>
+      <c r="M20" s="194"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="194"/>
+      <c r="P20" s="194"/>
+      <c r="Q20" s="194"/>
+      <c r="R20" s="194"/>
+      <c r="S20" s="194"/>
+      <c r="T20" s="194"/>
+      <c r="U20" s="194"/>
+      <c r="V20" s="194"/>
+      <c r="W20" s="194"/>
+      <c r="X20" s="194"/>
+      <c r="Y20" s="194"/>
+      <c r="Z20" s="194"/>
+      <c r="AA20" s="194"/>
+      <c r="AB20" s="194"/>
+      <c r="AC20" s="194"/>
+      <c r="AD20" s="194"/>
+      <c r="AE20" s="194"/>
+      <c r="AF20" s="194"/>
+      <c r="AG20" s="194"/>
+      <c r="AH20" s="194"/>
+      <c r="AI20" s="194"/>
+      <c r="AJ20" s="194"/>
+      <c r="AK20" s="194"/>
+      <c r="BA20" s="193"/>
+    </row>
+    <row r="21" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A21" s="195"/>
+      <c r="B21" s="194"/>
+      <c r="C21" s="194"/>
+      <c r="D21" s="194"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="194"/>
+      <c r="G21" s="194"/>
+      <c r="H21" s="194"/>
+      <c r="I21" s="194"/>
+      <c r="J21" s="194"/>
+      <c r="K21" s="194"/>
+      <c r="L21" s="194"/>
+      <c r="M21" s="194"/>
+      <c r="N21" s="194"/>
+      <c r="O21" s="194"/>
+      <c r="P21" s="194"/>
+      <c r="Q21" s="194"/>
+      <c r="R21" s="194"/>
+      <c r="S21" s="194"/>
+      <c r="T21" s="194"/>
+      <c r="U21" s="194"/>
+      <c r="V21" s="194"/>
+      <c r="W21" s="194"/>
+      <c r="X21" s="194"/>
+      <c r="Y21" s="194"/>
+      <c r="Z21" s="194"/>
+      <c r="AA21" s="194"/>
+      <c r="AB21" s="194"/>
+      <c r="AC21" s="194"/>
+      <c r="AD21" s="194"/>
+      <c r="AE21" s="194"/>
+      <c r="AF21" s="194"/>
+      <c r="AG21" s="194"/>
+      <c r="AH21" s="194"/>
+      <c r="AI21" s="194"/>
+      <c r="AJ21" s="194"/>
+      <c r="AK21" s="194"/>
+      <c r="BA21" s="193"/>
+    </row>
+    <row r="22" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A22" s="195"/>
+      <c r="B22" s="194"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="194"/>
+      <c r="G22" s="194"/>
+      <c r="H22" s="194"/>
+      <c r="I22" s="194"/>
+      <c r="J22" s="194"/>
+      <c r="K22" s="194"/>
+      <c r="L22" s="194"/>
+      <c r="M22" s="194"/>
+      <c r="N22" s="194"/>
+      <c r="O22" s="194"/>
+      <c r="P22" s="194"/>
+      <c r="Q22" s="194"/>
+      <c r="R22" s="194"/>
+      <c r="S22" s="194"/>
+      <c r="T22" s="194"/>
+      <c r="U22" s="194"/>
+      <c r="V22" s="194"/>
+      <c r="W22" s="194"/>
+      <c r="X22" s="194"/>
+      <c r="Y22" s="194"/>
+      <c r="Z22" s="194"/>
+      <c r="AA22" s="194"/>
+      <c r="AB22" s="194"/>
+      <c r="AC22" s="194"/>
+      <c r="AD22" s="194"/>
+      <c r="AE22" s="194"/>
+      <c r="AF22" s="194"/>
+      <c r="AG22" s="194"/>
+      <c r="AH22" s="194"/>
+      <c r="AI22" s="194"/>
+      <c r="AJ22" s="194"/>
+      <c r="AK22" s="194"/>
+      <c r="BA22" s="193"/>
+    </row>
+    <row r="23" spans="1:53" ht="21.75" customHeight="1">
+      <c r="A23" s="195"/>
+      <c r="B23" s="194"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="194"/>
+      <c r="G23" s="194"/>
+      <c r="H23" s="194"/>
+      <c r="I23" s="194"/>
+      <c r="J23" s="194"/>
+      <c r="K23" s="194"/>
+      <c r="L23" s="194"/>
+      <c r="M23" s="194"/>
+      <c r="N23" s="194"/>
+      <c r="O23" s="194"/>
+      <c r="P23" s="194"/>
+      <c r="Q23" s="194"/>
+      <c r="R23" s="194"/>
+      <c r="S23" s="194"/>
+      <c r="T23" s="194"/>
+      <c r="U23" s="194"/>
+      <c r="V23" s="194"/>
+      <c r="W23" s="194"/>
+      <c r="X23" s="194"/>
+      <c r="Y23" s="194"/>
+      <c r="Z23" s="194"/>
+      <c r="AA23" s="194"/>
+      <c r="AB23" s="194"/>
+      <c r="AC23" s="194"/>
+      <c r="AD23" s="194"/>
+      <c r="AE23" s="194"/>
+      <c r="AF23" s="194"/>
+      <c r="AG23" s="194"/>
+      <c r="AH23" s="194"/>
+      <c r="AI23" s="194"/>
+      <c r="AJ23" s="194"/>
+      <c r="AK23" s="194"/>
+      <c r="BA23" s="193"/>
+    </row>
+    <row r="24" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A24" s="195"/>
+      <c r="B24" s="194"/>
+      <c r="C24" s="194"/>
+      <c r="D24" s="194"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="194"/>
+      <c r="G24" s="194"/>
+      <c r="H24" s="194"/>
+      <c r="I24" s="194"/>
+      <c r="J24" s="194"/>
+      <c r="K24" s="194"/>
+      <c r="L24" s="194"/>
+      <c r="M24" s="194"/>
+      <c r="N24" s="194"/>
+      <c r="O24" s="194"/>
+      <c r="P24" s="194"/>
+      <c r="Q24" s="194"/>
+      <c r="R24" s="194"/>
+      <c r="S24" s="194"/>
+      <c r="T24" s="194"/>
+      <c r="U24" s="194"/>
+      <c r="V24" s="194"/>
+      <c r="W24" s="194"/>
+      <c r="X24" s="194"/>
+      <c r="Y24" s="194"/>
+      <c r="Z24" s="194"/>
+      <c r="AA24" s="194"/>
+      <c r="AB24" s="194"/>
+      <c r="AC24" s="194"/>
+      <c r="AD24" s="194"/>
+      <c r="AE24" s="194"/>
+      <c r="AF24" s="194"/>
+      <c r="AG24" s="194"/>
+      <c r="AH24" s="194"/>
+      <c r="AI24" s="194"/>
+      <c r="AJ24" s="194"/>
+      <c r="AK24" s="194"/>
+      <c r="BA24" s="193"/>
+    </row>
+    <row r="25" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A25" s="195"/>
+      <c r="B25" s="194"/>
+      <c r="C25" s="194"/>
+      <c r="D25" s="194"/>
+      <c r="E25" s="194"/>
+      <c r="F25" s="194"/>
+      <c r="G25" s="194"/>
+      <c r="H25" s="194"/>
+      <c r="I25" s="194"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="194"/>
+      <c r="L25" s="194"/>
+      <c r="M25" s="194"/>
+      <c r="N25" s="194"/>
+      <c r="O25" s="194"/>
+      <c r="P25" s="194"/>
+      <c r="Q25" s="194"/>
+      <c r="R25" s="194"/>
+      <c r="S25" s="194"/>
+      <c r="T25" s="194"/>
+      <c r="U25" s="194"/>
+      <c r="V25" s="194"/>
+      <c r="W25" s="194"/>
+      <c r="X25" s="194"/>
+      <c r="Y25" s="194"/>
+      <c r="Z25" s="194"/>
+      <c r="AA25" s="194"/>
+      <c r="AB25" s="194"/>
+      <c r="AC25" s="194"/>
+      <c r="AD25" s="194"/>
+      <c r="AE25" s="194"/>
+      <c r="AF25" s="194"/>
+      <c r="AG25" s="194"/>
+      <c r="AH25" s="194"/>
+      <c r="AI25" s="194"/>
+      <c r="AJ25" s="194"/>
+      <c r="AK25" s="194"/>
+      <c r="BA25" s="193"/>
+    </row>
+    <row r="26" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A26" s="195"/>
+      <c r="B26" s="194"/>
+      <c r="C26" s="194"/>
+      <c r="D26" s="194"/>
+      <c r="E26" s="194"/>
+      <c r="F26" s="194"/>
+      <c r="G26" s="194"/>
+      <c r="H26" s="194"/>
+      <c r="I26" s="194"/>
+      <c r="J26" s="194"/>
+      <c r="K26" s="194"/>
+      <c r="L26" s="194"/>
+      <c r="M26" s="194"/>
+      <c r="N26" s="194"/>
+      <c r="O26" s="194"/>
+      <c r="P26" s="194"/>
+      <c r="Q26" s="194"/>
+      <c r="R26" s="194"/>
+      <c r="S26" s="194"/>
+      <c r="T26" s="194"/>
+      <c r="U26" s="194"/>
+      <c r="V26" s="194"/>
+      <c r="W26" s="194"/>
+      <c r="X26" s="194"/>
+      <c r="Y26" s="194"/>
+      <c r="Z26" s="194"/>
+      <c r="AA26" s="194"/>
+      <c r="AB26" s="194"/>
+      <c r="AC26" s="194"/>
+      <c r="AD26" s="194"/>
+      <c r="AE26" s="194"/>
+      <c r="AF26" s="194"/>
+      <c r="AG26" s="194"/>
+      <c r="AH26" s="194"/>
+      <c r="AI26" s="194"/>
+      <c r="AJ26" s="194"/>
+      <c r="AK26" s="194"/>
+      <c r="BA26" s="193"/>
+    </row>
+    <row r="27" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A27" s="195"/>
+      <c r="B27" s="194"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="194"/>
+      <c r="L27" s="194"/>
+      <c r="M27" s="194"/>
+      <c r="N27" s="194"/>
+      <c r="O27" s="194"/>
+      <c r="P27" s="194"/>
+      <c r="Q27" s="194"/>
+      <c r="R27" s="194"/>
+      <c r="S27" s="194"/>
+      <c r="T27" s="194"/>
+      <c r="U27" s="194"/>
+      <c r="V27" s="194"/>
+      <c r="W27" s="194"/>
+      <c r="X27" s="194"/>
+      <c r="Y27" s="194"/>
+      <c r="Z27" s="194"/>
+      <c r="AA27" s="194"/>
+      <c r="AB27" s="194"/>
+      <c r="AC27" s="194"/>
+      <c r="AD27" s="194"/>
+      <c r="AE27" s="194"/>
+      <c r="AF27" s="194"/>
+      <c r="AG27" s="194"/>
+      <c r="AH27" s="194"/>
+      <c r="AI27" s="194"/>
+      <c r="AJ27" s="194"/>
+      <c r="AK27" s="194"/>
+      <c r="BA27" s="193"/>
+    </row>
+    <row r="28" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A28" s="195"/>
+      <c r="B28" s="194"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="194"/>
+      <c r="E28" s="194"/>
+      <c r="F28" s="194"/>
+      <c r="G28" s="194"/>
+      <c r="H28" s="194"/>
+      <c r="I28" s="194"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="194"/>
+      <c r="L28" s="194"/>
+      <c r="M28" s="194"/>
+      <c r="N28" s="194"/>
+      <c r="O28" s="194"/>
+      <c r="P28" s="194"/>
+      <c r="Q28" s="194"/>
+      <c r="R28" s="194"/>
+      <c r="S28" s="194"/>
+      <c r="T28" s="194"/>
+      <c r="U28" s="194"/>
+      <c r="V28" s="194"/>
+      <c r="W28" s="194"/>
+      <c r="X28" s="194"/>
+      <c r="Y28" s="194"/>
+      <c r="Z28" s="194"/>
+      <c r="AA28" s="194"/>
+      <c r="AB28" s="194"/>
+      <c r="AC28" s="194"/>
+      <c r="AD28" s="194"/>
+      <c r="AE28" s="194"/>
+      <c r="AF28" s="194"/>
+      <c r="AG28" s="194"/>
+      <c r="AH28" s="194"/>
+      <c r="AI28" s="194"/>
+      <c r="AJ28" s="194"/>
+      <c r="AK28" s="194"/>
+      <c r="BA28" s="193"/>
+    </row>
+    <row r="29" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A29" s="195"/>
+      <c r="B29" s="194"/>
+      <c r="C29" s="194"/>
+      <c r="D29" s="194"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="194"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="194"/>
+      <c r="I29" s="194"/>
+      <c r="J29" s="194"/>
+      <c r="K29" s="194"/>
+      <c r="L29" s="194"/>
+      <c r="M29" s="194"/>
+      <c r="N29" s="194"/>
+      <c r="O29" s="194"/>
+      <c r="P29" s="194"/>
+      <c r="Q29" s="194"/>
+      <c r="R29" s="194"/>
+      <c r="S29" s="194"/>
+      <c r="T29" s="194"/>
+      <c r="U29" s="194"/>
+      <c r="V29" s="194"/>
+      <c r="W29" s="194"/>
+      <c r="X29" s="194"/>
+      <c r="Y29" s="194"/>
+      <c r="Z29" s="194"/>
+      <c r="AA29" s="194"/>
+      <c r="AB29" s="194"/>
+      <c r="AC29" s="194"/>
+      <c r="AD29" s="194"/>
+      <c r="AE29" s="194"/>
+      <c r="AF29" s="194"/>
+      <c r="AG29" s="194"/>
+      <c r="AH29" s="194"/>
+      <c r="AI29" s="194"/>
+      <c r="AJ29" s="194"/>
+      <c r="AK29" s="194"/>
+      <c r="BA29" s="193"/>
+    </row>
+    <row r="30" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A30" s="195"/>
+      <c r="B30" s="194"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="194"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="194"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="194"/>
+      <c r="I30" s="194"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="194"/>
+      <c r="L30" s="194"/>
+      <c r="M30" s="194"/>
+      <c r="N30" s="194"/>
+      <c r="O30" s="194"/>
+      <c r="P30" s="194"/>
+      <c r="Q30" s="194"/>
+      <c r="R30" s="194"/>
+      <c r="S30" s="194"/>
+      <c r="T30" s="194"/>
+      <c r="U30" s="194"/>
+      <c r="V30" s="194"/>
+      <c r="W30" s="194"/>
+      <c r="X30" s="194"/>
+      <c r="Y30" s="194"/>
+      <c r="Z30" s="194"/>
+      <c r="AA30" s="194"/>
+      <c r="AB30" s="194"/>
+      <c r="AC30" s="194"/>
+      <c r="AD30" s="194"/>
+      <c r="AE30" s="194"/>
+      <c r="AF30" s="194"/>
+      <c r="AG30" s="194"/>
+      <c r="AH30" s="194"/>
+      <c r="AI30" s="194"/>
+      <c r="AJ30" s="194"/>
+      <c r="AK30" s="194"/>
+      <c r="BA30" s="193"/>
+    </row>
+    <row r="31" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A31" s="195"/>
+      <c r="B31" s="194"/>
+      <c r="C31" s="194"/>
+      <c r="D31" s="194"/>
+      <c r="E31" s="194"/>
+      <c r="F31" s="194"/>
+      <c r="G31" s="194"/>
+      <c r="H31" s="194"/>
+      <c r="I31" s="194"/>
+      <c r="J31" s="194"/>
+      <c r="K31" s="194"/>
+      <c r="L31" s="194"/>
+      <c r="M31" s="194"/>
+      <c r="N31" s="194"/>
+      <c r="O31" s="194"/>
+      <c r="P31" s="194"/>
+      <c r="Q31" s="194"/>
+      <c r="R31" s="194"/>
+      <c r="S31" s="194"/>
+      <c r="T31" s="194"/>
+      <c r="U31" s="194"/>
+      <c r="V31" s="194"/>
+      <c r="W31" s="194"/>
+      <c r="X31" s="194"/>
+      <c r="Y31" s="194"/>
+      <c r="Z31" s="194"/>
+      <c r="AA31" s="194"/>
+      <c r="AB31" s="194"/>
+      <c r="AC31" s="194"/>
+      <c r="AD31" s="194"/>
+      <c r="AE31" s="194"/>
+      <c r="AF31" s="194"/>
+      <c r="AG31" s="194"/>
+      <c r="AH31" s="194"/>
+      <c r="AI31" s="194"/>
+      <c r="AJ31" s="194"/>
+      <c r="AK31" s="194"/>
+      <c r="BA31" s="193"/>
+    </row>
+    <row r="32" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A32" s="195"/>
+      <c r="B32" s="194"/>
+      <c r="C32" s="194"/>
+      <c r="D32" s="194"/>
+      <c r="E32" s="194"/>
+      <c r="F32" s="194"/>
+      <c r="G32" s="194"/>
+      <c r="H32" s="194"/>
+      <c r="I32" s="194"/>
+      <c r="J32" s="194"/>
+      <c r="K32" s="194"/>
+      <c r="L32" s="194"/>
+      <c r="M32" s="194"/>
+      <c r="N32" s="194"/>
+      <c r="O32" s="194"/>
+      <c r="P32" s="194"/>
+      <c r="Q32" s="194"/>
+      <c r="R32" s="194"/>
+      <c r="S32" s="194"/>
+      <c r="T32" s="194"/>
+      <c r="U32" s="194"/>
+      <c r="V32" s="194"/>
+      <c r="W32" s="194"/>
+      <c r="X32" s="194"/>
+      <c r="Y32" s="194"/>
+      <c r="Z32" s="194"/>
+      <c r="AA32" s="194"/>
+      <c r="AB32" s="194"/>
+      <c r="AC32" s="194"/>
+      <c r="AD32" s="194"/>
+      <c r="AE32" s="194"/>
+      <c r="AF32" s="194"/>
+      <c r="AG32" s="194"/>
+      <c r="AH32" s="194"/>
+      <c r="AI32" s="194"/>
+      <c r="AJ32" s="194"/>
+      <c r="AK32" s="194"/>
+      <c r="BA32" s="193"/>
+    </row>
+    <row r="33" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A33" s="195"/>
+      <c r="B33" s="194"/>
+      <c r="C33" s="194"/>
+      <c r="D33" s="194"/>
+      <c r="E33" s="194"/>
+      <c r="F33" s="194"/>
+      <c r="G33" s="194"/>
+      <c r="H33" s="194"/>
+      <c r="I33" s="194"/>
+      <c r="J33" s="194"/>
+      <c r="K33" s="194"/>
+      <c r="L33" s="194"/>
+      <c r="M33" s="194"/>
+      <c r="N33" s="194"/>
+      <c r="O33" s="194"/>
+      <c r="P33" s="194"/>
+      <c r="Q33" s="194"/>
+      <c r="R33" s="194"/>
+      <c r="S33" s="194"/>
+      <c r="T33" s="194"/>
+      <c r="U33" s="194"/>
+      <c r="V33" s="194"/>
+      <c r="W33" s="194"/>
+      <c r="X33" s="194"/>
+      <c r="Y33" s="194"/>
+      <c r="Z33" s="194"/>
+      <c r="AA33" s="194"/>
+      <c r="AB33" s="194"/>
+      <c r="AC33" s="194"/>
+      <c r="AD33" s="194"/>
+      <c r="AE33" s="194"/>
+      <c r="AF33" s="194"/>
+      <c r="AG33" s="194"/>
+      <c r="AH33" s="194"/>
+      <c r="AI33" s="194"/>
+      <c r="AJ33" s="194"/>
+      <c r="AK33" s="194"/>
+      <c r="BA33" s="193"/>
+    </row>
+    <row r="34" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A34" s="195"/>
+      <c r="B34" s="194"/>
+      <c r="C34" s="194"/>
+      <c r="D34" s="194"/>
+      <c r="E34" s="194"/>
+      <c r="F34" s="194"/>
+      <c r="G34" s="194"/>
+      <c r="H34" s="194"/>
+      <c r="I34" s="194"/>
+      <c r="J34" s="194"/>
+      <c r="K34" s="194"/>
+      <c r="L34" s="194"/>
+      <c r="M34" s="194"/>
+      <c r="N34" s="194"/>
+      <c r="O34" s="194"/>
+      <c r="P34" s="194"/>
+      <c r="Q34" s="194"/>
+      <c r="R34" s="194"/>
+      <c r="S34" s="194"/>
+      <c r="T34" s="194"/>
+      <c r="U34" s="194"/>
+      <c r="V34" s="194"/>
+      <c r="W34" s="194"/>
+      <c r="X34" s="194"/>
+      <c r="Y34" s="194"/>
+      <c r="Z34" s="194"/>
+      <c r="AA34" s="194"/>
+      <c r="AB34" s="194"/>
+      <c r="AC34" s="194"/>
+      <c r="AD34" s="194"/>
+      <c r="AE34" s="194"/>
+      <c r="AF34" s="194"/>
+      <c r="AG34" s="194"/>
+      <c r="AH34" s="194"/>
+      <c r="AI34" s="194"/>
+      <c r="AJ34" s="194"/>
+      <c r="AK34" s="194"/>
+      <c r="BA34" s="193"/>
+    </row>
+    <row r="35" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A35" s="195"/>
+      <c r="B35" s="194"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="194"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="194"/>
+      <c r="G35" s="194"/>
+      <c r="H35" s="194"/>
+      <c r="I35" s="194"/>
+      <c r="J35" s="194"/>
+      <c r="K35" s="194"/>
+      <c r="L35" s="194"/>
+      <c r="M35" s="194"/>
+      <c r="N35" s="194"/>
+      <c r="O35" s="194"/>
+      <c r="P35" s="194"/>
+      <c r="Q35" s="194"/>
+      <c r="R35" s="194"/>
+      <c r="S35" s="194"/>
+      <c r="T35" s="194"/>
+      <c r="U35" s="194"/>
+      <c r="V35" s="194"/>
+      <c r="W35" s="194"/>
+      <c r="X35" s="194"/>
+      <c r="Y35" s="194"/>
+      <c r="Z35" s="194"/>
+      <c r="AA35" s="194"/>
+      <c r="AB35" s="194"/>
+      <c r="AC35" s="194"/>
+      <c r="AD35" s="194"/>
+      <c r="AE35" s="194"/>
+      <c r="AF35" s="194"/>
+      <c r="AG35" s="194"/>
+      <c r="AH35" s="194"/>
+      <c r="AI35" s="194"/>
+      <c r="AJ35" s="194"/>
+      <c r="AK35" s="194"/>
+      <c r="BA35" s="193"/>
+    </row>
+    <row r="36" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A36" s="195"/>
+      <c r="B36" s="194"/>
+      <c r="C36" s="194"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="194"/>
+      <c r="G36" s="194"/>
+      <c r="H36" s="194"/>
+      <c r="I36" s="194"/>
+      <c r="J36" s="194"/>
+      <c r="K36" s="194"/>
+      <c r="L36" s="194"/>
+      <c r="M36" s="194"/>
+      <c r="N36" s="194"/>
+      <c r="O36" s="194"/>
+      <c r="P36" s="194"/>
+      <c r="Q36" s="194"/>
+      <c r="R36" s="194"/>
+      <c r="S36" s="194"/>
+      <c r="T36" s="194"/>
+      <c r="U36" s="194"/>
+      <c r="V36" s="194"/>
+      <c r="W36" s="194"/>
+      <c r="X36" s="194"/>
+      <c r="Y36" s="194"/>
+      <c r="Z36" s="194"/>
+      <c r="AA36" s="194"/>
+      <c r="AB36" s="194"/>
+      <c r="AC36" s="194"/>
+      <c r="AD36" s="194"/>
+      <c r="AE36" s="194"/>
+      <c r="AF36" s="194"/>
+      <c r="AG36" s="194"/>
+      <c r="AH36" s="194"/>
+      <c r="AI36" s="194"/>
+      <c r="AJ36" s="194"/>
+      <c r="AK36" s="194"/>
+      <c r="BA36" s="193"/>
+    </row>
+    <row r="37" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A37" s="195"/>
+      <c r="B37" s="194"/>
+      <c r="C37" s="194"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="194"/>
+      <c r="M37" s="194"/>
+      <c r="N37" s="194"/>
+      <c r="O37" s="194"/>
+      <c r="P37" s="194"/>
+      <c r="Q37" s="194"/>
+      <c r="R37" s="194"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="194"/>
+      <c r="U37" s="194"/>
+      <c r="V37" s="194"/>
+      <c r="W37" s="194"/>
+      <c r="X37" s="194"/>
+      <c r="Y37" s="194"/>
+      <c r="Z37" s="194"/>
+      <c r="AA37" s="194"/>
+      <c r="AB37" s="194"/>
+      <c r="AC37" s="194"/>
+      <c r="AD37" s="194"/>
+      <c r="AE37" s="194"/>
+      <c r="AF37" s="194"/>
+      <c r="AG37" s="194"/>
+      <c r="AH37" s="194"/>
+      <c r="AI37" s="194"/>
+      <c r="AJ37" s="194"/>
+      <c r="AK37" s="194"/>
+      <c r="BA37" s="193"/>
+    </row>
+    <row r="38" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A38" s="195"/>
+      <c r="B38" s="194"/>
+      <c r="C38" s="194"/>
+      <c r="D38" s="194"/>
+      <c r="E38" s="194"/>
+      <c r="F38" s="194"/>
+      <c r="G38" s="194"/>
+      <c r="H38" s="194"/>
+      <c r="I38" s="194"/>
+      <c r="J38" s="194"/>
+      <c r="K38" s="194"/>
+      <c r="L38" s="194"/>
+      <c r="M38" s="194"/>
+      <c r="N38" s="194"/>
+      <c r="O38" s="194"/>
+      <c r="P38" s="194"/>
+      <c r="Q38" s="194"/>
+      <c r="R38" s="194"/>
+      <c r="S38" s="194"/>
+      <c r="T38" s="194"/>
+      <c r="U38" s="194"/>
+      <c r="V38" s="194"/>
+      <c r="W38" s="194"/>
+      <c r="X38" s="194"/>
+      <c r="Y38" s="194"/>
+      <c r="Z38" s="194"/>
+      <c r="AA38" s="194"/>
+      <c r="AB38" s="194"/>
+      <c r="AC38" s="194"/>
+      <c r="AD38" s="194"/>
+      <c r="AE38" s="194"/>
+      <c r="AF38" s="194"/>
+      <c r="AG38" s="194"/>
+      <c r="AH38" s="194"/>
+      <c r="AI38" s="194"/>
+      <c r="AJ38" s="194"/>
+      <c r="AK38" s="194"/>
+      <c r="BA38" s="193"/>
+    </row>
+    <row r="39" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A39" s="195"/>
+      <c r="B39" s="194"/>
+      <c r="C39" s="194"/>
+      <c r="D39" s="194"/>
+      <c r="E39" s="194"/>
+      <c r="F39" s="194"/>
+      <c r="G39" s="194"/>
+      <c r="H39" s="194"/>
+      <c r="I39" s="194"/>
+      <c r="J39" s="194"/>
+      <c r="K39" s="194"/>
+      <c r="L39" s="194"/>
+      <c r="M39" s="194"/>
+      <c r="N39" s="194"/>
+      <c r="O39" s="194"/>
+      <c r="P39" s="194"/>
+      <c r="Q39" s="194"/>
+      <c r="R39" s="194"/>
+      <c r="S39" s="194"/>
+      <c r="T39" s="194"/>
+      <c r="U39" s="194"/>
+      <c r="V39" s="194"/>
+      <c r="W39" s="194"/>
+      <c r="X39" s="194"/>
+      <c r="Y39" s="194"/>
+      <c r="Z39" s="194"/>
+      <c r="AA39" s="194"/>
+      <c r="AB39" s="194"/>
+      <c r="AC39" s="194"/>
+      <c r="AD39" s="194"/>
+      <c r="AE39" s="194"/>
+      <c r="AF39" s="194"/>
+      <c r="AG39" s="194"/>
+      <c r="AH39" s="194"/>
+      <c r="AI39" s="194"/>
+      <c r="AJ39" s="194"/>
+      <c r="AK39" s="194"/>
+      <c r="BA39" s="193"/>
+    </row>
+    <row r="40" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A40" s="195"/>
+      <c r="B40" s="194"/>
+      <c r="C40" s="194"/>
+      <c r="D40" s="194"/>
+      <c r="E40" s="194"/>
+      <c r="F40" s="194"/>
+      <c r="G40" s="194"/>
+      <c r="H40" s="194"/>
+      <c r="I40" s="194"/>
+      <c r="J40" s="194"/>
+      <c r="K40" s="194"/>
+      <c r="L40" s="194"/>
+      <c r="M40" s="194"/>
+      <c r="N40" s="194"/>
+      <c r="O40" s="194"/>
+      <c r="P40" s="194"/>
+      <c r="Q40" s="194"/>
+      <c r="R40" s="194"/>
+      <c r="S40" s="194"/>
+      <c r="T40" s="194"/>
+      <c r="U40" s="194"/>
+      <c r="V40" s="194"/>
+      <c r="W40" s="194"/>
+      <c r="X40" s="194"/>
+      <c r="Y40" s="194"/>
+      <c r="Z40" s="194"/>
+      <c r="AA40" s="194"/>
+      <c r="AB40" s="194"/>
+      <c r="AC40" s="194"/>
+      <c r="AD40" s="194"/>
+      <c r="AE40" s="194"/>
+      <c r="AF40" s="194"/>
+      <c r="AG40" s="194"/>
+      <c r="AH40" s="194"/>
+      <c r="AI40" s="194"/>
+      <c r="AJ40" s="194"/>
+      <c r="AK40" s="194"/>
+      <c r="BA40" s="193"/>
+    </row>
+    <row r="41" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A41" s="195"/>
+      <c r="B41" s="194"/>
+      <c r="C41" s="194"/>
+      <c r="D41" s="194"/>
+      <c r="E41" s="194"/>
+      <c r="F41" s="194"/>
+      <c r="G41" s="194"/>
+      <c r="H41" s="194"/>
+      <c r="I41" s="194"/>
+      <c r="J41" s="194"/>
+      <c r="K41" s="194"/>
+      <c r="L41" s="194"/>
+      <c r="M41" s="194"/>
+      <c r="N41" s="194"/>
+      <c r="O41" s="194"/>
+      <c r="P41" s="194"/>
+      <c r="Q41" s="194"/>
+      <c r="R41" s="194"/>
+      <c r="S41" s="194"/>
+      <c r="T41" s="194"/>
+      <c r="U41" s="194"/>
+      <c r="V41" s="194"/>
+      <c r="W41" s="194"/>
+      <c r="X41" s="194"/>
+      <c r="Y41" s="194"/>
+      <c r="Z41" s="194"/>
+      <c r="AA41" s="194"/>
+      <c r="AB41" s="194"/>
+      <c r="AC41" s="194"/>
+      <c r="AD41" s="194"/>
+      <c r="AE41" s="194"/>
+      <c r="AF41" s="194"/>
+      <c r="AG41" s="194"/>
+      <c r="AH41" s="194"/>
+      <c r="AI41" s="194"/>
+      <c r="AJ41" s="194"/>
+      <c r="AK41" s="194"/>
+      <c r="BA41" s="193"/>
+    </row>
+    <row r="42" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A42" s="195"/>
+      <c r="B42" s="194"/>
+      <c r="C42" s="194"/>
+      <c r="D42" s="194"/>
+      <c r="E42" s="194"/>
+      <c r="F42" s="194"/>
+      <c r="G42" s="194"/>
+      <c r="H42" s="194"/>
+      <c r="I42" s="194"/>
+      <c r="J42" s="194"/>
+      <c r="K42" s="194"/>
+      <c r="L42" s="194"/>
+      <c r="M42" s="194"/>
+      <c r="N42" s="194"/>
+      <c r="O42" s="194"/>
+      <c r="P42" s="194"/>
+      <c r="Q42" s="194"/>
+      <c r="R42" s="194"/>
+      <c r="S42" s="194"/>
+      <c r="T42" s="194"/>
+      <c r="U42" s="194"/>
+      <c r="V42" s="194"/>
+      <c r="W42" s="194"/>
+      <c r="X42" s="194"/>
+      <c r="Y42" s="194"/>
+      <c r="Z42" s="194"/>
+      <c r="AA42" s="194"/>
+      <c r="AB42" s="194"/>
+      <c r="AC42" s="194"/>
+      <c r="AD42" s="194"/>
+      <c r="AE42" s="194"/>
+      <c r="AF42" s="194"/>
+      <c r="AG42" s="194"/>
+      <c r="AH42" s="194"/>
+      <c r="AI42" s="194"/>
+      <c r="AJ42" s="194"/>
+      <c r="AK42" s="194"/>
+      <c r="BA42" s="193"/>
+    </row>
+    <row r="43" spans="1:53" ht="18" customHeight="1">
+      <c r="A43" s="199" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="198"/>
+      <c r="C43" s="198"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="198"/>
+      <c r="F43" s="198"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="198"/>
+      <c r="T43" s="198"/>
+      <c r="U43" s="198"/>
+      <c r="V43" s="198"/>
+      <c r="W43" s="198"/>
+      <c r="X43" s="198"/>
+      <c r="Y43" s="198"/>
+      <c r="Z43" s="198"/>
+      <c r="AA43" s="198"/>
+      <c r="AB43" s="198"/>
+      <c r="AC43" s="198"/>
+      <c r="AD43" s="198"/>
+      <c r="AE43" s="198"/>
+      <c r="AF43" s="198"/>
+      <c r="AG43" s="198"/>
+      <c r="AH43" s="198"/>
+      <c r="AI43" s="198"/>
+      <c r="AJ43" s="198"/>
+      <c r="AK43" s="198"/>
+      <c r="AL43" s="198"/>
+      <c r="AM43" s="198"/>
+      <c r="AN43" s="198"/>
+      <c r="AO43" s="198"/>
+      <c r="AP43" s="198"/>
+      <c r="AQ43" s="198"/>
+      <c r="AR43" s="198"/>
+      <c r="AS43" s="198"/>
+      <c r="AT43" s="198"/>
+      <c r="AU43" s="198"/>
+      <c r="AV43" s="198"/>
+      <c r="AW43" s="198"/>
+      <c r="AX43" s="198"/>
+      <c r="AY43" s="198"/>
+      <c r="AZ43" s="198"/>
+      <c r="BA43" s="200"/>
+    </row>
+    <row r="44" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A44" s="197"/>
+      <c r="B44" s="196"/>
+      <c r="C44" s="196"/>
+      <c r="D44" s="196"/>
+      <c r="E44" s="196"/>
+      <c r="F44" s="196"/>
+      <c r="G44" s="196"/>
+      <c r="H44" s="196"/>
+      <c r="I44" s="196"/>
+      <c r="J44" s="196"/>
+      <c r="K44" s="196"/>
+      <c r="L44" s="196"/>
+      <c r="M44" s="196"/>
+      <c r="N44" s="196"/>
+      <c r="O44" s="196"/>
+      <c r="P44" s="196"/>
+      <c r="Q44" s="196"/>
+      <c r="R44" s="196"/>
+      <c r="S44" s="196"/>
+      <c r="T44" s="196"/>
+      <c r="U44" s="196"/>
+      <c r="V44" s="196"/>
+      <c r="W44" s="196"/>
+      <c r="X44" s="196"/>
+      <c r="Y44" s="196"/>
+      <c r="Z44" s="196"/>
+      <c r="AA44" s="196"/>
+      <c r="AB44" s="196"/>
+      <c r="AC44" s="196"/>
+      <c r="AD44" s="196"/>
+      <c r="AE44" s="196"/>
+      <c r="AF44" s="196"/>
+      <c r="AG44" s="196"/>
+      <c r="AH44" s="196"/>
+      <c r="AI44" s="194"/>
+      <c r="AJ44" s="194"/>
+      <c r="AK44" s="194"/>
+      <c r="BA44" s="193"/>
+    </row>
+    <row r="45" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A45" s="195"/>
+      <c r="B45" s="194"/>
+      <c r="C45" s="194"/>
+      <c r="D45" s="194"/>
+      <c r="E45" s="194"/>
+      <c r="F45" s="194"/>
+      <c r="G45" s="194"/>
+      <c r="H45" s="194"/>
+      <c r="I45" s="194"/>
+      <c r="J45" s="194"/>
+      <c r="K45" s="194"/>
+      <c r="L45" s="194"/>
+      <c r="M45" s="194"/>
+      <c r="N45" s="194"/>
+      <c r="O45" s="194"/>
+      <c r="P45" s="194"/>
+      <c r="Q45" s="194"/>
+      <c r="R45" s="194"/>
+      <c r="S45" s="194"/>
+      <c r="T45" s="194"/>
+      <c r="U45" s="194"/>
+      <c r="V45" s="194"/>
+      <c r="W45" s="194"/>
+      <c r="X45" s="194"/>
+      <c r="Y45" s="194"/>
+      <c r="Z45" s="194"/>
+      <c r="AA45" s="194"/>
+      <c r="AB45" s="194"/>
+      <c r="AC45" s="194"/>
+      <c r="AD45" s="194"/>
+      <c r="AE45" s="194"/>
+      <c r="AF45" s="194"/>
+      <c r="AG45" s="194"/>
+      <c r="AH45" s="194"/>
+      <c r="AI45" s="194"/>
+      <c r="AJ45" s="194"/>
+      <c r="AK45" s="194"/>
+      <c r="BA45" s="193"/>
+    </row>
+    <row r="46" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A46" s="195"/>
+      <c r="B46" s="194"/>
+      <c r="C46" s="194"/>
+      <c r="D46" s="194"/>
+      <c r="E46" s="194"/>
+      <c r="F46" s="194"/>
+      <c r="G46" s="194"/>
+      <c r="H46" s="194"/>
+      <c r="I46" s="194"/>
+      <c r="J46" s="194"/>
+      <c r="K46" s="194"/>
+      <c r="L46" s="194"/>
+      <c r="M46" s="194"/>
+      <c r="N46" s="194"/>
+      <c r="O46" s="194"/>
+      <c r="P46" s="194"/>
+      <c r="Q46" s="194"/>
+      <c r="R46" s="194"/>
+      <c r="S46" s="194"/>
+      <c r="T46" s="194"/>
+      <c r="U46" s="194"/>
+      <c r="V46" s="194"/>
+      <c r="W46" s="194"/>
+      <c r="X46" s="194"/>
+      <c r="Y46" s="194"/>
+      <c r="Z46" s="194"/>
+      <c r="AA46" s="194"/>
+      <c r="AB46" s="194"/>
+      <c r="AC46" s="194"/>
+      <c r="AD46" s="194"/>
+      <c r="AE46" s="194"/>
+      <c r="AF46" s="194"/>
+      <c r="AG46" s="194"/>
+      <c r="AH46" s="194"/>
+      <c r="AI46" s="194"/>
+      <c r="AJ46" s="194"/>
+      <c r="AK46" s="194"/>
+      <c r="BA46" s="193"/>
+    </row>
+    <row r="47" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A47" s="195"/>
+      <c r="B47" s="194"/>
+      <c r="C47" s="194"/>
+      <c r="D47" s="194"/>
+      <c r="E47" s="194"/>
+      <c r="F47" s="194"/>
+      <c r="G47" s="194"/>
+      <c r="H47" s="194"/>
+      <c r="I47" s="194"/>
+      <c r="J47" s="194"/>
+      <c r="K47" s="194"/>
+      <c r="L47" s="194"/>
+      <c r="M47" s="194"/>
+      <c r="N47" s="194"/>
+      <c r="O47" s="194"/>
+      <c r="P47" s="194"/>
+      <c r="Q47" s="194"/>
+      <c r="R47" s="194"/>
+      <c r="S47" s="194"/>
+      <c r="T47" s="194"/>
+      <c r="U47" s="194"/>
+      <c r="V47" s="194"/>
+      <c r="W47" s="194"/>
+      <c r="X47" s="194"/>
+      <c r="Y47" s="194"/>
+      <c r="Z47" s="194"/>
+      <c r="AA47" s="194"/>
+      <c r="AB47" s="194"/>
+      <c r="AC47" s="194"/>
+      <c r="AD47" s="194"/>
+      <c r="AE47" s="194"/>
+      <c r="AF47" s="194"/>
+      <c r="AG47" s="194"/>
+      <c r="AH47" s="194"/>
+      <c r="AI47" s="194"/>
+      <c r="AJ47" s="194"/>
+      <c r="AK47" s="194"/>
+      <c r="BA47" s="193"/>
+    </row>
+    <row r="48" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A48" s="195"/>
+      <c r="B48" s="194"/>
+      <c r="C48" s="194"/>
+      <c r="D48" s="194"/>
+      <c r="E48" s="194"/>
+      <c r="F48" s="194"/>
+      <c r="G48" s="194"/>
+      <c r="H48" s="194"/>
+      <c r="I48" s="194"/>
+      <c r="J48" s="194"/>
+      <c r="K48" s="194"/>
+      <c r="L48" s="194"/>
+      <c r="M48" s="194"/>
+      <c r="N48" s="194"/>
+      <c r="O48" s="194"/>
+      <c r="P48" s="194"/>
+      <c r="Q48" s="194"/>
+      <c r="R48" s="194"/>
+      <c r="S48" s="194"/>
+      <c r="T48" s="194"/>
+      <c r="U48" s="194"/>
+      <c r="V48" s="194"/>
+      <c r="W48" s="194"/>
+      <c r="X48" s="194"/>
+      <c r="Y48" s="194"/>
+      <c r="Z48" s="194"/>
+      <c r="AA48" s="194"/>
+      <c r="AB48" s="194"/>
+      <c r="AC48" s="194"/>
+      <c r="AD48" s="194"/>
+      <c r="AE48" s="194"/>
+      <c r="AF48" s="194"/>
+      <c r="AG48" s="194"/>
+      <c r="AH48" s="194"/>
+      <c r="AI48" s="194"/>
+      <c r="AJ48" s="194"/>
+      <c r="AK48" s="194"/>
+      <c r="BA48" s="193"/>
+    </row>
+    <row r="49" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A49" s="195"/>
+      <c r="B49" s="194"/>
+      <c r="C49" s="194"/>
+      <c r="D49" s="194"/>
+      <c r="E49" s="194"/>
+      <c r="F49" s="194"/>
+      <c r="G49" s="194"/>
+      <c r="H49" s="194"/>
+      <c r="I49" s="194"/>
+      <c r="J49" s="194"/>
+      <c r="K49" s="194"/>
+      <c r="L49" s="194"/>
+      <c r="M49" s="194"/>
+      <c r="N49" s="194"/>
+      <c r="O49" s="194"/>
+      <c r="P49" s="194"/>
+      <c r="Q49" s="194"/>
+      <c r="R49" s="194"/>
+      <c r="S49" s="194"/>
+      <c r="T49" s="194"/>
+      <c r="U49" s="194"/>
+      <c r="V49" s="194"/>
+      <c r="W49" s="194"/>
+      <c r="X49" s="194"/>
+      <c r="Y49" s="194"/>
+      <c r="Z49" s="194"/>
+      <c r="AA49" s="194"/>
+      <c r="AB49" s="194"/>
+      <c r="AC49" s="194"/>
+      <c r="AD49" s="194"/>
+      <c r="AE49" s="194"/>
+      <c r="AF49" s="194"/>
+      <c r="AG49" s="194"/>
+      <c r="AH49" s="194"/>
+      <c r="AI49" s="194"/>
+      <c r="AJ49" s="194"/>
+      <c r="AK49" s="194"/>
+      <c r="BA49" s="193"/>
+    </row>
+    <row r="50" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A50" s="195"/>
+      <c r="B50" s="194"/>
+      <c r="C50" s="194"/>
+      <c r="D50" s="194"/>
+      <c r="E50" s="194"/>
+      <c r="F50" s="194"/>
+      <c r="G50" s="194"/>
+      <c r="H50" s="194"/>
+      <c r="I50" s="194"/>
+      <c r="J50" s="194"/>
+      <c r="K50" s="194"/>
+      <c r="L50" s="194"/>
+      <c r="M50" s="194"/>
+      <c r="N50" s="194"/>
+      <c r="O50" s="194"/>
+      <c r="P50" s="194"/>
+      <c r="Q50" s="194"/>
+      <c r="R50" s="194"/>
+      <c r="S50" s="194"/>
+      <c r="T50" s="194"/>
+      <c r="U50" s="194"/>
+      <c r="V50" s="194"/>
+      <c r="W50" s="194"/>
+      <c r="X50" s="194"/>
+      <c r="Y50" s="194"/>
+      <c r="Z50" s="194"/>
+      <c r="AA50" s="194"/>
+      <c r="AB50" s="194"/>
+      <c r="AC50" s="194"/>
+      <c r="AD50" s="194"/>
+      <c r="AE50" s="194"/>
+      <c r="AF50" s="194"/>
+      <c r="AG50" s="194"/>
+      <c r="AH50" s="194"/>
+      <c r="AI50" s="194"/>
+      <c r="AJ50" s="194"/>
+      <c r="AK50" s="194"/>
+      <c r="BA50" s="193"/>
+    </row>
+    <row r="51" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A51" s="192"/>
+      <c r="B51" s="191"/>
+      <c r="C51" s="191"/>
+      <c r="D51" s="191"/>
+      <c r="E51" s="191"/>
+      <c r="F51" s="191"/>
+      <c r="G51" s="191"/>
+      <c r="H51" s="191"/>
+      <c r="I51" s="191"/>
+      <c r="J51" s="191"/>
+      <c r="K51" s="191"/>
+      <c r="L51" s="191"/>
+      <c r="M51" s="191"/>
+      <c r="N51" s="191"/>
+      <c r="O51" s="191"/>
+      <c r="P51" s="191"/>
+      <c r="Q51" s="191"/>
+      <c r="R51" s="191"/>
+      <c r="S51" s="191"/>
+      <c r="T51" s="191"/>
+      <c r="U51" s="191"/>
+      <c r="V51" s="191"/>
+      <c r="W51" s="191"/>
+      <c r="X51" s="191"/>
+      <c r="Y51" s="191"/>
+      <c r="Z51" s="191"/>
+      <c r="AA51" s="191"/>
+      <c r="AB51" s="191"/>
+      <c r="AC51" s="191"/>
+      <c r="AD51" s="191"/>
+      <c r="AE51" s="191"/>
+      <c r="AF51" s="191"/>
+      <c r="AG51" s="191"/>
+      <c r="AH51" s="191"/>
+      <c r="AI51" s="191"/>
+      <c r="AJ51" s="191"/>
+      <c r="AK51" s="194"/>
+      <c r="BA51" s="193"/>
+    </row>
+    <row r="52" spans="1:53" ht="18" customHeight="1">
+      <c r="A52" s="199" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="198"/>
+      <c r="C52" s="198"/>
+      <c r="D52" s="198"/>
+      <c r="E52" s="198"/>
+      <c r="F52" s="198"/>
+      <c r="G52" s="198"/>
+      <c r="H52" s="198"/>
+      <c r="I52" s="198"/>
+      <c r="J52" s="198"/>
+      <c r="K52" s="198"/>
+      <c r="L52" s="198"/>
+      <c r="M52" s="198"/>
+      <c r="N52" s="198"/>
+      <c r="O52" s="198"/>
+      <c r="P52" s="198"/>
+      <c r="Q52" s="198"/>
+      <c r="R52" s="198"/>
+      <c r="S52" s="198"/>
+      <c r="T52" s="198"/>
+      <c r="U52" s="198"/>
+      <c r="V52" s="198"/>
+      <c r="W52" s="198"/>
+      <c r="X52" s="198"/>
+      <c r="Y52" s="198"/>
+      <c r="Z52" s="198"/>
+      <c r="AA52" s="198"/>
+      <c r="AB52" s="198"/>
+      <c r="AC52" s="198"/>
+      <c r="AD52" s="198"/>
+      <c r="AE52" s="198"/>
+      <c r="AF52" s="198"/>
+      <c r="AG52" s="198"/>
+      <c r="AH52" s="198"/>
+      <c r="AI52" s="198"/>
+      <c r="AJ52" s="198"/>
+      <c r="AK52" s="198"/>
+      <c r="AL52" s="198"/>
+      <c r="AM52" s="198"/>
+      <c r="AN52" s="198"/>
+      <c r="AO52" s="198"/>
+      <c r="AP52" s="198"/>
+      <c r="AQ52" s="198"/>
+      <c r="AR52" s="198"/>
+      <c r="AS52" s="198"/>
+      <c r="AT52" s="198"/>
+      <c r="AU52" s="198"/>
+      <c r="AV52" s="198"/>
+      <c r="AW52" s="198"/>
+      <c r="AX52" s="198"/>
+      <c r="AY52" s="198"/>
+      <c r="AZ52" s="198"/>
+      <c r="BA52" s="198"/>
+    </row>
+    <row r="53" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A53" s="197"/>
+      <c r="B53" s="196"/>
+      <c r="C53" s="196"/>
+      <c r="D53" s="196"/>
+      <c r="E53" s="196"/>
+      <c r="F53" s="196"/>
+      <c r="G53" s="196"/>
+      <c r="H53" s="196"/>
+      <c r="I53" s="196"/>
+      <c r="J53" s="196"/>
+      <c r="K53" s="196"/>
+      <c r="L53" s="196"/>
+      <c r="M53" s="196"/>
+      <c r="N53" s="196"/>
+      <c r="O53" s="196"/>
+      <c r="P53" s="196"/>
+      <c r="Q53" s="196"/>
+      <c r="R53" s="196"/>
+      <c r="S53" s="196"/>
+      <c r="T53" s="196"/>
+      <c r="U53" s="196"/>
+      <c r="V53" s="196"/>
+      <c r="W53" s="196"/>
+      <c r="X53" s="196"/>
+      <c r="Y53" s="196"/>
+      <c r="Z53" s="196"/>
+      <c r="AA53" s="196"/>
+      <c r="AB53" s="196"/>
+      <c r="AC53" s="196"/>
+      <c r="AD53" s="196"/>
+      <c r="AE53" s="196"/>
+      <c r="AF53" s="196"/>
+      <c r="AG53" s="196"/>
+      <c r="AH53" s="196"/>
+      <c r="AI53" s="196"/>
+      <c r="AJ53" s="196"/>
+      <c r="AK53" s="194"/>
+      <c r="BA53" s="193"/>
+    </row>
+    <row r="54" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A54" s="195"/>
+      <c r="B54" s="194"/>
+      <c r="C54" s="194"/>
+      <c r="D54" s="194"/>
+      <c r="E54" s="194"/>
+      <c r="F54" s="194"/>
+      <c r="G54" s="194"/>
+      <c r="H54" s="194"/>
+      <c r="I54" s="194"/>
+      <c r="J54" s="194"/>
+      <c r="K54" s="194"/>
+      <c r="L54" s="194"/>
+      <c r="M54" s="194"/>
+      <c r="N54" s="194"/>
+      <c r="O54" s="194"/>
+      <c r="P54" s="194"/>
+      <c r="Q54" s="194"/>
+      <c r="R54" s="194"/>
+      <c r="S54" s="194"/>
+      <c r="T54" s="194"/>
+      <c r="U54" s="194"/>
+      <c r="V54" s="194"/>
+      <c r="W54" s="194"/>
+      <c r="X54" s="194"/>
+      <c r="Y54" s="194"/>
+      <c r="Z54" s="194"/>
+      <c r="AA54" s="194"/>
+      <c r="AB54" s="194"/>
+      <c r="AC54" s="194"/>
+      <c r="AD54" s="194"/>
+      <c r="AE54" s="194"/>
+      <c r="AF54" s="194"/>
+      <c r="AG54" s="194"/>
+      <c r="AH54" s="194"/>
+      <c r="AI54" s="194"/>
+      <c r="AJ54" s="194"/>
+      <c r="AK54" s="194"/>
+      <c r="BA54" s="193"/>
+    </row>
+    <row r="55" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A55" s="192"/>
+      <c r="B55" s="191"/>
+      <c r="C55" s="191"/>
+      <c r="D55" s="191"/>
+      <c r="E55" s="191"/>
+      <c r="F55" s="191"/>
+      <c r="G55" s="191"/>
+      <c r="H55" s="191"/>
+      <c r="I55" s="191"/>
+      <c r="J55" s="191"/>
+      <c r="K55" s="191"/>
+      <c r="L55" s="191"/>
+      <c r="M55" s="191"/>
+      <c r="N55" s="191"/>
+      <c r="O55" s="191"/>
+      <c r="P55" s="191"/>
+      <c r="Q55" s="191"/>
+      <c r="R55" s="191"/>
+      <c r="S55" s="191"/>
+      <c r="T55" s="191"/>
+      <c r="U55" s="191"/>
+      <c r="V55" s="191"/>
+      <c r="W55" s="191"/>
+      <c r="X55" s="191"/>
+      <c r="Y55" s="191"/>
+      <c r="Z55" s="191"/>
+      <c r="AA55" s="191"/>
+      <c r="AB55" s="191"/>
+      <c r="AC55" s="191"/>
+      <c r="AD55" s="191"/>
+      <c r="AE55" s="191"/>
+      <c r="AF55" s="191"/>
+      <c r="AG55" s="191"/>
+      <c r="AH55" s="191"/>
+      <c r="AI55" s="191"/>
+      <c r="AJ55" s="191"/>
+      <c r="AK55" s="191"/>
+      <c r="AL55" s="190"/>
+      <c r="AM55" s="190"/>
+      <c r="AN55" s="190"/>
+      <c r="AO55" s="190"/>
+      <c r="AP55" s="190"/>
+      <c r="AQ55" s="190"/>
+      <c r="AR55" s="190"/>
+      <c r="AS55" s="190"/>
+      <c r="AT55" s="190"/>
+      <c r="AU55" s="190"/>
+      <c r="AV55" s="190"/>
+      <c r="AW55" s="190"/>
+      <c r="AX55" s="190"/>
+      <c r="AY55" s="190"/>
+      <c r="AZ55" s="190"/>
+      <c r="BA55" s="189"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A9:BA9"/>
+    <mergeCell ref="A43:BA43"/>
+    <mergeCell ref="A52:BA52"/>
+    <mergeCell ref="AT1:BA1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:S5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:S6"/>
+    <mergeCell ref="AO1:AS1"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <dataValidations count="2">
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A10:AK42 N1:O1 I1:L1 A53:AK55 G5:G6 V1 AC1 AE1 A44:AK51" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>